--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9896,6 +9896,130 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>109015621</v>
+      </c>
+      <c r="B79" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Moberg, Hackmora, Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>512218</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6733064</v>
+      </c>
+      <c r="S79" t="n">
+        <v>75</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10020,6 +10020,260 @@
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120520450</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Leksand Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>511633</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6733072</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rakt fram i bild skymtar en myr,/mosse en av många  myrar/mossar, i området</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120516126</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>511388</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6733145</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Vi såg och hörde två talltitor ikring oss en stund, söta!</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -10022,7 +10022,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120520450</v>
+        <v>120516126</v>
       </c>
       <c r="B80" t="n">
         <v>57473</v>
@@ -10055,7 +10055,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
@@ -10066,14 +10070,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>511633</v>
+        <v>511388</v>
       </c>
       <c r="R80" t="n">
-        <v>6733072</v>
+        <v>6733145</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10105,7 +10109,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10115,12 +10119,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Rakt fram i bild skymtar en myr,/mosse en av många  myrar/mossar, i området</t>
+          <t>Vi såg och hörde två talltitor ikring oss en stund, söta!</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10140,14 +10144,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120516126</v>
+        <v>120520450</v>
       </c>
       <c r="B81" t="n">
         <v>57473</v>
@@ -10180,11 +10184,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
@@ -10195,14 +10195,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>511388</v>
+        <v>511633</v>
       </c>
       <c r="R81" t="n">
-        <v>6733145</v>
+        <v>6733072</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Vi såg och hörde två talltitor ikring oss en stund, söta!</t>
+          <t>Rakt fram i bild skymtar en myr,/mosse en av många  myrar/mossar, i området</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12856,6 +12856,490 @@
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121401369</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>512088</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6733213</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosök, mycket rikligt med död ved.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>121401438</v>
+      </c>
+      <c r="B104" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>512055</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6733202</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121401354</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>512088</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6733213</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121401511</v>
+      </c>
+      <c r="B106" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hackmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>512151</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6733225</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401369</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12952,11 +12952,6 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12983,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B104" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12995,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13021,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13066,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13076,12 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13108,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B105" t="n">
-        <v>57504</v>
+        <v>56563</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13120,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13146,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R105" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13191,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13201,7 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13340,6 +13340,3291 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>121425509</v>
+      </c>
+      <c r="B107" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>512110</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6733025</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>121426863</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>512104</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6733063</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>121423745</v>
+      </c>
+      <c r="B109" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>511789</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6732877</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>121423726</v>
+      </c>
+      <c r="B110" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>512164</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6733000</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>121423760</v>
+      </c>
+      <c r="B111" t="n">
+        <v>92008</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>511818</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6733114</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>121423788</v>
+      </c>
+      <c r="B112" t="n">
+        <v>100347</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>511830</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6732919</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>121423779</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>512098</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6733157</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>121423781</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>512210</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6733094</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>121425773</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>512215</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6733081</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>121425511</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>512223</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6733062</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>121426864</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>512216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6733046</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>121425818</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>512221</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6733056</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121423780</v>
+      </c>
+      <c r="B119" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>512100</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6733148</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>121425857</v>
+      </c>
+      <c r="B120" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>512211</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6733056</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>121425156</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>512108</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6733054</v>
+      </c>
+      <c r="S121" t="n">
+        <v>15</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121423757</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>512093</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6733205</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121425519</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>512131</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6733029</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>121425158</v>
+      </c>
+      <c r="B124" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>512156</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6733044</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>121425157</v>
+      </c>
+      <c r="B125" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>512155</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6733037</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>121425159</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>512216</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6733046</v>
+      </c>
+      <c r="S126" t="n">
+        <v>15</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>121423776</v>
+      </c>
+      <c r="B127" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>512152</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6733230</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>121423767</v>
+      </c>
+      <c r="B128" t="n">
+        <v>90910</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>512147</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6733153</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>121423778</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>512091</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6733225</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>121423777</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>512148</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6733216</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>121423727</v>
+      </c>
+      <c r="B131" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>512156</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6733279</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>121426316</v>
+      </c>
+      <c r="B132" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>658</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>512215</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6733055</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>121425507</v>
+      </c>
+      <c r="B133" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>512100</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6733039</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>121425873</v>
+      </c>
+      <c r="B134" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>512218</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6733062</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>121423747</v>
+      </c>
+      <c r="B135" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>512148</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6733263</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>121426859</v>
+      </c>
+      <c r="B136" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>512108</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6733054</v>
+      </c>
+      <c r="S136" t="n">
+        <v>15</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14195,10 +14195,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425773</v>
+        <v>121425511</v>
       </c>
       <c r="B115" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14211,45 +14211,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512215</v>
+        <v>512223</v>
       </c>
       <c r="R115" t="n">
-        <v>6733081</v>
+        <v>6733062</v>
       </c>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14293,22 +14285,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121425511</v>
+        <v>121426864</v>
       </c>
       <c r="B116" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14321,37 +14313,45 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512223</v>
+        <v>512216</v>
       </c>
       <c r="R116" t="n">
-        <v>6733062</v>
+        <v>6733046</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14378,9 +14378,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14395,22 +14410,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121426864</v>
+        <v>121425818</v>
       </c>
       <c r="B117" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14423,45 +14438,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512216</v>
+        <v>512221</v>
       </c>
       <c r="R117" t="n">
-        <v>6733046</v>
+        <v>6733056</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14488,51 +14506,37 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425818</v>
+        <v>121423780</v>
       </c>
       <c r="B118" t="n">
         <v>78601</v>
@@ -14565,31 +14569,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512221</v>
+        <v>512100</v>
       </c>
       <c r="R118" t="n">
-        <v>6733056</v>
+        <v>6733148</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14627,26 +14620,25 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423780</v>
+        <v>121425857</v>
       </c>
       <c r="B119" t="n">
         <v>78601</v>
@@ -14679,20 +14671,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512100</v>
+        <v>512211</v>
       </c>
       <c r="R119" t="n">
-        <v>6733148</v>
+        <v>6733056</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14730,25 +14733,26 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425857</v>
+        <v>121425156</v>
       </c>
       <c r="B120" t="n">
         <v>78601</v>
@@ -14781,31 +14785,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512211</v>
+        <v>512108</v>
       </c>
       <c r="R120" t="n">
-        <v>6733056</v>
+        <v>6733054</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14832,9 +14828,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14850,22 +14856,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121425156</v>
+        <v>121423757</v>
       </c>
       <c r="B121" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14878,40 +14884,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512108</v>
+        <v>512093</v>
       </c>
       <c r="R121" t="n">
-        <v>6733054</v>
+        <v>6733205</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14938,19 +14946,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14959,29 +14962,28 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423757</v>
+        <v>121425519</v>
       </c>
       <c r="B122" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14994,39 +14996,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512093</v>
+        <v>512131</v>
       </c>
       <c r="R122" t="n">
-        <v>6733205</v>
+        <v>6733029</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15061,11 +15058,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -15078,19 +15070,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121425519</v>
+        <v>121425158</v>
       </c>
       <c r="B123" t="n">
         <v>78601</v>
@@ -15124,19 +15116,22 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512131</v>
+        <v>512156</v>
       </c>
       <c r="R123" t="n">
-        <v>6733029</v>
+        <v>6733044</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15163,36 +15158,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121425158</v>
+        <v>121425157</v>
       </c>
       <c r="B124" t="n">
         <v>78601</v>
@@ -15235,10 +15241,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512156</v>
+        <v>512155</v>
       </c>
       <c r="R124" t="n">
-        <v>6733044</v>
+        <v>6733037</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -15270,7 +15276,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15280,7 +15286,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15308,7 +15314,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425157</v>
+        <v>121425159</v>
       </c>
       <c r="B125" t="n">
         <v>78601</v>
@@ -15351,10 +15357,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512155</v>
+        <v>512216</v>
       </c>
       <c r="R125" t="n">
-        <v>6733037</v>
+        <v>6733046</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -15386,7 +15392,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15396,7 +15402,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15424,7 +15435,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121425159</v>
+        <v>121423776</v>
       </c>
       <c r="B126" t="n">
         <v>78601</v>
@@ -15458,22 +15469,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512216</v>
+        <v>512152</v>
       </c>
       <c r="R126" t="n">
-        <v>6733046</v>
+        <v>6733230</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15500,55 +15508,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423776</v>
+        <v>121423767</v>
       </c>
       <c r="B127" t="n">
-        <v>78601</v>
+        <v>90910</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15557,38 +15549,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512152</v>
+        <v>512147</v>
       </c>
       <c r="R127" t="n">
-        <v>6733230</v>
+        <v>6733153</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15629,6 +15624,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -15647,10 +15643,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423767</v>
+        <v>121423778</v>
       </c>
       <c r="B128" t="n">
-        <v>90910</v>
+        <v>78601</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15659,41 +15655,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512147</v>
+        <v>512091</v>
       </c>
       <c r="R128" t="n">
-        <v>6733153</v>
+        <v>6733225</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15734,7 +15727,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -15753,7 +15745,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423778</v>
+        <v>121423777</v>
       </c>
       <c r="B129" t="n">
         <v>78601</v>
@@ -15793,10 +15785,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512091</v>
+        <v>512148</v>
       </c>
       <c r="R129" t="n">
-        <v>6733225</v>
+        <v>6733216</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15855,10 +15847,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423777</v>
+        <v>121423727</v>
       </c>
       <c r="B130" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15867,25 +15859,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15895,10 +15887,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512148</v>
+        <v>512156</v>
       </c>
       <c r="R130" t="n">
-        <v>6733216</v>
+        <v>6733279</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15957,10 +15949,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423727</v>
+        <v>121426316</v>
       </c>
       <c r="B131" t="n">
-        <v>90662</v>
+        <v>90983</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15969,41 +15961,48 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512156</v>
+        <v>512215</v>
       </c>
       <c r="R131" t="n">
-        <v>6733279</v>
+        <v>6733055</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16030,39 +16029,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121426316</v>
+        <v>121425507</v>
       </c>
       <c r="B132" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16075,44 +16085,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512215</v>
+        <v>512100</v>
       </c>
       <c r="R132" t="n">
-        <v>6733055</v>
+        <v>6733039</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16139,19 +16142,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:06</t>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16160,29 +16158,28 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121425507</v>
+        <v>121425873</v>
       </c>
       <c r="B133" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16195,37 +16192,48 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512100</v>
+        <v>512218</v>
       </c>
       <c r="R133" t="n">
-        <v>6733039</v>
+        <v>6733062</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16257,39 +16265,35 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121425873</v>
+        <v>121423747</v>
       </c>
       <c r="B134" t="n">
-        <v>90697</v>
+        <v>4766</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16298,52 +16302,46 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512218</v>
+        <v>512148</v>
       </c>
       <c r="R134" t="n">
-        <v>6733062</v>
+        <v>6733263</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16381,29 +16379,28 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121423747</v>
+        <v>121426850</v>
       </c>
       <c r="B135" t="n">
-        <v>4766</v>
+        <v>90697</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16412,46 +16409,44 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512148</v>
+        <v>512216</v>
       </c>
       <c r="R135" t="n">
-        <v>6733263</v>
+        <v>6733046</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16478,39 +16473,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121425773</v>
       </c>
       <c r="B136" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16519,25 +16525,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16545,23 +16551,23 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733081</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16588,19 +16594,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16615,15 +16616,259 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>121426859</v>
+      </c>
+      <c r="B137" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>512108</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6733054</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
+      <c r="AX137" t="inlineStr">
         <is>
           <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
-      <c r="AY136" t="inlineStr"/>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>121426851</v>
+      </c>
+      <c r="B138" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Hackmora Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>512219</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6733049</v>
+      </c>
+      <c r="S138" t="n">
+        <v>15</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12978,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401369</v>
+        <v>121401438</v>
       </c>
       <c r="B104" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R104" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13103,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B105" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13115,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13141,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R105" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13196,12 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13342,7 +13342,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425509</v>
+        <v>121425510</v>
       </c>
       <c r="B107" t="n">
         <v>78601</v>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512110</v>
+        <v>512131</v>
       </c>
       <c r="R107" t="n">
-        <v>6733025</v>
+        <v>6733029</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13444,10 +13444,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121426863</v>
+        <v>121423778</v>
       </c>
       <c r="B108" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13460,45 +13460,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512104</v>
+        <v>512091</v>
       </c>
       <c r="R108" t="n">
-        <v>6733063</v>
+        <v>6733225</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13525,24 +13517,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13557,22 +13534,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423745</v>
+        <v>121425511</v>
       </c>
       <c r="B109" t="n">
-        <v>56563</v>
+        <v>78601</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13581,43 +13558,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>511789</v>
+        <v>512223</v>
       </c>
       <c r="R109" t="n">
-        <v>6732877</v>
+        <v>6733062</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13664,22 +13636,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423726</v>
+        <v>121425509</v>
       </c>
       <c r="B110" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13688,25 +13660,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13716,10 +13688,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512164</v>
+        <v>512110</v>
       </c>
       <c r="R110" t="n">
-        <v>6733000</v>
+        <v>6733025</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13766,22 +13738,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423760</v>
+        <v>121425873</v>
       </c>
       <c r="B111" t="n">
-        <v>92008</v>
+        <v>90697</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13794,46 +13766,48 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>511818</v>
+        <v>512218</v>
       </c>
       <c r="R111" t="n">
-        <v>6733114</v>
+        <v>6733062</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13871,28 +13845,29 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423788</v>
+        <v>121423779</v>
       </c>
       <c r="B112" t="n">
-        <v>100347</v>
+        <v>78601</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13901,25 +13876,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13929,10 +13904,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>511830</v>
+        <v>512098</v>
       </c>
       <c r="R112" t="n">
-        <v>6732919</v>
+        <v>6733157</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13991,7 +13966,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423779</v>
+        <v>121423776</v>
       </c>
       <c r="B113" t="n">
         <v>78601</v>
@@ -14031,10 +14006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512098</v>
+        <v>512152</v>
       </c>
       <c r="R113" t="n">
-        <v>6733157</v>
+        <v>6733230</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14093,10 +14068,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423781</v>
+        <v>121426863</v>
       </c>
       <c r="B114" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14109,37 +14084,45 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512210</v>
+        <v>512104</v>
       </c>
       <c r="R114" t="n">
-        <v>6733094</v>
+        <v>6733063</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14166,9 +14149,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14183,22 +14181,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425511</v>
+        <v>121423745</v>
       </c>
       <c r="B115" t="n">
-        <v>78601</v>
+        <v>56563</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14207,38 +14205,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512223</v>
+        <v>511789</v>
       </c>
       <c r="R115" t="n">
-        <v>6733062</v>
+        <v>6732877</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14285,22 +14288,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121426864</v>
+        <v>121423757</v>
       </c>
       <c r="B116" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14313,16 +14316,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -14331,27 +14334,24 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512216</v>
+        <v>512093</v>
       </c>
       <c r="R116" t="n">
-        <v>6733046</v>
+        <v>6733205</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14378,24 +14378,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>mycket färska födosökshack</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14410,19 +14400,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425818</v>
+        <v>121425156</v>
       </c>
       <c r="B117" t="n">
         <v>78601</v>
@@ -14455,31 +14445,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512221</v>
+        <v>512108</v>
       </c>
       <c r="R117" t="n">
-        <v>6733056</v>
+        <v>6733054</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14506,9 +14488,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14524,19 +14516,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121423780</v>
+        <v>121425516</v>
       </c>
       <c r="B118" t="n">
         <v>78601</v>
@@ -14579,7 +14571,7 @@
         <v>512100</v>
       </c>
       <c r="R118" t="n">
-        <v>6733148</v>
+        <v>6733039</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14614,6 +14606,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14626,19 +14623,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425857</v>
+        <v>121425818</v>
       </c>
       <c r="B119" t="n">
         <v>78601</v>
@@ -14673,7 +14670,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14689,7 +14686,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512211</v>
+        <v>512221</v>
       </c>
       <c r="R119" t="n">
         <v>6733056</v>
@@ -14752,10 +14749,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425156</v>
+        <v>121423767</v>
       </c>
       <c r="B120" t="n">
-        <v>78601</v>
+        <v>90910</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14764,25 +14761,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14791,17 +14788,17 @@
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512108</v>
+        <v>512147</v>
       </c>
       <c r="R120" t="n">
-        <v>6733054</v>
+        <v>6733153</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14828,19 +14825,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14856,22 +14843,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423757</v>
+        <v>121423747</v>
       </c>
       <c r="B121" t="n">
-        <v>57351</v>
+        <v>4766</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14880,31 +14867,31 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14913,10 +14900,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512093</v>
+        <v>512148</v>
       </c>
       <c r="R121" t="n">
-        <v>6733205</v>
+        <v>6733263</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14949,11 +14936,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14980,7 +14962,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425519</v>
+        <v>121425157</v>
       </c>
       <c r="B122" t="n">
         <v>78601</v>
@@ -15014,19 +14996,22 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512131</v>
+        <v>512155</v>
       </c>
       <c r="R122" t="n">
-        <v>6733029</v>
+        <v>6733037</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15053,36 +15038,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121425158</v>
+        <v>121423781</v>
       </c>
       <c r="B123" t="n">
         <v>78601</v>
@@ -15116,22 +15112,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512156</v>
+        <v>512210</v>
       </c>
       <c r="R123" t="n">
-        <v>6733044</v>
+        <v>6733094</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15158,47 +15151,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121425157</v>
+        <v>121425158</v>
       </c>
       <c r="B124" t="n">
         <v>78601</v>
@@ -15241,10 +15223,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512155</v>
+        <v>512156</v>
       </c>
       <c r="R124" t="n">
-        <v>6733037</v>
+        <v>6733044</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -15276,7 +15258,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15286,7 +15268,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15314,10 +15296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425159</v>
+        <v>121423727</v>
       </c>
       <c r="B125" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15326,44 +15308,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512216</v>
+        <v>512156</v>
       </c>
       <c r="R125" t="n">
-        <v>6733046</v>
+        <v>6733279</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15390,55 +15369,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423776</v>
+        <v>121423760</v>
       </c>
       <c r="B126" t="n">
-        <v>78601</v>
+        <v>92008</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15451,34 +15414,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512152</v>
+        <v>511818</v>
       </c>
       <c r="R126" t="n">
-        <v>6733230</v>
+        <v>6733114</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15537,10 +15509,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423767</v>
+        <v>121423780</v>
       </c>
       <c r="B127" t="n">
-        <v>90910</v>
+        <v>78601</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15549,41 +15521,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512147</v>
+        <v>512100</v>
       </c>
       <c r="R127" t="n">
-        <v>6733153</v>
+        <v>6733148</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15624,7 +15593,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -15643,10 +15611,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423778</v>
+        <v>121423726</v>
       </c>
       <c r="B128" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15655,25 +15623,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15683,10 +15651,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512091</v>
+        <v>512164</v>
       </c>
       <c r="R128" t="n">
-        <v>6733225</v>
+        <v>6733000</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15738,14 +15706,14 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423777</v>
+        <v>121425159</v>
       </c>
       <c r="B129" t="n">
         <v>78601</v>
@@ -15779,19 +15747,22 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512148</v>
+        <v>512216</v>
       </c>
       <c r="R129" t="n">
-        <v>6733216</v>
+        <v>6733046</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15818,39 +15789,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423727</v>
+        <v>121426864</v>
       </c>
       <c r="B130" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15859,41 +15846,49 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512156</v>
+        <v>512216</v>
       </c>
       <c r="R130" t="n">
-        <v>6733279</v>
+        <v>6733046</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15920,9 +15915,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15937,22 +15947,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121426316</v>
+        <v>121425857</v>
       </c>
       <c r="B131" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15965,21 +15975,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -15987,22 +15997,26 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512215</v>
+        <v>512211</v>
       </c>
       <c r="R131" t="n">
-        <v>6733055</v>
+        <v>6733056</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16029,19 +16043,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16057,22 +16061,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425507</v>
+        <v>121423788</v>
       </c>
       <c r="B132" t="n">
-        <v>78601</v>
+        <v>100347</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16081,25 +16085,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -16109,10 +16113,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512100</v>
+        <v>511830</v>
       </c>
       <c r="R132" t="n">
-        <v>6733039</v>
+        <v>6732919</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16147,11 +16151,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -16164,22 +16163,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121425873</v>
+        <v>121426316</v>
       </c>
       <c r="B133" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16192,48 +16191,44 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512218</v>
+        <v>512215</v>
       </c>
       <c r="R133" t="n">
-        <v>6733062</v>
+        <v>6733055</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16260,9 +16255,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16278,22 +16283,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423747</v>
+        <v>121423777</v>
       </c>
       <c r="B134" t="n">
-        <v>4766</v>
+        <v>78601</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16302,33 +16307,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
@@ -16338,7 +16338,7 @@
         <v>512148</v>
       </c>
       <c r="R134" t="n">
-        <v>6733263</v>
+        <v>6733216</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16397,7 +16397,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426850</v>
+        <v>121426851</v>
       </c>
       <c r="B135" t="n">
         <v>90697</v>
@@ -16430,8 +16430,16 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -16440,10 +16448,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512216</v>
+        <v>512219</v>
       </c>
       <c r="R135" t="n">
-        <v>6733046</v>
+        <v>6733049</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16475,7 +16483,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16485,7 +16493,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16513,10 +16521,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121425773</v>
+        <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16525,25 +16533,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16551,23 +16559,23 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512215</v>
+        <v>512108</v>
       </c>
       <c r="R136" t="n">
-        <v>6733081</v>
+        <v>6733054</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16594,14 +16602,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16616,22 +16629,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B137" t="n">
-        <v>56563</v>
+        <v>90697</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16640,35 +16653,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16676,10 +16684,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R137" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16711,7 +16719,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16721,7 +16729,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16730,6 +16738,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16748,10 +16757,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121426851</v>
+        <v>121425773</v>
       </c>
       <c r="B138" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16764,48 +16773,45 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512219</v>
+        <v>512215</v>
       </c>
       <c r="R138" t="n">
-        <v>6733049</v>
+        <v>6733081</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16832,19 +16838,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>13:09</t>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16853,19 +16854,18 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16521,10 +16521,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B136" t="n">
-        <v>56563</v>
+        <v>90697</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16533,35 +16533,30 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16569,10 +16564,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16604,7 +16599,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16614,7 +16609,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16623,6 +16618,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16641,10 +16637,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B137" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16653,30 +16649,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16684,10 +16685,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R137" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16719,7 +16720,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16729,7 +16730,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16738,7 +16739,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401354</v>
+        <v>121401369</v>
       </c>
       <c r="B103" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12952,6 +12952,11 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12978,10 +12983,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B104" t="n">
-        <v>56563</v>
+        <v>57504</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12995,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13021,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13076,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13103,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401369</v>
+        <v>121401438</v>
       </c>
       <c r="B105" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13115,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13141,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R105" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13196,12 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425510</v>
+        <v>121423726</v>
       </c>
       <c r="B107" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,25 +13354,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512131</v>
+        <v>512164</v>
       </c>
       <c r="R107" t="n">
-        <v>6733029</v>
+        <v>6733000</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13432,22 +13432,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423778</v>
+        <v>121425510</v>
       </c>
       <c r="B108" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13484,10 +13484,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512091</v>
+        <v>512131</v>
       </c>
       <c r="R108" t="n">
-        <v>6733225</v>
+        <v>6733029</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13534,22 +13534,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425511</v>
+        <v>121423747</v>
       </c>
       <c r="B109" t="n">
-        <v>78601</v>
+        <v>4766</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13558,38 +13558,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512223</v>
+        <v>512148</v>
       </c>
       <c r="R109" t="n">
-        <v>6733062</v>
+        <v>6733263</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13636,22 +13641,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121425509</v>
+        <v>121423760</v>
       </c>
       <c r="B110" t="n">
-        <v>78601</v>
+        <v>92020</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13664,34 +13669,43 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512110</v>
+        <v>511818</v>
       </c>
       <c r="R110" t="n">
-        <v>6733025</v>
+        <v>6733114</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13738,22 +13752,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425873</v>
+        <v>121425516</v>
       </c>
       <c r="B111" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13766,48 +13780,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512218</v>
+        <v>512100</v>
       </c>
       <c r="R111" t="n">
-        <v>6733062</v>
+        <v>6733039</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13839,35 +13842,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423779</v>
+        <v>121423788</v>
       </c>
       <c r="B112" t="n">
-        <v>78601</v>
+        <v>100360</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13876,25 +13883,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13904,10 +13911,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512098</v>
+        <v>511830</v>
       </c>
       <c r="R112" t="n">
-        <v>6733157</v>
+        <v>6732919</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13966,10 +13973,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423776</v>
+        <v>121423727</v>
       </c>
       <c r="B113" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13978,25 +13985,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14006,10 +14013,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512152</v>
+        <v>512156</v>
       </c>
       <c r="R113" t="n">
-        <v>6733230</v>
+        <v>6733279</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14068,10 +14075,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121426863</v>
+        <v>121423781</v>
       </c>
       <c r="B114" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14084,45 +14091,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512104</v>
+        <v>512210</v>
       </c>
       <c r="R114" t="n">
-        <v>6733063</v>
+        <v>6733094</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14149,24 +14148,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14181,22 +14165,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121423745</v>
+        <v>121426863</v>
       </c>
       <c r="B115" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14205,46 +14189,49 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>511789</v>
+        <v>512104</v>
       </c>
       <c r="R115" t="n">
-        <v>6732877</v>
+        <v>6733063</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14271,9 +14258,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14288,22 +14290,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423757</v>
+        <v>121426864</v>
       </c>
       <c r="B116" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14316,16 +14318,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -14334,24 +14336,27 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512093</v>
+        <v>512216</v>
       </c>
       <c r="R116" t="n">
-        <v>6733205</v>
+        <v>6733046</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14378,14 +14383,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14400,22 +14415,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425156</v>
+        <v>121423778</v>
       </c>
       <c r="B117" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14446,22 +14461,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512108</v>
+        <v>512091</v>
       </c>
       <c r="R117" t="n">
-        <v>6733054</v>
+        <v>6733225</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14488,50 +14500,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425516</v>
+        <v>121425511</v>
       </c>
       <c r="B118" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14568,10 +14569,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512100</v>
+        <v>512223</v>
       </c>
       <c r="R118" t="n">
-        <v>6733039</v>
+        <v>6733062</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14604,11 +14605,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>mycket</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14635,10 +14631,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425818</v>
+        <v>121423776</v>
       </c>
       <c r="B119" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14668,31 +14664,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512221</v>
+        <v>512152</v>
       </c>
       <c r="R119" t="n">
-        <v>6733056</v>
+        <v>6733230</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14730,29 +14715,28 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121423767</v>
+        <v>121425157</v>
       </c>
       <c r="B120" t="n">
-        <v>90910</v>
+        <v>78604</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14761,25 +14745,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14788,17 +14772,17 @@
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512147</v>
+        <v>512155</v>
       </c>
       <c r="R120" t="n">
-        <v>6733153</v>
+        <v>6733037</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14825,9 +14809,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14843,22 +14837,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423747</v>
+        <v>121425818</v>
       </c>
       <c r="B121" t="n">
-        <v>4766</v>
+        <v>78604</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14867,46 +14861,52 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512148</v>
+        <v>512221</v>
       </c>
       <c r="R121" t="n">
-        <v>6733263</v>
+        <v>6733056</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14944,28 +14944,29 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425157</v>
+        <v>121423780</v>
       </c>
       <c r="B122" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14996,22 +14997,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512155</v>
+        <v>512100</v>
       </c>
       <c r="R122" t="n">
-        <v>6733037</v>
+        <v>6733148</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15038,50 +15036,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423781</v>
+        <v>121425873</v>
       </c>
       <c r="B123" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15094,37 +15081,48 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512210</v>
+        <v>512218</v>
       </c>
       <c r="R123" t="n">
-        <v>6733094</v>
+        <v>6733062</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15162,28 +15160,29 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121425158</v>
+        <v>121423767</v>
       </c>
       <c r="B124" t="n">
-        <v>78601</v>
+        <v>90922</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15192,25 +15191,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15219,17 +15218,17 @@
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512156</v>
+        <v>512147</v>
       </c>
       <c r="R124" t="n">
-        <v>6733044</v>
+        <v>6733153</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15256,19 +15255,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15284,22 +15273,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423727</v>
+        <v>121425857</v>
       </c>
       <c r="B125" t="n">
-        <v>90662</v>
+        <v>78604</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15308,41 +15297,52 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512156</v>
+        <v>512211</v>
       </c>
       <c r="R125" t="n">
-        <v>6733279</v>
+        <v>6733056</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15380,28 +15380,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423760</v>
+        <v>121423777</v>
       </c>
       <c r="B126" t="n">
-        <v>92008</v>
+        <v>78604</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15414,43 +15415,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>511818</v>
+        <v>512148</v>
       </c>
       <c r="R126" t="n">
-        <v>6733114</v>
+        <v>6733216</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15509,10 +15501,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423780</v>
+        <v>121423757</v>
       </c>
       <c r="B127" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15525,34 +15517,39 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512100</v>
+        <v>512093</v>
       </c>
       <c r="R127" t="n">
-        <v>6733148</v>
+        <v>6733205</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15585,6 +15582,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15611,10 +15613,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423726</v>
+        <v>121425158</v>
       </c>
       <c r="B128" t="n">
-        <v>90662</v>
+        <v>78604</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15623,41 +15625,44 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512164</v>
+        <v>512156</v>
       </c>
       <c r="R128" t="n">
-        <v>6733000</v>
+        <v>6733044</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15684,39 +15689,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Beke Regelin, Philipp Weiss</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121425159</v>
+        <v>121423779</v>
       </c>
       <c r="B129" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15747,22 +15763,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512216</v>
+        <v>512098</v>
       </c>
       <c r="R129" t="n">
-        <v>6733046</v>
+        <v>6733157</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15789,55 +15802,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121426864</v>
+        <v>121425156</v>
       </c>
       <c r="B130" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15850,31 +15847,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -15882,10 +15874,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R130" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -15917,7 +15909,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15927,12 +15919,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15941,6 +15928,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -15952,17 +15940,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121425857</v>
+        <v>121425509</v>
       </c>
       <c r="B131" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15992,31 +15980,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512211</v>
+        <v>512110</v>
       </c>
       <c r="R131" t="n">
-        <v>6733056</v>
+        <v>6733025</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16054,29 +16031,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121423788</v>
+        <v>121425159</v>
       </c>
       <c r="B132" t="n">
-        <v>100347</v>
+        <v>78604</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16085,41 +16061,44 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>511830</v>
+        <v>512216</v>
       </c>
       <c r="R132" t="n">
-        <v>6732919</v>
+        <v>6733046</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16146,29 +16125,45 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -16178,7 +16173,7 @@
         <v>121426316</v>
       </c>
       <c r="B133" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16295,10 +16290,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423777</v>
+        <v>121423745</v>
       </c>
       <c r="B134" t="n">
-        <v>78601</v>
+        <v>56563</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16307,38 +16302,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512148</v>
+        <v>511789</v>
       </c>
       <c r="R134" t="n">
-        <v>6733216</v>
+        <v>6732877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16397,10 +16397,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426851</v>
+        <v>121425773</v>
       </c>
       <c r="B135" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16413,48 +16413,45 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512219</v>
+        <v>512215</v>
       </c>
       <c r="R135" t="n">
-        <v>6733049</v>
+        <v>6733081</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16481,19 +16478,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>13:09</t>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16502,29 +16494,28 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16533,30 +16524,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16564,10 +16560,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R136" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16599,7 +16595,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16609,7 +16605,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16618,7 +16614,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16637,10 +16632,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B137" t="n">
-        <v>56563</v>
+        <v>90709</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16649,35 +16644,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16685,10 +16675,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R137" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16720,7 +16710,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16730,7 +16720,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16739,6 +16729,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16754,121 +16745,6 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>121425773</v>
-      </c>
-      <c r="B138" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>moberg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q138" t="n">
-        <v>512215</v>
-      </c>
-      <c r="R138" t="n">
-        <v>6733081</v>
-      </c>
-      <c r="S138" t="n">
-        <v>1</v>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
-        </is>
-      </c>
-      <c r="AD138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT138" t="inlineStr"/>
-      <c r="AW138" t="inlineStr">
-        <is>
-          <t>Irina Röjås</t>
-        </is>
-      </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>Irina Röjås</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401369</v>
+        <v>121401438</v>
       </c>
       <c r="B103" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R103" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13103,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B105" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13115,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13141,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R105" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13196,12 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121423726</v>
+        <v>121425873</v>
       </c>
       <c r="B107" t="n">
-        <v>90674</v>
+        <v>90710</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,41 +13354,52 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512164</v>
+        <v>512218</v>
       </c>
       <c r="R107" t="n">
-        <v>6733000</v>
+        <v>6733062</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13426,28 +13437,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121425510</v>
+        <v>121423727</v>
       </c>
       <c r="B108" t="n">
-        <v>78604</v>
+        <v>90675</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13456,25 +13468,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13484,10 +13496,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512131</v>
+        <v>512156</v>
       </c>
       <c r="R108" t="n">
-        <v>6733029</v>
+        <v>6733279</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13534,22 +13546,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423747</v>
+        <v>121425159</v>
       </c>
       <c r="B109" t="n">
-        <v>4766</v>
+        <v>78604</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13558,46 +13570,44 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512148</v>
+        <v>512216</v>
       </c>
       <c r="R109" t="n">
-        <v>6733263</v>
+        <v>6733046</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13624,39 +13634,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423760</v>
+        <v>121425157</v>
       </c>
       <c r="B110" t="n">
-        <v>92020</v>
+        <v>78604</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13669,46 +13695,40 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>511818</v>
+        <v>512155</v>
       </c>
       <c r="R110" t="n">
-        <v>6733114</v>
+        <v>6733037</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13735,36 +13755,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425516</v>
+        <v>121423780</v>
       </c>
       <c r="B111" t="n">
         <v>78604</v>
@@ -13807,7 +13838,7 @@
         <v>512100</v>
       </c>
       <c r="R111" t="n">
-        <v>6733039</v>
+        <v>6733148</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13842,11 +13873,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13859,22 +13885,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423788</v>
+        <v>121425519</v>
       </c>
       <c r="B112" t="n">
-        <v>100360</v>
+        <v>78604</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13883,25 +13909,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13911,10 +13937,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>511830</v>
+        <v>512131</v>
       </c>
       <c r="R112" t="n">
-        <v>6732919</v>
+        <v>6733029</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13961,22 +13987,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423727</v>
+        <v>121423779</v>
       </c>
       <c r="B113" t="n">
-        <v>90674</v>
+        <v>78604</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13985,25 +14011,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14013,10 +14039,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512156</v>
+        <v>512098</v>
       </c>
       <c r="R113" t="n">
-        <v>6733279</v>
+        <v>6733157</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14075,7 +14101,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423781</v>
+        <v>121425156</v>
       </c>
       <c r="B114" t="n">
         <v>78604</v>
@@ -14109,19 +14135,22 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512210</v>
+        <v>512108</v>
       </c>
       <c r="R114" t="n">
-        <v>6733094</v>
+        <v>6733054</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14148,29 +14177,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14302,10 +14342,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121426864</v>
+        <v>121423778</v>
       </c>
       <c r="B116" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14318,45 +14358,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512216</v>
+        <v>512091</v>
       </c>
       <c r="R116" t="n">
-        <v>6733046</v>
+        <v>6733225</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14383,24 +14415,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14415,19 +14432,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121423778</v>
+        <v>121425158</v>
       </c>
       <c r="B117" t="n">
         <v>78604</v>
@@ -14461,19 +14478,22 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512091</v>
+        <v>512156</v>
       </c>
       <c r="R117" t="n">
-        <v>6733225</v>
+        <v>6733044</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14500,36 +14520,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425511</v>
+        <v>121425516</v>
       </c>
       <c r="B118" t="n">
         <v>78604</v>
@@ -14569,10 +14600,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512223</v>
+        <v>512100</v>
       </c>
       <c r="R118" t="n">
-        <v>6733062</v>
+        <v>6733039</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14605,6 +14636,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14631,10 +14667,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423776</v>
+        <v>121423726</v>
       </c>
       <c r="B119" t="n">
-        <v>78604</v>
+        <v>90675</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14643,25 +14679,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14671,10 +14707,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512152</v>
+        <v>512164</v>
       </c>
       <c r="R119" t="n">
-        <v>6733230</v>
+        <v>6733000</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14733,7 +14769,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425157</v>
+        <v>121425509</v>
       </c>
       <c r="B120" t="n">
         <v>78604</v>
@@ -14767,22 +14803,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512155</v>
+        <v>512110</v>
       </c>
       <c r="R120" t="n">
-        <v>6733037</v>
+        <v>6733025</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14809,47 +14842,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121425818</v>
+        <v>121425857</v>
       </c>
       <c r="B121" t="n">
         <v>78604</v>
@@ -14884,7 +14906,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -14900,7 +14922,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512221</v>
+        <v>512211</v>
       </c>
       <c r="R121" t="n">
         <v>6733056</v>
@@ -14963,7 +14985,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423780</v>
+        <v>121425818</v>
       </c>
       <c r="B122" t="n">
         <v>78604</v>
@@ -14996,20 +15018,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512100</v>
+        <v>512221</v>
       </c>
       <c r="R122" t="n">
-        <v>6733148</v>
+        <v>6733056</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15047,28 +15080,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121425873</v>
+        <v>121423776</v>
       </c>
       <c r="B123" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15081,48 +15115,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512218</v>
+        <v>512152</v>
       </c>
       <c r="R123" t="n">
-        <v>6733062</v>
+        <v>6733230</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15160,29 +15183,28 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423767</v>
+        <v>121426316</v>
       </c>
       <c r="B124" t="n">
-        <v>90922</v>
+        <v>90996</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15191,44 +15213,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1618</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512147</v>
+        <v>512215</v>
       </c>
       <c r="R124" t="n">
-        <v>6733153</v>
+        <v>6733055</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15255,9 +15281,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15273,19 +15309,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425857</v>
+        <v>121423781</v>
       </c>
       <c r="B125" t="n">
         <v>78604</v>
@@ -15318,31 +15354,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512211</v>
+        <v>512210</v>
       </c>
       <c r="R125" t="n">
-        <v>6733056</v>
+        <v>6733094</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15380,29 +15405,28 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423777</v>
+        <v>121423757</v>
       </c>
       <c r="B126" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15415,34 +15439,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512148</v>
+        <v>512093</v>
       </c>
       <c r="R126" t="n">
-        <v>6733216</v>
+        <v>6733205</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15475,6 +15504,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15501,10 +15535,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423757</v>
+        <v>121425511</v>
       </c>
       <c r="B127" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15517,39 +15551,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512093</v>
+        <v>512223</v>
       </c>
       <c r="R127" t="n">
-        <v>6733205</v>
+        <v>6733062</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15584,11 +15613,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -15601,22 +15625,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425158</v>
+        <v>121423760</v>
       </c>
       <c r="B128" t="n">
-        <v>78604</v>
+        <v>92021</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15629,40 +15653,46 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512156</v>
+        <v>511818</v>
       </c>
       <c r="R128" t="n">
-        <v>6733044</v>
+        <v>6733114</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15689,50 +15719,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423779</v>
+        <v>121423788</v>
       </c>
       <c r="B129" t="n">
-        <v>78604</v>
+        <v>100361</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15741,25 +15760,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15769,10 +15788,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512098</v>
+        <v>511830</v>
       </c>
       <c r="R129" t="n">
-        <v>6733157</v>
+        <v>6732919</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15831,10 +15850,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121425156</v>
+        <v>121423747</v>
       </c>
       <c r="B130" t="n">
-        <v>78604</v>
+        <v>4766</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15843,44 +15862,46 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512108</v>
+        <v>512148</v>
       </c>
       <c r="R130" t="n">
-        <v>6733054</v>
+        <v>6733263</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15907,50 +15928,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121425509</v>
+        <v>121423767</v>
       </c>
       <c r="B131" t="n">
-        <v>78604</v>
+        <v>90923</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15959,38 +15969,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512110</v>
+        <v>512147</v>
       </c>
       <c r="R131" t="n">
-        <v>6733025</v>
+        <v>6733153</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16031,28 +16044,29 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425159</v>
+        <v>121423745</v>
       </c>
       <c r="B132" t="n">
-        <v>78604</v>
+        <v>56563</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16061,44 +16075,46 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512216</v>
+        <v>511789</v>
       </c>
       <c r="R132" t="n">
-        <v>6733046</v>
+        <v>6732877</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16125,55 +16141,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121426316</v>
+        <v>121426864</v>
       </c>
       <c r="B133" t="n">
-        <v>90995</v>
+        <v>57367</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16186,30 +16186,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -16217,10 +16218,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512215</v>
+        <v>512216</v>
       </c>
       <c r="R133" t="n">
-        <v>6733055</v>
+        <v>6733046</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -16252,7 +16253,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16262,7 +16263,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16271,7 +16277,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -16290,10 +16295,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423745</v>
+        <v>121423777</v>
       </c>
       <c r="B134" t="n">
-        <v>56563</v>
+        <v>78604</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16302,43 +16307,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>511789</v>
+        <v>512148</v>
       </c>
       <c r="R134" t="n">
-        <v>6732877</v>
+        <v>6733216</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16397,10 +16397,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121425773</v>
+        <v>121426850</v>
       </c>
       <c r="B135" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16413,45 +16413,40 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512215</v>
+        <v>512216</v>
       </c>
       <c r="R135" t="n">
-        <v>6733081</v>
+        <v>6733046</v>
       </c>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16478,14 +16473,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16494,28 +16494,29 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121425773</v>
       </c>
       <c r="B136" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16524,25 +16525,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16550,23 +16551,23 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733081</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16593,19 +16594,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16620,22 +16616,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B137" t="n">
-        <v>90709</v>
+        <v>56563</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16644,30 +16640,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16675,10 +16676,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R137" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16710,7 +16711,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16720,7 +16721,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16729,7 +16730,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12861,7 +12861,7 @@
         <v>121401438</v>
       </c>
       <c r="B103" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>121401354</v>
       </c>
       <c r="B104" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>121401369</v>
       </c>
       <c r="B105" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425873</v>
+        <v>121425509</v>
       </c>
       <c r="B107" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13358,48 +13358,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512218</v>
+        <v>512110</v>
       </c>
       <c r="R107" t="n">
-        <v>6733062</v>
+        <v>6733025</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13437,29 +13426,28 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423727</v>
+        <v>121425511</v>
       </c>
       <c r="B108" t="n">
-        <v>90675</v>
+        <v>78607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13468,25 +13456,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13496,10 +13484,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512156</v>
+        <v>512223</v>
       </c>
       <c r="R108" t="n">
-        <v>6733279</v>
+        <v>6733062</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13546,22 +13534,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425159</v>
+        <v>121423760</v>
       </c>
       <c r="B109" t="n">
-        <v>78604</v>
+        <v>92024</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13574,40 +13562,46 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512216</v>
+        <v>511818</v>
       </c>
       <c r="R109" t="n">
-        <v>6733046</v>
+        <v>6733114</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13634,55 +13628,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121425157</v>
+        <v>121426863</v>
       </c>
       <c r="B110" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13695,26 +13673,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13722,10 +13705,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512155</v>
+        <v>512104</v>
       </c>
       <c r="R110" t="n">
-        <v>6733037</v>
+        <v>6733063</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -13757,7 +13740,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13767,7 +13750,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13776,7 +13764,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -13788,17 +13775,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423780</v>
+        <v>121425158</v>
       </c>
       <c r="B111" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13829,19 +13816,22 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512100</v>
+        <v>512156</v>
       </c>
       <c r="R111" t="n">
-        <v>6733148</v>
+        <v>6733044</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13868,39 +13858,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121425519</v>
+        <v>121423745</v>
       </c>
       <c r="B112" t="n">
-        <v>78604</v>
+        <v>56566</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13909,38 +13910,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512131</v>
+        <v>511789</v>
       </c>
       <c r="R112" t="n">
-        <v>6733029</v>
+        <v>6732877</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13987,22 +13993,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423779</v>
+        <v>121423777</v>
       </c>
       <c r="B113" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14039,10 +14045,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512098</v>
+        <v>512148</v>
       </c>
       <c r="R113" t="n">
-        <v>6733157</v>
+        <v>6733216</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14101,10 +14107,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121425156</v>
+        <v>121423757</v>
       </c>
       <c r="B114" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14117,40 +14123,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512108</v>
+        <v>512093</v>
       </c>
       <c r="R114" t="n">
-        <v>6733054</v>
+        <v>6733205</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14177,19 +14185,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14198,29 +14201,28 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121426863</v>
+        <v>121425510</v>
       </c>
       <c r="B115" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14233,45 +14235,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512104</v>
+        <v>512131</v>
       </c>
       <c r="R115" t="n">
-        <v>6733063</v>
+        <v>6733029</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14298,24 +14292,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14330,22 +14309,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423778</v>
+        <v>121423767</v>
       </c>
       <c r="B116" t="n">
-        <v>78604</v>
+        <v>90926</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14354,38 +14333,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512091</v>
+        <v>512147</v>
       </c>
       <c r="R116" t="n">
-        <v>6733225</v>
+        <v>6733153</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14426,6 +14408,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -14444,10 +14427,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425158</v>
+        <v>121426864</v>
       </c>
       <c r="B117" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14460,26 +14443,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -14487,10 +14475,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512156</v>
+        <v>512216</v>
       </c>
       <c r="R117" t="n">
-        <v>6733044</v>
+        <v>6733046</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -14522,7 +14510,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14532,7 +14520,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14541,7 +14534,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -14553,17 +14545,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425516</v>
+        <v>121425157</v>
       </c>
       <c r="B118" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14594,19 +14586,22 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512100</v>
+        <v>512155</v>
       </c>
       <c r="R118" t="n">
-        <v>6733039</v>
+        <v>6733037</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14633,14 +14628,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>mycket</t>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14649,28 +14649,29 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423726</v>
+        <v>121423727</v>
       </c>
       <c r="B119" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14707,10 +14708,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512164</v>
+        <v>512156</v>
       </c>
       <c r="R119" t="n">
-        <v>6733000</v>
+        <v>6733279</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14769,10 +14770,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425509</v>
+        <v>121425159</v>
       </c>
       <c r="B120" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14803,19 +14804,22 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512110</v>
+        <v>512216</v>
       </c>
       <c r="R120" t="n">
-        <v>6733025</v>
+        <v>6733046</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14842,39 +14846,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121425857</v>
+        <v>121425507</v>
       </c>
       <c r="B121" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14904,31 +14924,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512211</v>
+        <v>512100</v>
       </c>
       <c r="R121" t="n">
-        <v>6733056</v>
+        <v>6733039</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14960,35 +14969,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425818</v>
+        <v>121423788</v>
       </c>
       <c r="B122" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14997,52 +15010,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512221</v>
+        <v>511830</v>
       </c>
       <c r="R122" t="n">
-        <v>6733056</v>
+        <v>6732919</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15080,29 +15082,28 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423776</v>
+        <v>121425857</v>
       </c>
       <c r="B123" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15132,20 +15133,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512152</v>
+        <v>512211</v>
       </c>
       <c r="R123" t="n">
-        <v>6733230</v>
+        <v>6733056</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15183,28 +15195,29 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121426316</v>
+        <v>121423781</v>
       </c>
       <c r="B124" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15217,44 +15230,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512215</v>
+        <v>512210</v>
       </c>
       <c r="R124" t="n">
-        <v>6733055</v>
+        <v>6733094</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15281,50 +15287,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423781</v>
+        <v>121423747</v>
       </c>
       <c r="B125" t="n">
-        <v>78604</v>
+        <v>4769</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15333,38 +15328,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512210</v>
+        <v>512148</v>
       </c>
       <c r="R125" t="n">
-        <v>6733094</v>
+        <v>6733263</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15416,17 +15416,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423757</v>
+        <v>121425873</v>
       </c>
       <c r="B126" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15439,42 +15439,48 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512093</v>
+        <v>512218</v>
       </c>
       <c r="R126" t="n">
-        <v>6733205</v>
+        <v>6733062</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15506,39 +15512,35 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121425511</v>
+        <v>121423776</v>
       </c>
       <c r="B127" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15575,10 +15577,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512223</v>
+        <v>512152</v>
       </c>
       <c r="R127" t="n">
-        <v>6733062</v>
+        <v>6733230</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15625,22 +15627,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423760</v>
+        <v>121425818</v>
       </c>
       <c r="B128" t="n">
-        <v>92021</v>
+        <v>78607</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15653,46 +15655,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>511818</v>
+        <v>512221</v>
       </c>
       <c r="R128" t="n">
-        <v>6733114</v>
+        <v>6733056</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15730,28 +15734,29 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423788</v>
+        <v>121423779</v>
       </c>
       <c r="B129" t="n">
-        <v>100361</v>
+        <v>78607</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15760,25 +15765,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15788,10 +15793,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>511830</v>
+        <v>512098</v>
       </c>
       <c r="R129" t="n">
-        <v>6732919</v>
+        <v>6733157</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15850,10 +15855,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423747</v>
+        <v>121425156</v>
       </c>
       <c r="B130" t="n">
-        <v>4766</v>
+        <v>78607</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15862,46 +15867,44 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512148</v>
+        <v>512108</v>
       </c>
       <c r="R130" t="n">
-        <v>6733263</v>
+        <v>6733054</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15928,39 +15931,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423767</v>
+        <v>121426316</v>
       </c>
       <c r="B131" t="n">
-        <v>90923</v>
+        <v>90999</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15969,44 +15983,48 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1618</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512147</v>
+        <v>512215</v>
       </c>
       <c r="R131" t="n">
-        <v>6733153</v>
+        <v>6733055</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16033,9 +16051,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16051,22 +16079,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121423745</v>
+        <v>121423778</v>
       </c>
       <c r="B132" t="n">
-        <v>56563</v>
+        <v>78607</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16075,43 +16103,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>511789</v>
+        <v>512091</v>
       </c>
       <c r="R132" t="n">
-        <v>6732877</v>
+        <v>6733225</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16170,10 +16193,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121426864</v>
+        <v>121423726</v>
       </c>
       <c r="B133" t="n">
-        <v>57367</v>
+        <v>90678</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16182,49 +16205,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512216</v>
+        <v>512164</v>
       </c>
       <c r="R133" t="n">
-        <v>6733046</v>
+        <v>6733000</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16251,24 +16266,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16283,22 +16283,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423777</v>
+        <v>121423780</v>
       </c>
       <c r="B134" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16335,10 +16335,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512148</v>
+        <v>512100</v>
       </c>
       <c r="R134" t="n">
-        <v>6733216</v>
+        <v>6733148</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16397,10 +16397,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B135" t="n">
-        <v>90710</v>
+        <v>56566</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16409,30 +16409,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -16440,10 +16445,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R135" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16475,7 +16480,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16485,7 +16490,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16494,7 +16499,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16506,17 +16510,17 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121425773</v>
+        <v>121426850</v>
       </c>
       <c r="B136" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16529,45 +16533,40 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512215</v>
+        <v>512216</v>
       </c>
       <c r="R136" t="n">
-        <v>6733081</v>
+        <v>6733046</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16594,14 +16593,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16610,28 +16614,29 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426859</v>
+        <v>121425773</v>
       </c>
       <c r="B137" t="n">
-        <v>56563</v>
+        <v>57370</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16640,25 +16645,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16666,23 +16671,23 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R137" t="n">
-        <v>6733054</v>
+        <v>6733081</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16709,19 +16714,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16736,12 +16736,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>56566</v>
+        <v>57507</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R103" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,12 +12951,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12983,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B104" t="n">
-        <v>57507</v>
+        <v>56566</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12995,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13021,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R104" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13066,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13076,7 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425509</v>
+        <v>121426316</v>
       </c>
       <c r="B107" t="n">
-        <v>78607</v>
+        <v>90999</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13358,37 +13358,44 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512110</v>
+        <v>512215</v>
       </c>
       <c r="R107" t="n">
-        <v>6733025</v>
+        <v>6733055</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13415,39 +13422,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121425511</v>
+        <v>121423745</v>
       </c>
       <c r="B108" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13456,38 +13474,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512223</v>
+        <v>511789</v>
       </c>
       <c r="R108" t="n">
-        <v>6733062</v>
+        <v>6732877</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13534,22 +13557,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423760</v>
+        <v>121423726</v>
       </c>
       <c r="B109" t="n">
-        <v>92024</v>
+        <v>90678</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13558,47 +13581,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>511818</v>
+        <v>512164</v>
       </c>
       <c r="R109" t="n">
-        <v>6733114</v>
+        <v>6733000</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13657,10 +13671,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121426863</v>
+        <v>121423757</v>
       </c>
       <c r="B110" t="n">
-        <v>57370</v>
+        <v>57354</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13673,16 +13687,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -13691,27 +13705,24 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512104</v>
+        <v>512093</v>
       </c>
       <c r="R110" t="n">
-        <v>6733063</v>
+        <v>6733205</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13738,24 +13749,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Mycket färska spår</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13770,22 +13771,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425158</v>
+        <v>121426863</v>
       </c>
       <c r="B111" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13798,26 +13799,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13825,10 +13831,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512156</v>
+        <v>512104</v>
       </c>
       <c r="R111" t="n">
-        <v>6733044</v>
+        <v>6733063</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -13860,7 +13866,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13870,7 +13876,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13879,7 +13890,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -13891,17 +13901,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423745</v>
+        <v>121425157</v>
       </c>
       <c r="B112" t="n">
-        <v>56566</v>
+        <v>78607</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13910,46 +13920,44 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>511789</v>
+        <v>512155</v>
       </c>
       <c r="R112" t="n">
-        <v>6732877</v>
+        <v>6733037</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13976,36 +13984,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423777</v>
+        <v>121425857</v>
       </c>
       <c r="B113" t="n">
         <v>78607</v>
@@ -14038,20 +14057,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512148</v>
+        <v>512211</v>
       </c>
       <c r="R113" t="n">
-        <v>6733216</v>
+        <v>6733056</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14089,28 +14119,29 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423757</v>
+        <v>121425519</v>
       </c>
       <c r="B114" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14123,39 +14154,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512093</v>
+        <v>512131</v>
       </c>
       <c r="R114" t="n">
-        <v>6733205</v>
+        <v>6733029</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14190,11 +14216,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -14207,19 +14228,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425510</v>
+        <v>121425520</v>
       </c>
       <c r="B115" t="n">
         <v>78607</v>
@@ -14259,10 +14280,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512131</v>
+        <v>512223</v>
       </c>
       <c r="R115" t="n">
-        <v>6733029</v>
+        <v>6733062</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14321,10 +14342,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423767</v>
+        <v>121423780</v>
       </c>
       <c r="B116" t="n">
-        <v>90926</v>
+        <v>78607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14333,41 +14354,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512147</v>
+        <v>512100</v>
       </c>
       <c r="R116" t="n">
-        <v>6733153</v>
+        <v>6733148</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14408,7 +14426,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -14427,10 +14444,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121426864</v>
+        <v>121425873</v>
       </c>
       <c r="B117" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14443,45 +14460,48 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512216</v>
+        <v>512218</v>
       </c>
       <c r="R117" t="n">
-        <v>6733046</v>
+        <v>6733062</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14508,51 +14528,37 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425157</v>
+        <v>121423778</v>
       </c>
       <c r="B118" t="n">
         <v>78607</v>
@@ -14586,22 +14592,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512155</v>
+        <v>512091</v>
       </c>
       <c r="R118" t="n">
-        <v>6733037</v>
+        <v>6733225</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14628,50 +14631,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423727</v>
+        <v>121423776</v>
       </c>
       <c r="B119" t="n">
-        <v>90678</v>
+        <v>78607</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14680,25 +14672,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14708,10 +14700,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512156</v>
+        <v>512152</v>
       </c>
       <c r="R119" t="n">
-        <v>6733279</v>
+        <v>6733230</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14770,10 +14762,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425159</v>
+        <v>121426864</v>
       </c>
       <c r="B120" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14786,26 +14778,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -14848,7 +14845,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14858,12 +14855,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>tussar på flera granar</t>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14872,7 +14869,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14884,17 +14880,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121425507</v>
+        <v>121423788</v>
       </c>
       <c r="B121" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14903,25 +14899,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14931,10 +14927,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512100</v>
+        <v>511830</v>
       </c>
       <c r="R121" t="n">
-        <v>6733039</v>
+        <v>6732919</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14969,11 +14965,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14986,22 +14977,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423788</v>
+        <v>121425156</v>
       </c>
       <c r="B122" t="n">
-        <v>100364</v>
+        <v>78607</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15010,41 +15001,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>511830</v>
+        <v>512108</v>
       </c>
       <c r="R122" t="n">
-        <v>6732919</v>
+        <v>6733054</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15071,36 +15065,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121425857</v>
+        <v>121423781</v>
       </c>
       <c r="B123" t="n">
         <v>78607</v>
@@ -15133,31 +15138,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512211</v>
+        <v>512210</v>
       </c>
       <c r="R123" t="n">
-        <v>6733056</v>
+        <v>6733094</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15195,26 +15189,25 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423781</v>
+        <v>121425518</v>
       </c>
       <c r="B124" t="n">
         <v>78607</v>
@@ -15254,10 +15247,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512210</v>
+        <v>512110</v>
       </c>
       <c r="R124" t="n">
-        <v>6733094</v>
+        <v>6733025</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15304,22 +15297,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423747</v>
+        <v>121425158</v>
       </c>
       <c r="B125" t="n">
-        <v>4769</v>
+        <v>78607</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15328,46 +15321,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512148</v>
+        <v>512156</v>
       </c>
       <c r="R125" t="n">
-        <v>6733263</v>
+        <v>6733044</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15394,39 +15385,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Beke Regelin, Irina Röjås, Evalena Sköld, Philipp Weiss</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121425873</v>
+        <v>121425159</v>
       </c>
       <c r="B126" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15439,48 +15441,40 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512218</v>
+        <v>512216</v>
       </c>
       <c r="R126" t="n">
-        <v>6733062</v>
+        <v>6733046</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15507,9 +15501,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15525,19 +15534,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423776</v>
+        <v>121423779</v>
       </c>
       <c r="B127" t="n">
         <v>78607</v>
@@ -15577,10 +15586,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512152</v>
+        <v>512098</v>
       </c>
       <c r="R127" t="n">
-        <v>6733230</v>
+        <v>6733157</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15639,10 +15648,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425818</v>
+        <v>121423747</v>
       </c>
       <c r="B128" t="n">
-        <v>78607</v>
+        <v>4769</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15651,52 +15660,46 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512221</v>
+        <v>512148</v>
       </c>
       <c r="R128" t="n">
-        <v>6733056</v>
+        <v>6733263</v>
       </c>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15734,29 +15737,28 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423779</v>
+        <v>121423760</v>
       </c>
       <c r="B129" t="n">
-        <v>78607</v>
+        <v>92024</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15769,34 +15771,43 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512098</v>
+        <v>511818</v>
       </c>
       <c r="R129" t="n">
-        <v>6733157</v>
+        <v>6733114</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15855,7 +15866,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121425156</v>
+        <v>121425516</v>
       </c>
       <c r="B130" t="n">
         <v>78607</v>
@@ -15889,22 +15900,19 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512108</v>
+        <v>512100</v>
       </c>
       <c r="R130" t="n">
-        <v>6733054</v>
+        <v>6733039</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15931,19 +15939,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15952,29 +15955,28 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121426316</v>
+        <v>121425818</v>
       </c>
       <c r="B131" t="n">
-        <v>90999</v>
+        <v>78607</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15987,44 +15989,48 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512215</v>
+        <v>512221</v>
       </c>
       <c r="R131" t="n">
-        <v>6733055</v>
+        <v>6733056</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16051,19 +16057,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16079,22 +16075,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121423778</v>
+        <v>121423727</v>
       </c>
       <c r="B132" t="n">
-        <v>78607</v>
+        <v>90678</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16103,25 +16099,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -16131,10 +16127,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512091</v>
+        <v>512156</v>
       </c>
       <c r="R132" t="n">
-        <v>6733225</v>
+        <v>6733279</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16193,10 +16189,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121423726</v>
+        <v>121423777</v>
       </c>
       <c r="B133" t="n">
-        <v>90678</v>
+        <v>78607</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16205,25 +16201,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -16233,10 +16229,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512164</v>
+        <v>512148</v>
       </c>
       <c r="R133" t="n">
-        <v>6733000</v>
+        <v>6733216</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16295,10 +16291,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423780</v>
+        <v>121423767</v>
       </c>
       <c r="B134" t="n">
-        <v>78607</v>
+        <v>90926</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16307,38 +16303,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512100</v>
+        <v>512147</v>
       </c>
       <c r="R134" t="n">
-        <v>6733148</v>
+        <v>6733153</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16379,6 +16378,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B103" t="n">
-        <v>57507</v>
+        <v>56566</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R103" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,7 +12951,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12978,10 +12983,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B104" t="n">
-        <v>56566</v>
+        <v>57507</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12995,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13021,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13076,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13569,10 +13569,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423726</v>
+        <v>121425157</v>
       </c>
       <c r="B109" t="n">
-        <v>90678</v>
+        <v>78607</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13581,41 +13581,44 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512164</v>
+        <v>512155</v>
       </c>
       <c r="R109" t="n">
-        <v>6733000</v>
+        <v>6733037</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13642,39 +13645,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423757</v>
+        <v>121423726</v>
       </c>
       <c r="B110" t="n">
-        <v>57354</v>
+        <v>90678</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13683,43 +13697,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512093</v>
+        <v>512164</v>
       </c>
       <c r="R110" t="n">
-        <v>6733205</v>
+        <v>6733000</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13752,11 +13761,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13783,10 +13787,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121426863</v>
+        <v>121423757</v>
       </c>
       <c r="B111" t="n">
-        <v>57370</v>
+        <v>57354</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13799,16 +13803,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -13817,27 +13821,24 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512104</v>
+        <v>512093</v>
       </c>
       <c r="R111" t="n">
-        <v>6733063</v>
+        <v>6733205</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13864,24 +13865,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Mycket färska spår</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13896,22 +13887,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121425157</v>
+        <v>121426863</v>
       </c>
       <c r="B112" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13924,26 +13915,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13951,10 +13947,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512155</v>
+        <v>512104</v>
       </c>
       <c r="R112" t="n">
-        <v>6733037</v>
+        <v>6733063</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -13986,7 +13982,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13996,7 +13992,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14005,7 +14006,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -14762,10 +14762,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121426864</v>
+        <v>121425156</v>
       </c>
       <c r="B120" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14778,31 +14778,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -14810,10 +14805,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R120" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14845,7 +14840,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14855,12 +14850,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14869,6 +14859,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14880,17 +14871,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423788</v>
+        <v>121423781</v>
       </c>
       <c r="B121" t="n">
-        <v>100364</v>
+        <v>78607</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14899,25 +14890,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14927,10 +14918,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>511830</v>
+        <v>512210</v>
       </c>
       <c r="R121" t="n">
-        <v>6732919</v>
+        <v>6733094</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14989,10 +14980,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425156</v>
+        <v>121426864</v>
       </c>
       <c r="B122" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15005,26 +14996,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -15032,10 +15028,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R122" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -15067,7 +15063,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15077,7 +15073,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15086,7 +15087,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -15098,17 +15098,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423781</v>
+        <v>121423788</v>
       </c>
       <c r="B123" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15117,25 +15117,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512210</v>
+        <v>511830</v>
       </c>
       <c r="R123" t="n">
-        <v>6733094</v>
+        <v>6732919</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>56566</v>
+        <v>57507</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R103" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,12 +12951,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12983,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B104" t="n">
-        <v>57507</v>
+        <v>56566</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12995,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13021,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R104" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13066,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13076,7 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14762,10 +14762,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425156</v>
+        <v>121426864</v>
       </c>
       <c r="B120" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14778,26 +14778,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -14805,10 +14810,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R120" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14840,7 +14845,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14850,7 +14855,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14859,7 +14869,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14871,17 +14880,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423781</v>
+        <v>121423788</v>
       </c>
       <c r="B121" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14890,25 +14899,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14918,10 +14927,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512210</v>
+        <v>511830</v>
       </c>
       <c r="R121" t="n">
-        <v>6733094</v>
+        <v>6732919</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14980,10 +14989,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121426864</v>
+        <v>121425156</v>
       </c>
       <c r="B122" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14996,31 +15005,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -15028,10 +15032,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R122" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -15063,7 +15067,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15073,12 +15077,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15087,6 +15086,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -15098,17 +15098,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423788</v>
+        <v>121423781</v>
       </c>
       <c r="B123" t="n">
-        <v>100364</v>
+        <v>78607</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15117,25 +15117,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>511830</v>
+        <v>512210</v>
       </c>
       <c r="R123" t="n">
-        <v>6732919</v>
+        <v>6733094</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B103" t="n">
-        <v>57507</v>
+        <v>56567</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R103" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,7 +12951,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12978,10 +12983,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B104" t="n">
-        <v>56566</v>
+        <v>57508</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12995,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13021,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13076,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13106,7 +13106,7 @@
         <v>121401369</v>
       </c>
       <c r="B105" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121426316</v>
+        <v>121423747</v>
       </c>
       <c r="B107" t="n">
-        <v>90999</v>
+        <v>4769</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,48 +13354,46 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512215</v>
+        <v>512148</v>
       </c>
       <c r="R107" t="n">
-        <v>6733055</v>
+        <v>6733263</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13422,50 +13420,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423745</v>
+        <v>121423767</v>
       </c>
       <c r="B108" t="n">
-        <v>56566</v>
+        <v>90932</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13474,43 +13461,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>1618</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>511789</v>
+        <v>512147</v>
       </c>
       <c r="R108" t="n">
-        <v>6732877</v>
+        <v>6733153</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13551,6 +13536,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13569,10 +13555,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425157</v>
+        <v>121425818</v>
       </c>
       <c r="B109" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13602,23 +13588,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512155</v>
+        <v>512221</v>
       </c>
       <c r="R109" t="n">
-        <v>6733037</v>
+        <v>6733056</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13645,19 +13639,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13673,22 +13657,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423726</v>
+        <v>121426864</v>
       </c>
       <c r="B110" t="n">
-        <v>90678</v>
+        <v>57371</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13697,41 +13681,49 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512164</v>
+        <v>512216</v>
       </c>
       <c r="R110" t="n">
-        <v>6733000</v>
+        <v>6733046</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13758,9 +13750,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13775,22 +13782,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423757</v>
+        <v>121425158</v>
       </c>
       <c r="B111" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13803,42 +13810,40 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512093</v>
+        <v>512156</v>
       </c>
       <c r="R111" t="n">
-        <v>6733205</v>
+        <v>6733044</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13865,14 +13870,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13881,28 +13891,29 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121426863</v>
+        <v>121425516</v>
       </c>
       <c r="B112" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13915,45 +13926,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512104</v>
+        <v>512100</v>
       </c>
       <c r="R112" t="n">
-        <v>6733063</v>
+        <v>6733039</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13980,24 +13983,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Mycket färska spår</t>
+          <t>mycket</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14012,22 +14005,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121425857</v>
+        <v>121423745</v>
       </c>
       <c r="B113" t="n">
-        <v>78607</v>
+        <v>56567</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14036,52 +14029,46 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512211</v>
+        <v>511789</v>
       </c>
       <c r="R113" t="n">
-        <v>6733056</v>
+        <v>6732877</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14119,29 +14106,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121425519</v>
+        <v>121423776</v>
       </c>
       <c r="B114" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14178,10 +14164,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512131</v>
+        <v>512152</v>
       </c>
       <c r="R114" t="n">
-        <v>6733029</v>
+        <v>6733230</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14228,22 +14214,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425520</v>
+        <v>121425511</v>
       </c>
       <c r="B115" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14342,10 +14328,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423780</v>
+        <v>121425156</v>
       </c>
       <c r="B116" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14376,19 +14362,22 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512100</v>
+        <v>512108</v>
       </c>
       <c r="R116" t="n">
-        <v>6733148</v>
+        <v>6733054</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14415,39 +14404,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425873</v>
+        <v>121425857</v>
       </c>
       <c r="B117" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14460,31 +14460,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -14495,10 +14495,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512218</v>
+        <v>512211</v>
       </c>
       <c r="R117" t="n">
-        <v>6733062</v>
+        <v>6733056</v>
       </c>
       <c r="S117" t="n">
         <v>1</v>
@@ -14558,10 +14558,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121423778</v>
+        <v>121426316</v>
       </c>
       <c r="B118" t="n">
-        <v>78607</v>
+        <v>91005</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14574,37 +14574,44 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512091</v>
+        <v>512215</v>
       </c>
       <c r="R118" t="n">
-        <v>6733225</v>
+        <v>6733055</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14631,39 +14638,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423776</v>
+        <v>121423780</v>
       </c>
       <c r="B119" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14700,10 +14718,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512152</v>
+        <v>512100</v>
       </c>
       <c r="R119" t="n">
-        <v>6733230</v>
+        <v>6733148</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14762,10 +14780,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121426864</v>
+        <v>121425157</v>
       </c>
       <c r="B120" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14778,31 +14796,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -14810,10 +14823,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512216</v>
+        <v>512155</v>
       </c>
       <c r="R120" t="n">
-        <v>6733046</v>
+        <v>6733037</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14845,7 +14858,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14855,12 +14868,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14869,6 +14877,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -14880,17 +14889,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423788</v>
+        <v>121423777</v>
       </c>
       <c r="B121" t="n">
-        <v>100364</v>
+        <v>78608</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14899,25 +14908,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14927,10 +14936,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>511830</v>
+        <v>512148</v>
       </c>
       <c r="R121" t="n">
-        <v>6732919</v>
+        <v>6733216</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14989,10 +14998,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425156</v>
+        <v>121423781</v>
       </c>
       <c r="B122" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15023,22 +15032,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512108</v>
+        <v>512210</v>
       </c>
       <c r="R122" t="n">
-        <v>6733054</v>
+        <v>6733094</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15065,50 +15071,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423781</v>
+        <v>121425873</v>
       </c>
       <c r="B123" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15121,37 +15116,48 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512210</v>
+        <v>512218</v>
       </c>
       <c r="R123" t="n">
-        <v>6733094</v>
+        <v>6733062</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15189,28 +15195,29 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121425518</v>
+        <v>121426863</v>
       </c>
       <c r="B124" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15223,37 +15230,45 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512110</v>
+        <v>512104</v>
       </c>
       <c r="R124" t="n">
-        <v>6733025</v>
+        <v>6733063</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15280,9 +15295,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15297,22 +15327,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425158</v>
+        <v>121425519</v>
       </c>
       <c r="B125" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15343,22 +15373,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512156</v>
+        <v>512131</v>
       </c>
       <c r="R125" t="n">
-        <v>6733044</v>
+        <v>6733029</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15385,50 +15412,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121425159</v>
+        <v>121423757</v>
       </c>
       <c r="B126" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15441,40 +15457,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512216</v>
+        <v>512093</v>
       </c>
       <c r="R126" t="n">
-        <v>6733046</v>
+        <v>6733205</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15501,24 +15519,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>tussar på flera granar</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15527,29 +15535,28 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423779</v>
+        <v>121423778</v>
       </c>
       <c r="B127" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15586,10 +15593,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512098</v>
+        <v>512091</v>
       </c>
       <c r="R127" t="n">
-        <v>6733157</v>
+        <v>6733225</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15648,10 +15655,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423747</v>
+        <v>121423779</v>
       </c>
       <c r="B128" t="n">
-        <v>4769</v>
+        <v>78608</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15660,43 +15667,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512148</v>
+        <v>512098</v>
       </c>
       <c r="R128" t="n">
-        <v>6733263</v>
+        <v>6733157</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15755,10 +15757,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423760</v>
+        <v>121425159</v>
       </c>
       <c r="B129" t="n">
-        <v>92024</v>
+        <v>78608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15771,46 +15773,40 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>511818</v>
+        <v>512216</v>
       </c>
       <c r="R129" t="n">
-        <v>6733114</v>
+        <v>6733046</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15837,39 +15833,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121425516</v>
+        <v>121423760</v>
       </c>
       <c r="B130" t="n">
-        <v>78607</v>
+        <v>92030</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15882,34 +15894,43 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512100</v>
+        <v>511818</v>
       </c>
       <c r="R130" t="n">
-        <v>6733039</v>
+        <v>6733114</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15944,11 +15965,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -15961,22 +15977,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121425818</v>
+        <v>121423726</v>
       </c>
       <c r="B131" t="n">
-        <v>78607</v>
+        <v>90684</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15985,52 +16001,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512221</v>
+        <v>512164</v>
       </c>
       <c r="R131" t="n">
-        <v>6733056</v>
+        <v>6733000</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16068,19 +16073,18 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -16090,7 +16094,7 @@
         <v>121423727</v>
       </c>
       <c r="B132" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16189,10 +16193,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121423777</v>
+        <v>121425509</v>
       </c>
       <c r="B133" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16229,10 +16233,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512148</v>
+        <v>512110</v>
       </c>
       <c r="R133" t="n">
-        <v>6733216</v>
+        <v>6733025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16279,22 +16283,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423767</v>
+        <v>121423788</v>
       </c>
       <c r="B134" t="n">
-        <v>90926</v>
+        <v>100370</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16303,41 +16307,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1618</v>
+        <v>222498</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512147</v>
+        <v>511830</v>
       </c>
       <c r="R134" t="n">
-        <v>6733153</v>
+        <v>6732919</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16378,7 +16379,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -16397,10 +16397,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B135" t="n">
-        <v>56566</v>
+        <v>90719</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16409,35 +16409,30 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -16445,10 +16440,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R135" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16480,7 +16475,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16490,7 +16485,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16499,6 +16494,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16517,10 +16513,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>90713</v>
+        <v>56567</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16529,30 +16525,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16560,10 +16561,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R136" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16595,7 +16596,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16605,7 +16606,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16614,7 +16615,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16636,7 +16636,7 @@
         <v>121425773</v>
       </c>
       <c r="B137" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>56567</v>
+        <v>57509</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R103" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,12 +12951,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12983,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B104" t="n">
-        <v>57508</v>
+        <v>56568</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12995,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13021,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R104" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13066,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13076,7 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13106,7 +13106,7 @@
         <v>121401369</v>
       </c>
       <c r="B105" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121423747</v>
+        <v>121425507</v>
       </c>
       <c r="B107" t="n">
-        <v>4769</v>
+        <v>78609</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,43 +13354,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512148</v>
+        <v>512100</v>
       </c>
       <c r="R107" t="n">
-        <v>6733263</v>
+        <v>6733039</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13425,6 +13420,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -13437,22 +13437,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423767</v>
+        <v>121425857</v>
       </c>
       <c r="B108" t="n">
-        <v>90932</v>
+        <v>78609</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13461,44 +13461,52 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512147</v>
+        <v>512211</v>
       </c>
       <c r="R108" t="n">
-        <v>6733153</v>
+        <v>6733056</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13543,22 +13551,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425818</v>
+        <v>121423776</v>
       </c>
       <c r="B109" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13588,31 +13596,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512221</v>
+        <v>512152</v>
       </c>
       <c r="R109" t="n">
-        <v>6733056</v>
+        <v>6733230</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13650,29 +13647,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121426864</v>
+        <v>121425818</v>
       </c>
       <c r="B110" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13685,45 +13681,48 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512216</v>
+        <v>512221</v>
       </c>
       <c r="R110" t="n">
-        <v>6733046</v>
+        <v>6733056</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13750,54 +13749,40 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425158</v>
+        <v>121426864</v>
       </c>
       <c r="B111" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13810,26 +13795,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13837,10 +13827,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512156</v>
+        <v>512216</v>
       </c>
       <c r="R111" t="n">
-        <v>6733044</v>
+        <v>6733046</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -13872,7 +13862,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13882,7 +13872,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13891,7 +13886,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -13903,17 +13897,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121425516</v>
+        <v>121423726</v>
       </c>
       <c r="B112" t="n">
-        <v>78608</v>
+        <v>90685</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13922,25 +13916,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13950,10 +13944,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512100</v>
+        <v>512164</v>
       </c>
       <c r="R112" t="n">
-        <v>6733039</v>
+        <v>6733000</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13988,11 +13982,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -14005,22 +13994,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423745</v>
+        <v>121425157</v>
       </c>
       <c r="B113" t="n">
-        <v>56567</v>
+        <v>78609</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14029,46 +14018,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>511789</v>
+        <v>512155</v>
       </c>
       <c r="R113" t="n">
-        <v>6732877</v>
+        <v>6733037</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14095,39 +14082,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423776</v>
+        <v>121423779</v>
       </c>
       <c r="B114" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14164,10 +14162,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512152</v>
+        <v>512098</v>
       </c>
       <c r="R114" t="n">
-        <v>6733230</v>
+        <v>6733157</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14226,10 +14224,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425511</v>
+        <v>121423781</v>
       </c>
       <c r="B115" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14266,10 +14264,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512223</v>
+        <v>512210</v>
       </c>
       <c r="R115" t="n">
-        <v>6733062</v>
+        <v>6733094</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14316,22 +14314,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121425156</v>
+        <v>121426316</v>
       </c>
       <c r="B116" t="n">
-        <v>78608</v>
+        <v>91006</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14344,24 +14342,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
@@ -14371,10 +14373,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R116" t="n">
-        <v>6733054</v>
+        <v>6733055</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -14406,7 +14408,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14416,7 +14418,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14437,17 +14439,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425857</v>
+        <v>121425518</v>
       </c>
       <c r="B117" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14477,31 +14479,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512211</v>
+        <v>512110</v>
       </c>
       <c r="R117" t="n">
-        <v>6733056</v>
+        <v>6733025</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14539,29 +14530,28 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121426316</v>
+        <v>121423760</v>
       </c>
       <c r="B118" t="n">
-        <v>91005</v>
+        <v>92031</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14574,44 +14564,46 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512215</v>
+        <v>511818</v>
       </c>
       <c r="R118" t="n">
-        <v>6733055</v>
+        <v>6733114</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14638,50 +14630,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423780</v>
+        <v>121425873</v>
       </c>
       <c r="B119" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14694,37 +14675,48 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512100</v>
+        <v>512218</v>
       </c>
       <c r="R119" t="n">
-        <v>6733148</v>
+        <v>6733062</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14762,28 +14754,29 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425157</v>
+        <v>121425510</v>
       </c>
       <c r="B120" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14814,22 +14807,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512155</v>
+        <v>512131</v>
       </c>
       <c r="R120" t="n">
-        <v>6733037</v>
+        <v>6733029</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14856,50 +14846,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423777</v>
+        <v>121423767</v>
       </c>
       <c r="B121" t="n">
-        <v>78608</v>
+        <v>90933</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14908,38 +14887,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512148</v>
+        <v>512147</v>
       </c>
       <c r="R121" t="n">
-        <v>6733216</v>
+        <v>6733153</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14980,6 +14962,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14998,10 +14981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423781</v>
+        <v>121423777</v>
       </c>
       <c r="B122" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15038,10 +15021,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512210</v>
+        <v>512148</v>
       </c>
       <c r="R122" t="n">
-        <v>6733094</v>
+        <v>6733216</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15100,10 +15083,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121425873</v>
+        <v>121426863</v>
       </c>
       <c r="B123" t="n">
-        <v>90719</v>
+        <v>57372</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15116,48 +15099,45 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512218</v>
+        <v>512104</v>
       </c>
       <c r="R123" t="n">
-        <v>6733062</v>
+        <v>6733063</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15184,40 +15164,54 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121426863</v>
+        <v>121423727</v>
       </c>
       <c r="B124" t="n">
-        <v>57371</v>
+        <v>90685</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15226,49 +15220,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512104</v>
+        <v>512156</v>
       </c>
       <c r="R124" t="n">
-        <v>6733063</v>
+        <v>6733279</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15295,24 +15281,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15327,22 +15298,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425519</v>
+        <v>121425511</v>
       </c>
       <c r="B125" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15379,10 +15350,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512131</v>
+        <v>512223</v>
       </c>
       <c r="R125" t="n">
-        <v>6733029</v>
+        <v>6733062</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15441,10 +15412,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423757</v>
+        <v>121425158</v>
       </c>
       <c r="B126" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15457,42 +15428,40 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512093</v>
+        <v>512156</v>
       </c>
       <c r="R126" t="n">
-        <v>6733205</v>
+        <v>6733044</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15519,14 +15488,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15535,28 +15509,29 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423778</v>
+        <v>121423745</v>
       </c>
       <c r="B127" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15565,38 +15540,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512091</v>
+        <v>511789</v>
       </c>
       <c r="R127" t="n">
-        <v>6733225</v>
+        <v>6732877</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15655,10 +15635,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423779</v>
+        <v>121425156</v>
       </c>
       <c r="B128" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15689,19 +15669,22 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512098</v>
+        <v>512108</v>
       </c>
       <c r="R128" t="n">
-        <v>6733157</v>
+        <v>6733054</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15728,39 +15711,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121425159</v>
+        <v>121423778</v>
       </c>
       <c r="B129" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15791,22 +15785,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512216</v>
+        <v>512091</v>
       </c>
       <c r="R129" t="n">
-        <v>6733046</v>
+        <v>6733225</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15833,55 +15824,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423760</v>
+        <v>121423780</v>
       </c>
       <c r="B130" t="n">
-        <v>92030</v>
+        <v>78609</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15894,43 +15869,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>511818</v>
+        <v>512100</v>
       </c>
       <c r="R130" t="n">
-        <v>6733114</v>
+        <v>6733148</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15989,10 +15955,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423726</v>
+        <v>121423757</v>
       </c>
       <c r="B131" t="n">
-        <v>90684</v>
+        <v>57356</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16001,38 +15967,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512164</v>
+        <v>512093</v>
       </c>
       <c r="R131" t="n">
-        <v>6733000</v>
+        <v>6733205</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16065,6 +16036,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16091,10 +16067,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121423727</v>
+        <v>121425159</v>
       </c>
       <c r="B132" t="n">
-        <v>90684</v>
+        <v>78609</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16103,41 +16079,44 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512156</v>
+        <v>512216</v>
       </c>
       <c r="R132" t="n">
-        <v>6733279</v>
+        <v>6733046</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16164,39 +16143,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121425509</v>
+        <v>121423747</v>
       </c>
       <c r="B133" t="n">
-        <v>78608</v>
+        <v>4769</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16205,38 +16200,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512110</v>
+        <v>512148</v>
       </c>
       <c r="R133" t="n">
-        <v>6733025</v>
+        <v>6733263</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16283,12 +16283,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -16298,7 +16298,7 @@
         <v>121423788</v>
       </c>
       <c r="B134" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>121426850</v>
       </c>
       <c r="B135" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>121425773</v>
       </c>
       <c r="B137" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B103" t="n">
-        <v>57509</v>
+        <v>56568</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R103" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,7 +12951,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12978,10 +12983,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B104" t="n">
-        <v>56568</v>
+        <v>57372</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12995,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13021,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13076,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13103,10 +13108,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401369</v>
+        <v>121401354</v>
       </c>
       <c r="B105" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13119,21 +13124,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13141,7 +13146,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -13197,11 +13202,6 @@
       <c r="AB105" t="inlineStr">
         <is>
           <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425507</v>
+        <v>121423767</v>
       </c>
       <c r="B107" t="n">
-        <v>78609</v>
+        <v>90933</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,38 +13354,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512100</v>
+        <v>512147</v>
       </c>
       <c r="R107" t="n">
-        <v>6733039</v>
+        <v>6733153</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13420,36 +13423,32 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121425857</v>
+        <v>121423777</v>
       </c>
       <c r="B108" t="n">
         <v>78609</v>
@@ -13482,31 +13481,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512211</v>
+        <v>512148</v>
       </c>
       <c r="R108" t="n">
-        <v>6733056</v>
+        <v>6733216</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13544,26 +13532,25 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423776</v>
+        <v>121425520</v>
       </c>
       <c r="B109" t="n">
         <v>78609</v>
@@ -13603,10 +13590,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512152</v>
+        <v>512223</v>
       </c>
       <c r="R109" t="n">
-        <v>6733230</v>
+        <v>6733062</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,19 +13640,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121425818</v>
+        <v>121425516</v>
       </c>
       <c r="B110" t="n">
         <v>78609</v>
@@ -13698,31 +13685,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512221</v>
+        <v>512100</v>
       </c>
       <c r="R110" t="n">
-        <v>6733056</v>
+        <v>6733039</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13754,35 +13730,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121426864</v>
+        <v>121423778</v>
       </c>
       <c r="B111" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13795,45 +13775,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512216</v>
+        <v>512091</v>
       </c>
       <c r="R111" t="n">
-        <v>6733046</v>
+        <v>6733225</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13860,24 +13832,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13892,22 +13849,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423726</v>
+        <v>121423747</v>
       </c>
       <c r="B112" t="n">
-        <v>90685</v>
+        <v>4769</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13920,34 +13877,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512164</v>
+        <v>512148</v>
       </c>
       <c r="R112" t="n">
-        <v>6733000</v>
+        <v>6733263</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14006,10 +13968,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121425157</v>
+        <v>121423760</v>
       </c>
       <c r="B113" t="n">
-        <v>78609</v>
+        <v>92031</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14022,40 +13984,46 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512155</v>
+        <v>511818</v>
       </c>
       <c r="R113" t="n">
-        <v>6733037</v>
+        <v>6733114</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14082,47 +14050,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423779</v>
+        <v>121423776</v>
       </c>
       <c r="B114" t="n">
         <v>78609</v>
@@ -14162,10 +14119,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512098</v>
+        <v>512152</v>
       </c>
       <c r="R114" t="n">
-        <v>6733157</v>
+        <v>6733230</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14224,7 +14181,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121423781</v>
+        <v>121425818</v>
       </c>
       <c r="B115" t="n">
         <v>78609</v>
@@ -14257,20 +14214,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512210</v>
+        <v>512221</v>
       </c>
       <c r="R115" t="n">
-        <v>6733094</v>
+        <v>6733056</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14308,18 +14276,19 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -14548,10 +14517,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121423760</v>
+        <v>121423745</v>
       </c>
       <c r="B118" t="n">
-        <v>92031</v>
+        <v>56568</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14560,35 +14529,31 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -14597,10 +14562,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>511818</v>
+        <v>511789</v>
       </c>
       <c r="R118" t="n">
-        <v>6733114</v>
+        <v>6732877</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14659,10 +14624,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425873</v>
+        <v>121425157</v>
       </c>
       <c r="B119" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14675,48 +14640,40 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512218</v>
+        <v>512155</v>
       </c>
       <c r="R119" t="n">
-        <v>6733062</v>
+        <v>6733037</v>
       </c>
       <c r="S119" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14743,9 +14700,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14761,12 +14728,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -14875,10 +14842,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423767</v>
+        <v>121426864</v>
       </c>
       <c r="B121" t="n">
-        <v>90933</v>
+        <v>57372</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14887,44 +14854,49 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1618</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512147</v>
+        <v>512216</v>
       </c>
       <c r="R121" t="n">
-        <v>6733153</v>
+        <v>6733046</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14951,37 +14923,51 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423777</v>
+        <v>121423779</v>
       </c>
       <c r="B122" t="n">
         <v>78609</v>
@@ -15021,10 +15007,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512148</v>
+        <v>512098</v>
       </c>
       <c r="R122" t="n">
-        <v>6733216</v>
+        <v>6733157</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15208,10 +15194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423727</v>
+        <v>121423788</v>
       </c>
       <c r="B124" t="n">
-        <v>90685</v>
+        <v>100371</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15224,21 +15210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15248,10 +15234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512156</v>
+        <v>511830</v>
       </c>
       <c r="R124" t="n">
-        <v>6733279</v>
+        <v>6732919</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15310,10 +15296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121425511</v>
+        <v>121423726</v>
       </c>
       <c r="B125" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15322,25 +15308,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15350,10 +15336,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512223</v>
+        <v>512164</v>
       </c>
       <c r="R125" t="n">
-        <v>6733062</v>
+        <v>6733000</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15400,19 +15386,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121425158</v>
+        <v>121423781</v>
       </c>
       <c r="B126" t="n">
         <v>78609</v>
@@ -15446,22 +15432,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512156</v>
+        <v>512210</v>
       </c>
       <c r="R126" t="n">
-        <v>6733044</v>
+        <v>6733094</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15488,50 +15471,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423745</v>
+        <v>121425156</v>
       </c>
       <c r="B127" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15540,46 +15512,44 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>511789</v>
+        <v>512108</v>
       </c>
       <c r="R127" t="n">
-        <v>6732877</v>
+        <v>6733054</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15606,36 +15576,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425156</v>
+        <v>121425158</v>
       </c>
       <c r="B128" t="n">
         <v>78609</v>
@@ -15678,10 +15659,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512108</v>
+        <v>512156</v>
       </c>
       <c r="R128" t="n">
-        <v>6733054</v>
+        <v>6733044</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -15713,7 +15694,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15723,7 +15704,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15751,10 +15732,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423778</v>
+        <v>121423727</v>
       </c>
       <c r="B129" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15763,25 +15744,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15791,10 +15772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512091</v>
+        <v>512156</v>
       </c>
       <c r="R129" t="n">
-        <v>6733225</v>
+        <v>6733279</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15955,10 +15936,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423757</v>
+        <v>121425873</v>
       </c>
       <c r="B131" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15971,42 +15952,48 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512093</v>
+        <v>512218</v>
       </c>
       <c r="R131" t="n">
-        <v>6733205</v>
+        <v>6733062</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16038,39 +16025,35 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425159</v>
+        <v>121423757</v>
       </c>
       <c r="B132" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16083,40 +16066,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512216</v>
+        <v>512093</v>
       </c>
       <c r="R132" t="n">
-        <v>6733046</v>
+        <v>6733205</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16143,24 +16128,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>tussar på flera granar</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16169,29 +16144,28 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121423747</v>
+        <v>121425857</v>
       </c>
       <c r="B133" t="n">
-        <v>4769</v>
+        <v>78609</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16200,46 +16174,52 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512148</v>
+        <v>512211</v>
       </c>
       <c r="R133" t="n">
-        <v>6733263</v>
+        <v>6733056</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16277,28 +16257,29 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423788</v>
+        <v>121425159</v>
       </c>
       <c r="B134" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16307,41 +16288,44 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>511830</v>
+        <v>512216</v>
       </c>
       <c r="R134" t="n">
-        <v>6732919</v>
+        <v>6733046</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16368,29 +16352,45 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>56568</v>
+        <v>57509</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12870,25 +12870,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,20 +12896,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R103" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12951,12 +12951,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13108,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B105" t="n">
-        <v>57509</v>
+        <v>56568</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13120,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13146,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R105" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13191,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13201,7 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121423767</v>
+        <v>121423776</v>
       </c>
       <c r="B107" t="n">
-        <v>90933</v>
+        <v>78609</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13354,41 +13354,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512147</v>
+        <v>512152</v>
       </c>
       <c r="R107" t="n">
-        <v>6733153</v>
+        <v>6733230</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13429,7 +13426,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -13448,10 +13444,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423777</v>
+        <v>121423767</v>
       </c>
       <c r="B108" t="n">
-        <v>78609</v>
+        <v>90933</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13460,38 +13456,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512148</v>
+        <v>512147</v>
       </c>
       <c r="R108" t="n">
-        <v>6733216</v>
+        <v>6733153</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13532,6 +13531,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425520</v>
+        <v>121423757</v>
       </c>
       <c r="B109" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13566,34 +13566,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512223</v>
+        <v>512093</v>
       </c>
       <c r="R109" t="n">
-        <v>6733062</v>
+        <v>6733205</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13628,6 +13633,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13640,22 +13650,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121425516</v>
+        <v>121423747</v>
       </c>
       <c r="B110" t="n">
-        <v>78609</v>
+        <v>4769</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13664,38 +13674,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512100</v>
+        <v>512148</v>
       </c>
       <c r="R110" t="n">
-        <v>6733039</v>
+        <v>6733263</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13730,11 +13745,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13747,22 +13757,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423778</v>
+        <v>121423726</v>
       </c>
       <c r="B111" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13771,25 +13781,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13799,10 +13809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512091</v>
+        <v>512164</v>
       </c>
       <c r="R111" t="n">
-        <v>6733225</v>
+        <v>6733000</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13861,10 +13871,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423747</v>
+        <v>121423780</v>
       </c>
       <c r="B112" t="n">
-        <v>4769</v>
+        <v>78609</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13873,43 +13883,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512148</v>
+        <v>512100</v>
       </c>
       <c r="R112" t="n">
-        <v>6733263</v>
+        <v>6733148</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13968,10 +13973,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423760</v>
+        <v>121425518</v>
       </c>
       <c r="B113" t="n">
-        <v>92031</v>
+        <v>78609</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13984,43 +13989,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>511818</v>
+        <v>512110</v>
       </c>
       <c r="R113" t="n">
-        <v>6733114</v>
+        <v>6733025</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14067,22 +14063,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423776</v>
+        <v>121423760</v>
       </c>
       <c r="B114" t="n">
-        <v>78609</v>
+        <v>92031</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14095,34 +14091,43 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512152</v>
+        <v>511818</v>
       </c>
       <c r="R114" t="n">
-        <v>6733230</v>
+        <v>6733114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14181,7 +14186,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425818</v>
+        <v>121425516</v>
       </c>
       <c r="B115" t="n">
         <v>78609</v>
@@ -14214,31 +14219,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512221</v>
+        <v>512100</v>
       </c>
       <c r="R115" t="n">
-        <v>6733056</v>
+        <v>6733039</v>
       </c>
       <c r="S115" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14270,35 +14264,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121426316</v>
+        <v>121425511</v>
       </c>
       <c r="B116" t="n">
-        <v>91006</v>
+        <v>78609</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14311,44 +14309,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512215</v>
+        <v>512223</v>
       </c>
       <c r="R116" t="n">
-        <v>6733055</v>
+        <v>6733062</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14375,47 +14366,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425518</v>
+        <v>121423779</v>
       </c>
       <c r="B117" t="n">
         <v>78609</v>
@@ -14455,10 +14435,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512110</v>
+        <v>512098</v>
       </c>
       <c r="R117" t="n">
-        <v>6733025</v>
+        <v>6733157</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14505,22 +14485,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121423745</v>
+        <v>121425873</v>
       </c>
       <c r="B118" t="n">
-        <v>56568</v>
+        <v>90720</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14529,46 +14509,52 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>511789</v>
+        <v>512218</v>
       </c>
       <c r="R118" t="n">
-        <v>6732877</v>
+        <v>6733062</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14606,28 +14592,29 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425157</v>
+        <v>121426863</v>
       </c>
       <c r="B119" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14640,26 +14627,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -14667,10 +14659,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512155</v>
+        <v>512104</v>
       </c>
       <c r="R119" t="n">
-        <v>6733037</v>
+        <v>6733063</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -14702,7 +14694,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14712,7 +14704,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14721,7 +14718,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -14733,14 +14729,14 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425510</v>
+        <v>121425857</v>
       </c>
       <c r="B120" t="n">
         <v>78609</v>
@@ -14773,20 +14769,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512131</v>
+        <v>512211</v>
       </c>
       <c r="R120" t="n">
-        <v>6733029</v>
+        <v>6733056</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14824,18 +14831,19 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14967,7 +14975,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423779</v>
+        <v>121425818</v>
       </c>
       <c r="B122" t="n">
         <v>78609</v>
@@ -15000,20 +15008,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512098</v>
+        <v>512221</v>
       </c>
       <c r="R122" t="n">
-        <v>6733157</v>
+        <v>6733056</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15051,28 +15070,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121426863</v>
+        <v>121426316</v>
       </c>
       <c r="B123" t="n">
-        <v>57372</v>
+        <v>91006</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15085,31 +15105,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -15117,10 +15136,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512104</v>
+        <v>512215</v>
       </c>
       <c r="R123" t="n">
-        <v>6733063</v>
+        <v>6733055</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -15152,7 +15171,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15162,12 +15181,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15176,6 +15190,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15194,10 +15209,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423788</v>
+        <v>121423777</v>
       </c>
       <c r="B124" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15206,25 +15221,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15234,10 +15249,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>511830</v>
+        <v>512148</v>
       </c>
       <c r="R124" t="n">
-        <v>6732919</v>
+        <v>6733216</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15296,10 +15311,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423726</v>
+        <v>121423781</v>
       </c>
       <c r="B125" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15308,25 +15323,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15336,10 +15351,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512164</v>
+        <v>512210</v>
       </c>
       <c r="R125" t="n">
-        <v>6733000</v>
+        <v>6733094</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15398,10 +15413,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423781</v>
+        <v>121423788</v>
       </c>
       <c r="B126" t="n">
-        <v>78609</v>
+        <v>100371</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15410,25 +15425,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15438,10 +15453,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512210</v>
+        <v>511830</v>
       </c>
       <c r="R126" t="n">
-        <v>6733094</v>
+        <v>6732919</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15500,7 +15515,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121425156</v>
+        <v>121425519</v>
       </c>
       <c r="B127" t="n">
         <v>78609</v>
@@ -15534,22 +15549,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512108</v>
+        <v>512131</v>
       </c>
       <c r="R127" t="n">
-        <v>6733054</v>
+        <v>6733029</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15576,47 +15588,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425158</v>
+        <v>121423778</v>
       </c>
       <c r="B128" t="n">
         <v>78609</v>
@@ -15650,22 +15651,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512156</v>
+        <v>512091</v>
       </c>
       <c r="R128" t="n">
-        <v>6733044</v>
+        <v>6733225</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15692,50 +15690,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423727</v>
+        <v>121425158</v>
       </c>
       <c r="B129" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15744,41 +15731,44 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
         <v>512156</v>
       </c>
       <c r="R129" t="n">
-        <v>6733279</v>
+        <v>6733044</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15805,36 +15795,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423780</v>
+        <v>121425159</v>
       </c>
       <c r="B130" t="n">
         <v>78609</v>
@@ -15868,19 +15869,22 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512100</v>
+        <v>512216</v>
       </c>
       <c r="R130" t="n">
-        <v>6733148</v>
+        <v>6733046</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15907,39 +15911,55 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121425873</v>
+        <v>121423727</v>
       </c>
       <c r="B131" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15948,52 +15968,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512218</v>
+        <v>512156</v>
       </c>
       <c r="R131" t="n">
-        <v>6733062</v>
+        <v>6733279</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16031,29 +16040,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121423757</v>
+        <v>121425157</v>
       </c>
       <c r="B132" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16066,42 +16074,40 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512093</v>
+        <v>512155</v>
       </c>
       <c r="R132" t="n">
-        <v>6733205</v>
+        <v>6733037</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16128,14 +16134,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16144,25 +16155,26 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121425857</v>
+        <v>121425156</v>
       </c>
       <c r="B133" t="n">
         <v>78609</v>
@@ -16195,31 +16207,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512211</v>
+        <v>512108</v>
       </c>
       <c r="R133" t="n">
-        <v>6733056</v>
+        <v>6733054</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16246,9 +16250,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16264,22 +16278,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121425159</v>
+        <v>121423745</v>
       </c>
       <c r="B134" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16288,44 +16302,46 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512216</v>
+        <v>511789</v>
       </c>
       <c r="R134" t="n">
-        <v>6733046</v>
+        <v>6732877</v>
       </c>
       <c r="S134" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16352,55 +16368,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426850</v>
+        <v>121425773</v>
       </c>
       <c r="B135" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16413,40 +16413,45 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512216</v>
+        <v>512215</v>
       </c>
       <c r="R135" t="n">
-        <v>6733046</v>
+        <v>6733081</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16473,19 +16478,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>13:19</t>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16494,29 +16494,28 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B136" t="n">
-        <v>56568</v>
+        <v>90720</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16525,35 +16524,30 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16561,10 +16555,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16596,7 +16590,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16606,7 +16600,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16615,6 +16609,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16633,10 +16628,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121425773</v>
+        <v>121426859</v>
       </c>
       <c r="B137" t="n">
-        <v>57372</v>
+        <v>56568</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16645,25 +16640,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16671,23 +16666,23 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512215</v>
+        <v>512108</v>
       </c>
       <c r="R137" t="n">
-        <v>6733081</v>
+        <v>6733054</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16714,14 +16709,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16736,12 +16736,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401354</v>
+        <v>121401369</v>
       </c>
       <c r="B103" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12952,6 +12952,11 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12978,10 +12983,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401369</v>
+        <v>121401438</v>
       </c>
       <c r="B104" t="n">
-        <v>57372</v>
+        <v>56568</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12990,25 +12995,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13016,20 +13021,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R104" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13061,7 +13066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13071,12 +13076,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13103,10 +13108,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401438</v>
+        <v>121401354</v>
       </c>
       <c r="B105" t="n">
-        <v>56568</v>
+        <v>57509</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13115,25 +13120,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13141,20 +13146,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R105" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13186,7 +13191,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13196,12 +13201,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>I grus under ett vindfälle</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13342,7 +13342,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121423776</v>
+        <v>121425158</v>
       </c>
       <c r="B107" t="n">
         <v>78609</v>
@@ -13376,19 +13376,22 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512152</v>
+        <v>512156</v>
       </c>
       <c r="R107" t="n">
-        <v>6733230</v>
+        <v>6733044</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13415,39 +13418,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423767</v>
+        <v>121423760</v>
       </c>
       <c r="B108" t="n">
-        <v>90933</v>
+        <v>92031</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13456,41 +13470,47 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1618</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512147</v>
+        <v>511818</v>
       </c>
       <c r="R108" t="n">
-        <v>6733153</v>
+        <v>6733114</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13531,7 +13551,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13550,10 +13569,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121423757</v>
+        <v>121426864</v>
       </c>
       <c r="B109" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13566,16 +13585,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -13584,24 +13603,27 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512093</v>
+        <v>512216</v>
       </c>
       <c r="R109" t="n">
-        <v>6733205</v>
+        <v>6733046</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13628,14 +13650,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13650,22 +13682,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423747</v>
+        <v>121423788</v>
       </c>
       <c r="B110" t="n">
-        <v>4769</v>
+        <v>100371</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13678,39 +13710,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512148</v>
+        <v>511830</v>
       </c>
       <c r="R110" t="n">
-        <v>6733263</v>
+        <v>6732919</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13769,10 +13796,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121423726</v>
+        <v>121425157</v>
       </c>
       <c r="B111" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13781,41 +13808,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512164</v>
+        <v>512155</v>
       </c>
       <c r="R111" t="n">
-        <v>6733000</v>
+        <v>6733037</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13842,39 +13872,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423780</v>
+        <v>121423757</v>
       </c>
       <c r="B112" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13887,34 +13928,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512100</v>
+        <v>512093</v>
       </c>
       <c r="R112" t="n">
-        <v>6733148</v>
+        <v>6733205</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13949,6 +13995,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13966,17 +14017,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Philipp Weiss, Irina Röjås, Evalena Sköld, Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121425518</v>
+        <v>121423767</v>
       </c>
       <c r="B113" t="n">
-        <v>78609</v>
+        <v>90933</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13985,38 +14036,41 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512110</v>
+        <v>512147</v>
       </c>
       <c r="R113" t="n">
-        <v>6733025</v>
+        <v>6733153</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14057,28 +14111,29 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423760</v>
+        <v>121425156</v>
       </c>
       <c r="B114" t="n">
-        <v>92031</v>
+        <v>78609</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14091,46 +14146,40 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>511818</v>
+        <v>512108</v>
       </c>
       <c r="R114" t="n">
-        <v>6733114</v>
+        <v>6733054</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14157,36 +14206,47 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121425516</v>
+        <v>121423779</v>
       </c>
       <c r="B115" t="n">
         <v>78609</v>
@@ -14226,10 +14286,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512100</v>
+        <v>512098</v>
       </c>
       <c r="R115" t="n">
-        <v>6733039</v>
+        <v>6733157</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14264,11 +14324,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -14281,19 +14336,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121425511</v>
+        <v>121425159</v>
       </c>
       <c r="B116" t="n">
         <v>78609</v>
@@ -14327,19 +14382,22 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512223</v>
+        <v>512216</v>
       </c>
       <c r="R116" t="n">
-        <v>6733062</v>
+        <v>6733046</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14366,36 +14424,52 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121423779</v>
+        <v>121425857</v>
       </c>
       <c r="B117" t="n">
         <v>78609</v>
@@ -14428,20 +14502,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512098</v>
+        <v>512211</v>
       </c>
       <c r="R117" t="n">
-        <v>6733157</v>
+        <v>6733056</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14479,28 +14564,29 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425873</v>
+        <v>121425510</v>
       </c>
       <c r="B118" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14513,48 +14599,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512218</v>
+        <v>512131</v>
       </c>
       <c r="R118" t="n">
-        <v>6733062</v>
+        <v>6733029</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14592,29 +14667,28 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121426863</v>
+        <v>121423776</v>
       </c>
       <c r="B119" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14627,45 +14701,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512104</v>
+        <v>512152</v>
       </c>
       <c r="R119" t="n">
-        <v>6733063</v>
+        <v>6733230</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14692,24 +14758,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14724,19 +14775,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425857</v>
+        <v>121425507</v>
       </c>
       <c r="B120" t="n">
         <v>78609</v>
@@ -14769,31 +14820,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512211</v>
+        <v>512100</v>
       </c>
       <c r="R120" t="n">
-        <v>6733056</v>
+        <v>6733039</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14825,35 +14865,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121426864</v>
+        <v>121423726</v>
       </c>
       <c r="B121" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14862,49 +14906,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512216</v>
+        <v>512164</v>
       </c>
       <c r="R121" t="n">
-        <v>6733046</v>
+        <v>6733000</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14931,24 +14967,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14963,22 +14984,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425818</v>
+        <v>121423727</v>
       </c>
       <c r="B122" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14987,52 +15008,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512221</v>
+        <v>512156</v>
       </c>
       <c r="R122" t="n">
-        <v>6733056</v>
+        <v>6733279</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15070,19 +15080,18 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -15209,7 +15218,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423777</v>
+        <v>121425818</v>
       </c>
       <c r="B124" t="n">
         <v>78609</v>
@@ -15242,20 +15251,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512148</v>
+        <v>512221</v>
       </c>
       <c r="R124" t="n">
-        <v>6733216</v>
+        <v>6733056</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15293,28 +15313,29 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423781</v>
+        <v>121423745</v>
       </c>
       <c r="B125" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15323,38 +15344,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512210</v>
+        <v>511789</v>
       </c>
       <c r="R125" t="n">
-        <v>6733094</v>
+        <v>6732877</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15413,10 +15439,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121423788</v>
+        <v>121426863</v>
       </c>
       <c r="B126" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15425,41 +15451,49 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>511830</v>
+        <v>512104</v>
       </c>
       <c r="R126" t="n">
-        <v>6732919</v>
+        <v>6733063</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15486,9 +15520,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15503,19 +15552,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121425519</v>
+        <v>121423780</v>
       </c>
       <c r="B127" t="n">
         <v>78609</v>
@@ -15555,10 +15604,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512131</v>
+        <v>512100</v>
       </c>
       <c r="R127" t="n">
-        <v>6733029</v>
+        <v>6733148</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15605,19 +15654,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423778</v>
+        <v>121425518</v>
       </c>
       <c r="B128" t="n">
         <v>78609</v>
@@ -15657,10 +15706,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512091</v>
+        <v>512110</v>
       </c>
       <c r="R128" t="n">
-        <v>6733225</v>
+        <v>6733025</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15707,19 +15756,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121425158</v>
+        <v>121425511</v>
       </c>
       <c r="B129" t="n">
         <v>78609</v>
@@ -15753,22 +15802,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512156</v>
+        <v>512223</v>
       </c>
       <c r="R129" t="n">
-        <v>6733044</v>
+        <v>6733062</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15795,47 +15841,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121425159</v>
+        <v>121423777</v>
       </c>
       <c r="B130" t="n">
         <v>78609</v>
@@ -15869,22 +15904,19 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512216</v>
+        <v>512148</v>
       </c>
       <c r="R130" t="n">
-        <v>6733046</v>
+        <v>6733216</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15911,55 +15943,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423727</v>
+        <v>121423778</v>
       </c>
       <c r="B131" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15968,25 +15984,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15996,10 +16012,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512156</v>
+        <v>512091</v>
       </c>
       <c r="R131" t="n">
-        <v>6733279</v>
+        <v>6733225</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16058,10 +16074,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425157</v>
+        <v>121425873</v>
       </c>
       <c r="B132" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16074,40 +16090,48 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512155</v>
+        <v>512218</v>
       </c>
       <c r="R132" t="n">
-        <v>6733037</v>
+        <v>6733062</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16134,19 +16158,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16162,19 +16176,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121425156</v>
+        <v>121423781</v>
       </c>
       <c r="B133" t="n">
         <v>78609</v>
@@ -16208,22 +16222,19 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512108</v>
+        <v>512210</v>
       </c>
       <c r="R133" t="n">
-        <v>6733054</v>
+        <v>6733094</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16250,50 +16261,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423745</v>
+        <v>121423747</v>
       </c>
       <c r="B134" t="n">
-        <v>56568</v>
+        <v>4769</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16306,27 +16306,27 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16335,10 +16335,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>511789</v>
+        <v>512148</v>
       </c>
       <c r="R134" t="n">
-        <v>6732877</v>
+        <v>6733263</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16512,10 +16512,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>90720</v>
+        <v>56568</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16524,30 +16524,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16555,10 +16560,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R136" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16590,7 +16595,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16600,7 +16605,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16609,7 +16614,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16621,17 +16625,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B137" t="n">
-        <v>56568</v>
+        <v>90720</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16640,35 +16644,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16676,10 +16675,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R137" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16711,7 +16710,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16721,7 +16720,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16730,6 +16729,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -15564,7 +15564,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423780</v>
+        <v>121425518</v>
       </c>
       <c r="B127" t="n">
         <v>78609</v>
@@ -15604,10 +15604,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512100</v>
+        <v>512110</v>
       </c>
       <c r="R127" t="n">
-        <v>6733148</v>
+        <v>6733025</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15654,19 +15654,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425518</v>
+        <v>121425511</v>
       </c>
       <c r="B128" t="n">
         <v>78609</v>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512110</v>
+        <v>512223</v>
       </c>
       <c r="R128" t="n">
-        <v>6733025</v>
+        <v>6733062</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15768,7 +15768,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121425511</v>
+        <v>121423780</v>
       </c>
       <c r="B129" t="n">
         <v>78609</v>
@@ -15808,10 +15808,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512223</v>
+        <v>512100</v>
       </c>
       <c r="R129" t="n">
-        <v>6733062</v>
+        <v>6733148</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15858,12 +15858,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -12858,10 +12858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401369</v>
+        <v>121401354</v>
       </c>
       <c r="B103" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12874,21 +12874,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12952,11 +12952,6 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12983,10 +12978,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B104" t="n">
-        <v>56568</v>
+        <v>57373</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12995,25 +12990,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13021,20 +13016,20 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R104" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -13066,7 +13061,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13076,12 +13071,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13108,10 +13103,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401354</v>
+        <v>121401438</v>
       </c>
       <c r="B105" t="n">
-        <v>57509</v>
+        <v>56569</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13120,25 +13115,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13146,20 +13141,20 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512088</v>
+        <v>512055</v>
       </c>
       <c r="R105" t="n">
-        <v>6733213</v>
+        <v>6733202</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13191,7 +13186,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13201,7 +13196,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13231,7 +13231,7 @@
         <v>121401511</v>
       </c>
       <c r="B106" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121425158</v>
+        <v>121425857</v>
       </c>
       <c r="B107" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13375,23 +13375,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512156</v>
+        <v>512211</v>
       </c>
       <c r="R107" t="n">
-        <v>6733044</v>
+        <v>6733056</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13418,19 +13426,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13446,22 +13444,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423760</v>
+        <v>121423727</v>
       </c>
       <c r="B108" t="n">
-        <v>92031</v>
+        <v>90693</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13470,47 +13468,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>511818</v>
+        <v>512156</v>
       </c>
       <c r="R108" t="n">
-        <v>6733114</v>
+        <v>6733279</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13569,10 +13558,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121426864</v>
+        <v>121423776</v>
       </c>
       <c r="B109" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13585,45 +13574,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512216</v>
+        <v>512152</v>
       </c>
       <c r="R109" t="n">
-        <v>6733046</v>
+        <v>6733230</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13650,24 +13631,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13682,22 +13648,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121423788</v>
+        <v>121423778</v>
       </c>
       <c r="B110" t="n">
-        <v>100371</v>
+        <v>78616</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13706,25 +13672,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13734,10 +13700,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>511830</v>
+        <v>512091</v>
       </c>
       <c r="R110" t="n">
-        <v>6732919</v>
+        <v>6733225</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13796,10 +13762,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425157</v>
+        <v>121425519</v>
       </c>
       <c r="B111" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13830,22 +13796,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512155</v>
+        <v>512131</v>
       </c>
       <c r="R111" t="n">
-        <v>6733037</v>
+        <v>6733029</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13872,50 +13835,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121423757</v>
+        <v>121425518</v>
       </c>
       <c r="B112" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13928,39 +13880,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512093</v>
+        <v>512110</v>
       </c>
       <c r="R112" t="n">
-        <v>6733205</v>
+        <v>6733025</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13995,11 +13942,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -14012,22 +13954,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Irina Röjås, Evalena Sköld, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121423767</v>
+        <v>121425520</v>
       </c>
       <c r="B113" t="n">
-        <v>90933</v>
+        <v>78616</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14036,41 +13978,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512147</v>
+        <v>512223</v>
       </c>
       <c r="R113" t="n">
-        <v>6733153</v>
+        <v>6733062</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14111,19 +14050,18 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -14133,7 +14071,7 @@
         <v>121425156</v>
       </c>
       <c r="B114" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14246,10 +14184,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121423779</v>
+        <v>121425516</v>
       </c>
       <c r="B115" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14286,10 +14224,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512098</v>
+        <v>512100</v>
       </c>
       <c r="R115" t="n">
-        <v>6733157</v>
+        <v>6733039</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14324,6 +14262,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -14336,22 +14279,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121425159</v>
+        <v>121425158</v>
       </c>
       <c r="B116" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14391,10 +14334,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512216</v>
+        <v>512156</v>
       </c>
       <c r="R116" t="n">
-        <v>6733046</v>
+        <v>6733044</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -14426,7 +14369,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14436,12 +14379,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14469,10 +14407,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425857</v>
+        <v>121425157</v>
       </c>
       <c r="B117" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14502,31 +14440,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512211</v>
+        <v>512155</v>
       </c>
       <c r="R117" t="n">
-        <v>6733056</v>
+        <v>6733037</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14553,9 +14483,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14571,22 +14511,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121425510</v>
+        <v>121423788</v>
       </c>
       <c r="B118" t="n">
-        <v>78609</v>
+        <v>100379</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14595,25 +14535,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14623,10 +14563,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512131</v>
+        <v>511830</v>
       </c>
       <c r="R118" t="n">
-        <v>6733029</v>
+        <v>6732919</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14673,22 +14613,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121423776</v>
+        <v>121426864</v>
       </c>
       <c r="B119" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14701,37 +14641,45 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512152</v>
+        <v>512216</v>
       </c>
       <c r="R119" t="n">
-        <v>6733230</v>
+        <v>6733046</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14758,9 +14706,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14775,22 +14738,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425507</v>
+        <v>121423781</v>
       </c>
       <c r="B120" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14827,10 +14790,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512100</v>
+        <v>512210</v>
       </c>
       <c r="R120" t="n">
-        <v>6733039</v>
+        <v>6733094</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14865,11 +14828,6 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>mycket</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14882,22 +14840,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121423726</v>
+        <v>121423745</v>
       </c>
       <c r="B121" t="n">
-        <v>90685</v>
+        <v>56569</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14910,34 +14868,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512164</v>
+        <v>511789</v>
       </c>
       <c r="R121" t="n">
-        <v>6733000</v>
+        <v>6732877</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14996,10 +14959,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423727</v>
+        <v>121425818</v>
       </c>
       <c r="B122" t="n">
-        <v>90685</v>
+        <v>78616</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15008,41 +14971,52 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512156</v>
+        <v>512221</v>
       </c>
       <c r="R122" t="n">
-        <v>6733279</v>
+        <v>6733056</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15080,28 +15054,29 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121426316</v>
+        <v>121426863</v>
       </c>
       <c r="B123" t="n">
-        <v>91006</v>
+        <v>57373</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15114,30 +15089,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -15145,10 +15121,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512215</v>
+        <v>512104</v>
       </c>
       <c r="R123" t="n">
-        <v>6733055</v>
+        <v>6733063</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -15180,7 +15156,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15190,7 +15166,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15199,7 +15180,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15218,10 +15198,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121425818</v>
+        <v>121423747</v>
       </c>
       <c r="B124" t="n">
-        <v>78609</v>
+        <v>4770</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15230,52 +15210,46 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512221</v>
+        <v>512148</v>
       </c>
       <c r="R124" t="n">
-        <v>6733056</v>
+        <v>6733263</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15313,29 +15287,28 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423745</v>
+        <v>121423726</v>
       </c>
       <c r="B125" t="n">
-        <v>56568</v>
+        <v>90693</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15348,39 +15321,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>511789</v>
+        <v>512164</v>
       </c>
       <c r="R125" t="n">
-        <v>6732877</v>
+        <v>6733000</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15439,10 +15407,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121426863</v>
+        <v>121425159</v>
       </c>
       <c r="B126" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15455,31 +15423,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -15487,10 +15450,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512104</v>
+        <v>512216</v>
       </c>
       <c r="R126" t="n">
-        <v>6733063</v>
+        <v>6733046</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -15522,7 +15485,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15532,12 +15495,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Mycket färska spår</t>
+          <t>tussar på flera granar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15546,6 +15509,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -15557,17 +15521,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121425518</v>
+        <v>121423780</v>
       </c>
       <c r="B127" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15604,10 +15568,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512110</v>
+        <v>512100</v>
       </c>
       <c r="R127" t="n">
-        <v>6733025</v>
+        <v>6733148</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15654,22 +15618,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425511</v>
+        <v>121425873</v>
       </c>
       <c r="B128" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15682,37 +15646,48 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512223</v>
+        <v>512218</v>
       </c>
       <c r="R128" t="n">
         <v>6733062</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15750,28 +15725,29 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423780</v>
+        <v>121426316</v>
       </c>
       <c r="B129" t="n">
-        <v>78609</v>
+        <v>91014</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15784,37 +15760,44 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512100</v>
+        <v>512215</v>
       </c>
       <c r="R129" t="n">
-        <v>6733148</v>
+        <v>6733055</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15841,39 +15824,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423777</v>
+        <v>121423767</v>
       </c>
       <c r="B130" t="n">
-        <v>78609</v>
+        <v>90941</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15882,38 +15876,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>1618</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512148</v>
+        <v>512147</v>
       </c>
       <c r="R130" t="n">
-        <v>6733216</v>
+        <v>6733153</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15954,6 +15951,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -15972,10 +15970,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423778</v>
+        <v>121423757</v>
       </c>
       <c r="B131" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15988,34 +15986,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512091</v>
+        <v>512093</v>
       </c>
       <c r="R131" t="n">
-        <v>6733225</v>
+        <v>6733205</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16048,6 +16051,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16074,10 +16082,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425873</v>
+        <v>121423760</v>
       </c>
       <c r="B132" t="n">
-        <v>90720</v>
+        <v>92039</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16090,48 +16098,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512218</v>
+        <v>511818</v>
       </c>
       <c r="R132" t="n">
-        <v>6733062</v>
+        <v>6733114</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16169,29 +16175,28 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121423781</v>
+        <v>121423777</v>
       </c>
       <c r="B133" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16228,10 +16233,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512210</v>
+        <v>512148</v>
       </c>
       <c r="R133" t="n">
-        <v>6733094</v>
+        <v>6733216</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16290,10 +16295,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121423747</v>
+        <v>121423779</v>
       </c>
       <c r="B134" t="n">
-        <v>4769</v>
+        <v>78616</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16302,43 +16307,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512148</v>
+        <v>512098</v>
       </c>
       <c r="R134" t="n">
-        <v>6733263</v>
+        <v>6733157</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16400,7 +16400,7 @@
         <v>121425773</v>
       </c>
       <c r="B135" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16512,10 +16512,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121426850</v>
       </c>
       <c r="B136" t="n">
-        <v>56568</v>
+        <v>90728</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16524,35 +16524,30 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16560,10 +16555,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512216</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733046</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16595,7 +16590,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16605,7 +16600,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16614,6 +16609,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16625,17 +16621,17 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B137" t="n">
-        <v>90720</v>
+        <v>56569</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16644,30 +16640,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16675,10 +16676,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R137" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16710,7 +16711,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16720,7 +16721,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16729,7 +16730,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Beke Regelin, Irina Röjås, Philipp Weiss</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -14959,10 +14959,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121425818</v>
+        <v>121426863</v>
       </c>
       <c r="B122" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14975,48 +14975,45 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>512221</v>
+        <v>512104</v>
       </c>
       <c r="R122" t="n">
-        <v>6733056</v>
+        <v>6733063</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15043,40 +15040,54 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121426863</v>
+        <v>121425818</v>
       </c>
       <c r="B123" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15089,45 +15100,48 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512104</v>
+        <v>512221</v>
       </c>
       <c r="R123" t="n">
-        <v>6733063</v>
+        <v>6733056</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15154,44 +15168,30 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -15528,10 +15528,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121423780</v>
+        <v>121425873</v>
       </c>
       <c r="B127" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15544,37 +15544,48 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512100</v>
+        <v>512218</v>
       </c>
       <c r="R127" t="n">
-        <v>6733148</v>
+        <v>6733062</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15612,28 +15623,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121425873</v>
+        <v>121426316</v>
       </c>
       <c r="B128" t="n">
-        <v>90728</v>
+        <v>91014</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15646,48 +15658,44 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512218</v>
+        <v>512215</v>
       </c>
       <c r="R128" t="n">
-        <v>6733062</v>
+        <v>6733055</v>
       </c>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15714,9 +15722,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15732,22 +15750,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121426316</v>
+        <v>121423780</v>
       </c>
       <c r="B129" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15760,44 +15778,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512215</v>
+        <v>512100</v>
       </c>
       <c r="R129" t="n">
-        <v>6733055</v>
+        <v>6733148</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15824,40 +15835,29 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16513,10 +16513,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121425773</v>
+        <v>121426859</v>
       </c>
       <c r="B136" t="n">
-        <v>57373</v>
+        <v>56569</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16525,25 +16525,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16551,23 +16551,23 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512215</v>
+        <v>512108</v>
       </c>
       <c r="R136" t="n">
-        <v>6733081</v>
+        <v>6733054</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16594,14 +16594,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16616,22 +16621,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121426859</v>
+        <v>121425773</v>
       </c>
       <c r="B137" t="n">
-        <v>56569</v>
+        <v>57373</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16640,25 +16645,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16666,23 +16671,23 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R137" t="n">
-        <v>6733054</v>
+        <v>6733081</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16709,19 +16714,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16736,12 +16736,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16856,10 +16856,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104996307</v>
+        <v>104720437</v>
       </c>
       <c r="B139" t="n">
-        <v>95640</v>
+        <v>79847</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16868,42 +16868,39 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511633</v>
+        <v>511526</v>
       </c>
       <c r="R139" t="n">
-        <v>6733072</v>
+        <v>6733148</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16930,22 +16927,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16954,7 +16951,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16966,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16976,7 +16972,7 @@
         <v>121426851</v>
       </c>
       <c r="B140" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -17097,10 +17093,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>104720835</v>
+        <v>104996307</v>
       </c>
       <c r="B141" t="n">
-        <v>90960</v>
+        <v>95648</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17109,39 +17105,42 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>511438</v>
+        <v>511633</v>
       </c>
       <c r="R141" t="n">
-        <v>6733126</v>
+        <v>6733072</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17168,22 +17167,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17192,6 +17191,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -17203,17 +17203,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>104720437</v>
+        <v>104720479</v>
       </c>
       <c r="B142" t="n">
-        <v>79843</v>
+        <v>91389</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17222,39 +17222,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>511526</v>
+        <v>511448</v>
       </c>
       <c r="R142" t="n">
-        <v>6733148</v>
+        <v>6733109</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17286,7 +17288,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17296,7 +17298,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17305,6 +17307,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17323,10 +17326,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>104720479</v>
+        <v>104720835</v>
       </c>
       <c r="B143" t="n">
-        <v>91385</v>
+        <v>90964</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17335,41 +17338,39 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>511448</v>
+        <v>511438</v>
       </c>
       <c r="R143" t="n">
-        <v>6733109</v>
+        <v>6733126</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -17401,7 +17402,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17411,7 +17412,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17420,7 +17421,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Från början var denna bild en miljöbild men det kan vara  ringhack på granen till höger i bild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -17210,10 +17210,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>104720479</v>
+        <v>104720835</v>
       </c>
       <c r="B142" t="n">
-        <v>91389</v>
+        <v>90964</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17222,41 +17222,39 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>511448</v>
+        <v>511438</v>
       </c>
       <c r="R142" t="n">
-        <v>6733109</v>
+        <v>6733126</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17288,7 +17286,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17298,7 +17296,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17307,7 +17305,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17326,10 +17323,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>104720835</v>
+        <v>104720479</v>
       </c>
       <c r="B143" t="n">
-        <v>90964</v>
+        <v>91389</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17338,39 +17335,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>511438</v>
+        <v>511448</v>
       </c>
       <c r="R143" t="n">
-        <v>6733126</v>
+        <v>6733109</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -17402,7 +17401,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17412,7 +17411,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17421,6 +17420,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>104757748</v>
+        <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>56688</v>
+        <v>95648</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16744,53 +16744,41 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>2869</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512039</v>
+        <v>511633</v>
       </c>
       <c r="R138" t="n">
-        <v>6732944</v>
+        <v>6733072</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16814,22 +16802,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16838,6 +16826,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16849,17 +16838,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Bo karlstens, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104720437</v>
+        <v>104757748</v>
       </c>
       <c r="B139" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16868,42 +16857,57 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511526</v>
+        <v>512039</v>
       </c>
       <c r="R139" t="n">
-        <v>6733148</v>
+        <v>6732944</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16927,22 +16931,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16966,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Bo karlstens, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -17093,10 +17097,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>104996307</v>
+        <v>104720835</v>
       </c>
       <c r="B141" t="n">
-        <v>95648</v>
+        <v>90964</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,42 +17109,39 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>511633</v>
+        <v>511438</v>
       </c>
       <c r="R141" t="n">
-        <v>6733072</v>
+        <v>6733126</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17167,22 +17168,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17191,7 +17192,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -17203,17 +17203,17 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>104720835</v>
+        <v>104720437</v>
       </c>
       <c r="B142" t="n">
-        <v>90964</v>
+        <v>79847</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17226,21 +17226,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17251,10 +17251,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>511438</v>
+        <v>511526</v>
       </c>
       <c r="R142" t="n">
-        <v>6733126</v>
+        <v>6733148</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B138" t="n">
-        <v>95648</v>
+        <v>90944</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,45 +16740,52 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R138" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16802,22 +16809,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16838,7 +16845,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16973,10 +16980,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B140" t="n">
-        <v>90944</v>
+        <v>95650</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16985,52 +16992,45 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R140" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -17054,22 +17054,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17090,17 +17090,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>104720835</v>
+        <v>104720479</v>
       </c>
       <c r="B141" t="n">
-        <v>90964</v>
+        <v>91389</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17109,39 +17109,41 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>511438</v>
+        <v>511448</v>
       </c>
       <c r="R141" t="n">
-        <v>6733126</v>
+        <v>6733109</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17173,7 +17175,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17183,7 +17185,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17192,6 +17194,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -17207,235 +17210,6 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>104720437</v>
-      </c>
-      <c r="B142" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Leksand, Dlr</t>
-        </is>
-      </c>
-      <c r="Q142" t="n">
-        <v>511526</v>
-      </c>
-      <c r="R142" t="n">
-        <v>6733148</v>
-      </c>
-      <c r="S142" t="n">
-        <v>25</v>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AD142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT142" t="inlineStr"/>
-      <c r="AW142" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>104720479</v>
-      </c>
-      <c r="B143" t="n">
-        <v>91389</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Leksand, Dlr</t>
-        </is>
-      </c>
-      <c r="Q143" t="n">
-        <v>511448</v>
-      </c>
-      <c r="R143" t="n">
-        <v>6733109</v>
-      </c>
-      <c r="S143" t="n">
-        <v>25</v>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AD143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF143" t="inlineStr"/>
-      <c r="AG143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT143" t="inlineStr"/>
-      <c r="AW143" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY141"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16852,10 +16852,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104757748</v>
+        <v>104996307</v>
       </c>
       <c r="B139" t="n">
-        <v>56688</v>
+        <v>95650</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16868,53 +16868,41 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>2869</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>512039</v>
+        <v>511633</v>
       </c>
       <c r="R139" t="n">
-        <v>6732944</v>
+        <v>6733072</v>
       </c>
       <c r="S139" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16938,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,6 +16950,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -16973,17 +16962,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Bo karlstens, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>104996307</v>
+        <v>104720479</v>
       </c>
       <c r="B140" t="n">
-        <v>95650</v>
+        <v>91389</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16992,42 +16981,41 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>511633</v>
+        <v>511448</v>
       </c>
       <c r="R140" t="n">
-        <v>6733072</v>
+        <v>6733109</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -17054,22 +17042,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17090,126 +17078,10 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>104720479</v>
-      </c>
-      <c r="B141" t="n">
-        <v>91389</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Leksand, Dlr</t>
-        </is>
-      </c>
-      <c r="Q141" t="n">
-        <v>511448</v>
-      </c>
-      <c r="R141" t="n">
-        <v>6733109</v>
-      </c>
-      <c r="S141" t="n">
-        <v>25</v>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AD141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="inlineStr"/>
-      <c r="AG141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT141" t="inlineStr"/>
-      <c r="AW141" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16731,7 +16731,7 @@
         <v>121426851</v>
       </c>
       <c r="B138" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>104996307</v>
       </c>
       <c r="B139" t="n">
-        <v>95650</v>
+        <v>95658</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>104720479</v>
       </c>
       <c r="B140" t="n">
-        <v>91389</v>
+        <v>91397</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>90952</v>
+        <v>95658</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,52 +16740,45 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R138" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16809,22 +16802,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16845,17 +16838,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B139" t="n">
-        <v>95658</v>
+        <v>90952</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16864,45 +16857,52 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R139" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Paula Testad</t>
+          <t>Paula Testad, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B138" t="n">
-        <v>95658</v>
+        <v>90952</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,45 +16740,52 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R138" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16802,22 +16809,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16838,17 +16845,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B139" t="n">
-        <v>90952</v>
+        <v>95658</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16857,52 +16864,45 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R139" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Paula Testad, Evalena Sköld</t>
+          <t>Evalena Sköld, Paula Testad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Paula Testad</t>
+          <t>Paula Testad, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>90952</v>
+        <v>95658</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,52 +16740,45 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R138" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16809,22 +16802,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16845,17 +16838,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B139" t="n">
-        <v>95658</v>
+        <v>90952</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16864,45 +16857,52 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R139" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -2220,7 +2220,7 @@
         <v>106820920</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>107112512</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>107112558</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>107112862</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>107112000</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>107112612</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Paula Testad, Evalena Sköld</t>
+          <t>Evalena Sköld, Paula Testad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
         <v>107111878</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>107112906</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>107111650</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>107187792</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>107711765</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>107711582</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>109779386</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>115536805</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>121423757</v>
       </c>
       <c r="B131" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B138" t="n">
-        <v>95658</v>
+        <v>90955</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,45 +16740,52 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R138" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16802,22 +16809,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16838,17 +16845,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B139" t="n">
-        <v>90952</v>
+        <v>95661</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16857,52 +16864,45 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R139" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16972,7 +16972,7 @@
         <v>104720479</v>
       </c>
       <c r="B140" t="n">
-        <v>91397</v>
+        <v>91400</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16728,10 +16728,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>90955</v>
+        <v>95663</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,52 +16740,45 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R138" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16809,22 +16802,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16845,17 +16838,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104996307</v>
+        <v>121426851</v>
       </c>
       <c r="B139" t="n">
-        <v>95661</v>
+        <v>90957</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16864,45 +16857,52 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511633</v>
+        <v>512219</v>
       </c>
       <c r="R139" t="n">
-        <v>6733072</v>
+        <v>6733049</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16972,7 +16972,7 @@
         <v>104720479</v>
       </c>
       <c r="B140" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16731,7 +16731,7 @@
         <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>95663</v>
+        <v>95669</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>121426851</v>
       </c>
       <c r="B139" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>104720479</v>
       </c>
       <c r="B140" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY140"/>
+  <dimension ref="A1:AY139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7274,10 +7274,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>109554232</v>
+        <v>109573919</v>
       </c>
       <c r="B57" t="n">
-        <v>77507</v>
+        <v>5135</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7286,39 +7286,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>230405</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>512184.4327369915</v>
+        <v>511560.4397725284</v>
       </c>
       <c r="R57" t="n">
-        <v>6733079.230250133</v>
+        <v>6733173.522986764</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7345,22 +7353,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kan vara Bronshjon ?</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7369,28 +7382,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>109573919</v>
+        <v>107299889</v>
       </c>
       <c r="B58" t="n">
-        <v>5135</v>
+        <v>56411</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7399,20 +7413,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7420,13 +7434,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7436,10 +7453,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>511560.4397725284</v>
+        <v>511574.7960015915</v>
       </c>
       <c r="R58" t="n">
-        <v>6733173.522986764</v>
+        <v>6732975.953357909</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7466,27 +7483,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>06:06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Kan vara Bronshjon ?</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7495,29 +7507,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>107299889</v>
+        <v>107711765</v>
       </c>
       <c r="B59" t="n">
-        <v>56411</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7530,16 +7541,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7547,32 +7558,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>511574.7960015915</v>
+        <v>511997</v>
       </c>
       <c r="R59" t="n">
-        <v>6732975.953357909</v>
+        <v>6732945</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7596,22 +7603,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Sav sugning på Tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7626,19 +7628,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>107711765</v>
+        <v>107711582</v>
       </c>
       <c r="B60" t="n">
         <v>57481</v>
@@ -7686,10 +7688,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>511997</v>
+        <v>512139</v>
       </c>
       <c r="R60" t="n">
-        <v>6732945</v>
+        <v>6733053</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7726,7 +7728,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sav sugning på Tall</t>
+          <t>Sav sugning på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7753,10 +7755,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>107711582</v>
+        <v>109778867</v>
       </c>
       <c r="B61" t="n">
-        <v>57481</v>
+        <v>89412</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7769,45 +7771,44 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Moberget, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>512139</v>
+        <v>512203.9233118462</v>
       </c>
       <c r="R61" t="n">
-        <v>6733053</v>
+        <v>6733110.601970053</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7831,17 +7832,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Sav sugning på tall</t>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7850,28 +7856,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>109778867</v>
+        <v>109779386</v>
       </c>
       <c r="B62" t="n">
-        <v>89412</v>
+        <v>57481</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7884,21 +7891,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7906,8 +7913,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7915,10 +7927,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>512203.9233118462</v>
+        <v>512197</v>
       </c>
       <c r="R62" t="n">
-        <v>6733110.601970053</v>
+        <v>6733167</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7945,22 +7957,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7969,7 +7986,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7988,10 +8004,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>109779386</v>
+        <v>109778917</v>
       </c>
       <c r="B63" t="n">
-        <v>57481</v>
+        <v>55608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8004,16 +8020,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8026,11 +8042,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8040,10 +8060,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512197</v>
+        <v>512070.8301600809</v>
       </c>
       <c r="R63" t="n">
-        <v>6733167</v>
+        <v>6733206.021980882</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8070,27 +8090,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>Uppflygande när jag närmade mig</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8117,10 +8137,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>109778917</v>
+        <v>109778802</v>
       </c>
       <c r="B64" t="n">
-        <v>55608</v>
+        <v>77506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8133,50 +8153,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>SJös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>512070.8301600809</v>
+        <v>512137.7749503604</v>
       </c>
       <c r="R64" t="n">
-        <v>6733206.021980882</v>
+        <v>6733112.822935515</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8208,7 +8223,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8218,12 +8233,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Uppflygande när jag närmade mig</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8232,6 +8242,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8250,7 +8261,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>109778802</v>
+        <v>109779154</v>
       </c>
       <c r="B65" t="n">
         <v>77506</v>
@@ -8283,28 +8294,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>SJös Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>512137.7749503604</v>
+        <v>512285.3869880111</v>
       </c>
       <c r="R65" t="n">
-        <v>6733112.822935515</v>
+        <v>6733071.259532289</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8331,22 +8334,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8374,7 +8377,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>109779154</v>
+        <v>109778778</v>
       </c>
       <c r="B66" t="n">
         <v>77506</v>
@@ -8407,8 +8410,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -8417,10 +8428,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>512285.3869880111</v>
+        <v>512051.9967279172</v>
       </c>
       <c r="R66" t="n">
-        <v>6733071.259532289</v>
+        <v>6733124.761877734</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8447,22 +8458,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8490,10 +8501,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>109778778</v>
+        <v>109779324</v>
       </c>
       <c r="B67" t="n">
-        <v>77506</v>
+        <v>96334</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8502,38 +8513,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8541,10 +8553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>512051.9967279172</v>
+        <v>512259.7565126864</v>
       </c>
       <c r="R67" t="n">
-        <v>6733124.761877734</v>
+        <v>6733116.173210732</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8571,22 +8583,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8614,10 +8626,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109779324</v>
+        <v>110261958</v>
       </c>
       <c r="B68" t="n">
-        <v>96334</v>
+        <v>77506</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8626,50 +8638,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>512259.7565126864</v>
+        <v>511848.2512184178</v>
       </c>
       <c r="R68" t="n">
-        <v>6733116.173210732</v>
+        <v>6733105.005563889</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8696,22 +8697,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8720,26 +8721,25 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>110261958</v>
+        <v>109022721</v>
       </c>
       <c r="B69" t="n">
         <v>77506</v>
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>511848.2512184178</v>
+        <v>512109.4452190898</v>
       </c>
       <c r="R69" t="n">
-        <v>6733105.005563889</v>
+        <v>6733087.291480071</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8810,22 +8810,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8852,10 +8852,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>109022721</v>
+        <v>111783083</v>
       </c>
       <c r="B70" t="n">
-        <v>77506</v>
+        <v>96735</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8864,39 +8864,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>512109.4452190898</v>
+        <v>511377</v>
       </c>
       <c r="R70" t="n">
-        <v>6733087.291480071</v>
+        <v>6733130</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8923,22 +8923,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>19:42</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8953,22 +8943,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Göran Ehn, Bo karlstens, Kajsa Larsson, Lars-Erik Nilsson, Erik Danielsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>111783083</v>
+        <v>112056163</v>
       </c>
       <c r="B71" t="n">
-        <v>96735</v>
+        <v>95702</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8977,42 +8967,42 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Leksand (Leksand), Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>511377</v>
+        <v>511889</v>
       </c>
       <c r="R71" t="n">
-        <v>6733130</v>
+        <v>6732965</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9036,12 +9026,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9056,22 +9056,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn, Bo karlstens, Kajsa Larsson, Lars-Erik Nilsson, Erik Danielsson, Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112056163</v>
+        <v>115536805</v>
       </c>
       <c r="B72" t="n">
-        <v>95702</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9080,42 +9080,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Leksand (Leksand), Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>511889</v>
+        <v>511406</v>
       </c>
       <c r="R72" t="n">
-        <v>6732965</v>
+        <v>6733131</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9139,22 +9147,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9169,22 +9167,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>115536805</v>
+        <v>109024922</v>
       </c>
       <c r="B73" t="n">
-        <v>57481</v>
+        <v>90297</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9193,47 +9191,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>511406</v>
+        <v>512068</v>
       </c>
       <c r="R73" t="n">
-        <v>6733131</v>
+        <v>6733203</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9260,12 +9250,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9280,22 +9280,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>109024922</v>
+        <v>109018319</v>
       </c>
       <c r="B74" t="n">
-        <v>90297</v>
+        <v>96612</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9308,35 +9308,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>224363</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>512068</v>
+        <v>511581</v>
       </c>
       <c r="R74" t="n">
-        <v>6733203</v>
+        <v>6733088</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9368,7 +9372,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9378,7 +9382,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9405,10 +9409,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>109018319</v>
+        <v>115536788</v>
       </c>
       <c r="B75" t="n">
-        <v>96612</v>
+        <v>5165</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9421,42 +9425,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>224363</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Leksand (Leksand), Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>511581</v>
+        <v>511441</v>
       </c>
       <c r="R75" t="n">
-        <v>6733088</v>
+        <v>6733082</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9480,22 +9484,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9504,6 +9508,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9515,17 +9520,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>115536788</v>
+        <v>115929844</v>
       </c>
       <c r="B76" t="n">
-        <v>5165</v>
+        <v>57281</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9534,43 +9539,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Leksand (Leksand), Dlr</t>
+          <t>Sjös-Moberg (Sjös-Moberg), Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>511441</v>
+        <v>511717</v>
       </c>
       <c r="R76" t="n">
-        <v>6733082</v>
+        <v>6733116</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9597,22 +9605,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9621,9 +9629,13 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9633,17 +9645,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>115929844</v>
+        <v>104744866</v>
       </c>
       <c r="B77" t="n">
-        <v>57281</v>
+        <v>97693</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9652,49 +9664,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sjös-Moberg (Sjös-Moberg), Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>511717</v>
+        <v>511495</v>
       </c>
       <c r="R77" t="n">
-        <v>6733116</v>
+        <v>6733158</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9718,22 +9723,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2022-11-19</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2022-11-19</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9744,11 +9749,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9765,10 +9765,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104744866</v>
+        <v>109015621</v>
       </c>
       <c r="B78" t="n">
-        <v>97693</v>
+        <v>56560</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9781,38 +9781,49 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Moberg, Hackmora, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>511495</v>
+        <v>512218</v>
       </c>
       <c r="R78" t="n">
-        <v>6733158</v>
+        <v>6733064</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9836,22 +9847,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9866,22 +9877,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>109015621</v>
+        <v>120516126</v>
       </c>
       <c r="B79" t="n">
-        <v>56560</v>
+        <v>57501</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9890,53 +9901,53 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Moberg, Hackmora, Leksand, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>512218</v>
+        <v>511388</v>
       </c>
       <c r="R79" t="n">
-        <v>6733064</v>
+        <v>6733145</v>
       </c>
       <c r="S79" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9960,22 +9971,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Vi såg och hörde två talltitor ikring oss en stund, söta!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9990,19 +10006,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120516126</v>
+        <v>120520450</v>
       </c>
       <c r="B80" t="n">
         <v>57501</v>
@@ -10035,11 +10051,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
@@ -10050,14 +10062,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>511388</v>
+        <v>511633</v>
       </c>
       <c r="R80" t="n">
-        <v>6733145</v>
+        <v>6733072</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10089,7 +10101,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10099,12 +10111,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Vi såg och hörde två talltitor ikring oss en stund, söta!</t>
+          <t>Rakt fram i bild skymtar en myr,/mosse en av många  myrar/mossar, i området</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10124,17 +10136,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120520450</v>
+        <v>115538714</v>
       </c>
       <c r="B81" t="n">
-        <v>57501</v>
+        <v>56560</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10143,49 +10155,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>511633</v>
+        <v>511866</v>
       </c>
       <c r="R81" t="n">
-        <v>6733072</v>
+        <v>6733109</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10209,27 +10225,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:57</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rakt fram i bild skymtar en myr,/mosse en av många  myrar/mossar, i området</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10249,14 +10260,14 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>115538714</v>
+        <v>110261844</v>
       </c>
       <c r="B82" t="n">
         <v>56560</v>
@@ -10291,7 +10302,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -10304,17 +10315,17 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>511866</v>
+        <v>511846</v>
       </c>
       <c r="R82" t="n">
-        <v>6733109</v>
+        <v>6733117</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10338,22 +10349,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Mycket vacker avverkningshotad fäbodskog på högsta berget.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10373,14 +10389,14 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110261844</v>
+        <v>115538585</v>
       </c>
       <c r="B83" t="n">
         <v>56560</v>
@@ -10415,7 +10431,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -10428,17 +10444,17 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>511846</v>
+        <v>511814</v>
       </c>
       <c r="R83" t="n">
-        <v>6733117</v>
+        <v>6733107</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10462,27 +10478,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Mycket vacker avverkningshotad fäbodskog på högsta berget.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10502,14 +10513,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>115538585</v>
+        <v>110260485</v>
       </c>
       <c r="B84" t="n">
         <v>56560</v>
@@ -10544,7 +10555,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -10557,17 +10568,17 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>511814</v>
+        <v>511749</v>
       </c>
       <c r="R84" t="n">
-        <v>6733107</v>
+        <v>6733051</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10591,22 +10602,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10626,14 +10637,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>110260485</v>
+        <v>115930127</v>
       </c>
       <c r="B85" t="n">
         <v>56560</v>
@@ -10668,7 +10679,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -10681,17 +10692,17 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>511749</v>
+        <v>511715</v>
       </c>
       <c r="R85" t="n">
-        <v>6733051</v>
+        <v>6733086</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10715,22 +10726,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10750,14 +10761,14 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>115930127</v>
+        <v>110261494</v>
       </c>
       <c r="B86" t="n">
         <v>56560</v>
@@ -10792,7 +10803,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -10805,17 +10816,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>511715</v>
+        <v>511734</v>
       </c>
       <c r="R86" t="n">
-        <v>6733086</v>
+        <v>6733082</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10839,22 +10850,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Mycket vacker avverkningshotat höghöjds skog, fäbodskog.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10874,14 +10890,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>110261494</v>
+        <v>108144601</v>
       </c>
       <c r="B87" t="n">
         <v>56560</v>
@@ -10916,7 +10932,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -10929,14 +10945,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>511734</v>
+        <v>511536</v>
       </c>
       <c r="R87" t="n">
-        <v>6733082</v>
+        <v>6733013</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10963,27 +10979,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Mycket vacker avverkningshotat höghöjds skog, fäbodskog.</t>
+          <t>Ett 50 tal spillning/ostkrokar, all spillning är inte med på bilden.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11003,14 +11019,14 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>108144601</v>
+        <v>120644581</v>
       </c>
       <c r="B88" t="n">
         <v>56560</v>
@@ -11045,27 +11061,24 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>511536</v>
+        <v>511979</v>
       </c>
       <c r="R88" t="n">
-        <v>6733013</v>
+        <v>6732946</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11092,27 +11105,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ett 50 tal spillning/ostkrokar, all spillning är inte med på bilden.</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11132,17 +11140,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120644581</v>
+        <v>120252571</v>
       </c>
       <c r="B89" t="n">
-        <v>56560</v>
+        <v>90644</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11155,43 +11163,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>511979</v>
+        <v>511734</v>
       </c>
       <c r="R89" t="n">
-        <v>6732946</v>
+        <v>6733082</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -11218,22 +11217,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11260,10 +11259,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120252571</v>
+        <v>115536894</v>
       </c>
       <c r="B90" t="n">
-        <v>90644</v>
+        <v>56560</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11276,37 +11275,53 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>511734</v>
+        <v>511445</v>
       </c>
       <c r="R90" t="n">
-        <v>6733082</v>
+        <v>6733052</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11330,22 +11345,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11365,14 +11380,14 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>115536894</v>
+        <v>115930630</v>
       </c>
       <c r="B91" t="n">
         <v>56560</v>
@@ -11407,34 +11422,30 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>511445</v>
+        <v>511873</v>
       </c>
       <c r="R91" t="n">
-        <v>6733052</v>
+        <v>6733122</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11458,22 +11469,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11500,10 +11511,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>115930630</v>
+        <v>120251411</v>
       </c>
       <c r="B92" t="n">
-        <v>56560</v>
+        <v>57501</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11512,53 +11523,53 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>511873</v>
+        <v>511536</v>
       </c>
       <c r="R92" t="n">
-        <v>6733122</v>
+        <v>6733013</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11582,22 +11593,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Den lät som talltitor gör om hösten. Jag vet inte om det kallas "övriga läten" eller sång.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11617,17 +11633,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120251411</v>
+        <v>120645186</v>
       </c>
       <c r="B93" t="n">
-        <v>57501</v>
+        <v>57717</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11636,25 +11652,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11662,27 +11678,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>511536</v>
+        <v>512138</v>
       </c>
       <c r="R93" t="n">
-        <v>6733013</v>
+        <v>6733019</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11706,27 +11719,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Den lät som talltitor gör om hösten. Jag vet inte om det kallas "övriga läten" eller sång.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11753,10 +11761,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120645186</v>
+        <v>120667335</v>
       </c>
       <c r="B94" t="n">
-        <v>57717</v>
+        <v>56560</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11769,46 +11777,49 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512138</v>
+        <v>511699</v>
       </c>
       <c r="R94" t="n">
-        <v>6733019</v>
+        <v>6733120</v>
       </c>
       <c r="S94" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11832,22 +11843,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11874,10 +11885,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120667335</v>
+        <v>120252254</v>
       </c>
       <c r="B95" t="n">
-        <v>56560</v>
+        <v>91990</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11886,53 +11897,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>511699</v>
+        <v>511734</v>
       </c>
       <c r="R95" t="n">
-        <v>6733120</v>
+        <v>6733082</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11956,22 +11955,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11998,14 +11997,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120252254</v>
+        <v>120642824</v>
       </c>
       <c r="B96" t="n">
         <v>91990</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12031,17 +12030,28 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>511734</v>
+        <v>511816</v>
       </c>
       <c r="R96" t="n">
-        <v>6733082</v>
+        <v>6733100</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -12068,22 +12078,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Största över 30 cm. Hällmark</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12092,6 +12107,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12110,64 +12126,61 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120642824</v>
+        <v>115538485</v>
       </c>
       <c r="B97" t="n">
-        <v>91990</v>
+        <v>56560</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>511816</v>
+        <v>511779</v>
       </c>
       <c r="R97" t="n">
-        <v>6733100</v>
+        <v>6732965</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12191,27 +12204,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Största över 30 cm. Hällmark</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12220,7 +12228,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12232,17 +12239,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>115538485</v>
+        <v>115926171</v>
       </c>
       <c r="B98" t="n">
-        <v>56560</v>
+        <v>57364</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12251,49 +12258,45 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Sjös Moberg, Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>511779</v>
+        <v>511474</v>
       </c>
       <c r="R98" t="n">
-        <v>6732965</v>
+        <v>6733099</v>
       </c>
       <c r="S98" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12317,22 +12320,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12359,10 +12362,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>115926171</v>
+        <v>120252447</v>
       </c>
       <c r="B99" t="n">
-        <v>57364</v>
+        <v>91963</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12371,45 +12374,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Sjös Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>511474</v>
+        <v>511734</v>
       </c>
       <c r="R99" t="n">
-        <v>6733099</v>
+        <v>6733082</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12433,22 +12432,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Minst 24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12468,17 +12472,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120252447</v>
+        <v>120789806</v>
       </c>
       <c r="B100" t="n">
-        <v>91963</v>
+        <v>57364</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12487,41 +12491,49 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>511734</v>
+        <v>511612</v>
       </c>
       <c r="R100" t="n">
-        <v>6733082</v>
+        <v>6732873</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12545,27 +12557,27 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Minst 24</t>
+          <t>Födohack i gran. Vacker bäckravin i kalkbarrskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12592,10 +12604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120789806</v>
+        <v>120789839</v>
       </c>
       <c r="B101" t="n">
-        <v>57364</v>
+        <v>78598</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12608,31 +12620,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12640,10 +12647,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>511612</v>
+        <v>511639</v>
       </c>
       <c r="R101" t="n">
-        <v>6732873</v>
+        <v>6732817</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12675,7 +12682,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12685,12 +12692,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Födohack i gran. Vacker bäckravin i kalkbarrskog som hotas av avverkning</t>
+          <t>i träden närmast bäcken i ravinen. vacker myr ovanför. Avverkningshotad skog i bäckravin.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12699,6 +12706,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12717,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120789839</v>
+        <v>121401438</v>
       </c>
       <c r="B102" t="n">
-        <v>78598</v>
+        <v>56569</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12729,44 +12737,49 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>511639</v>
+        <v>512055</v>
       </c>
       <c r="R102" t="n">
-        <v>6732817</v>
+        <v>6733202</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12790,27 +12803,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>i träden närmast bäcken i ravinen. vacker myr ovanför. Avverkningshotad skog i bäckravin.</t>
+          <t>I grus under ett vindfälle</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12819,7 +12832,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12838,10 +12850,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121401438</v>
+        <v>121401369</v>
       </c>
       <c r="B103" t="n">
-        <v>56569</v>
+        <v>57373</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12850,25 +12862,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12876,20 +12888,20 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512055</v>
+        <v>512088</v>
       </c>
       <c r="R103" t="n">
-        <v>6733202</v>
+        <v>6733213</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12921,7 +12933,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12931,12 +12943,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>I grus under ett vindfälle</t>
+          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12963,10 +12975,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121401369</v>
+        <v>121401354</v>
       </c>
       <c r="B104" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12979,21 +12991,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13001,7 +13013,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -13057,11 +13069,6 @@
       <c r="AB104" t="inlineStr">
         <is>
           <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Födosök, mycket rikligt med död ved.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13088,10 +13095,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121401354</v>
+        <v>121401511</v>
       </c>
       <c r="B105" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13104,31 +13111,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13136,10 +13146,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>512088</v>
+        <v>512151</v>
       </c>
       <c r="R105" t="n">
-        <v>6733213</v>
+        <v>6733225</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13169,27 +13179,18 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13208,10 +13209,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121401511</v>
+        <v>121426864</v>
       </c>
       <c r="B106" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13224,48 +13225,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>512151</v>
+        <v>512216</v>
       </c>
       <c r="R106" t="n">
-        <v>6733225</v>
+        <v>6733046</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13289,12 +13287,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13303,7 +13316,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -13315,17 +13327,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121426864</v>
+        <v>121423727</v>
       </c>
       <c r="B107" t="n">
-        <v>57373</v>
+        <v>90693</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13334,49 +13346,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>512216</v>
+        <v>512156</v>
       </c>
       <c r="R107" t="n">
-        <v>6733046</v>
+        <v>6733279</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13403,24 +13407,9 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>mycket färska födosökshack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13435,22 +13424,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121423727</v>
+        <v>121425873</v>
       </c>
       <c r="B108" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13459,41 +13448,52 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>512156</v>
+        <v>512218</v>
       </c>
       <c r="R108" t="n">
-        <v>6733279</v>
+        <v>6733062</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13531,28 +13531,29 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121425873</v>
+        <v>121425157</v>
       </c>
       <c r="B109" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13565,48 +13566,40 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>512218</v>
+        <v>512155</v>
       </c>
       <c r="R109" t="n">
-        <v>6733062</v>
+        <v>6733037</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13633,9 +13626,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13651,19 +13654,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121425157</v>
+        <v>121425509</v>
       </c>
       <c r="B110" t="n">
         <v>78616</v>
@@ -13697,22 +13700,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512155</v>
+        <v>512110</v>
       </c>
       <c r="R110" t="n">
-        <v>6733037</v>
+        <v>6733025</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13739,50 +13739,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121425509</v>
+        <v>121426316</v>
       </c>
       <c r="B111" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13795,37 +13784,44 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512110</v>
+        <v>512215</v>
       </c>
       <c r="R111" t="n">
-        <v>6733025</v>
+        <v>6733055</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13852,39 +13848,50 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121426316</v>
+        <v>121425158</v>
       </c>
       <c r="B112" t="n">
-        <v>91014</v>
+        <v>78616</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13897,28 +13904,24 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
@@ -13928,10 +13931,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512215</v>
+        <v>512156</v>
       </c>
       <c r="R112" t="n">
-        <v>6733055</v>
+        <v>6733044</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -13963,7 +13966,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13973,7 +13976,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13994,17 +13997,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121425158</v>
+        <v>121423726</v>
       </c>
       <c r="B113" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -14013,44 +14016,41 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512156</v>
+        <v>512164</v>
       </c>
       <c r="R113" t="n">
-        <v>6733044</v>
+        <v>6733000</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -14077,50 +14077,39 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121423726</v>
+        <v>121423767</v>
       </c>
       <c r="B114" t="n">
-        <v>90693</v>
+        <v>90941</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14129,38 +14118,41 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>1618</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512164</v>
+        <v>512147</v>
       </c>
       <c r="R114" t="n">
-        <v>6733000</v>
+        <v>6733153</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14201,6 +14193,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -14219,10 +14212,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121423767</v>
+        <v>121423776</v>
       </c>
       <c r="B115" t="n">
-        <v>90941</v>
+        <v>78616</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14231,41 +14224,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1618</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512147</v>
+        <v>512152</v>
       </c>
       <c r="R115" t="n">
-        <v>6733153</v>
+        <v>6733230</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14306,7 +14296,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -14325,7 +14314,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121423776</v>
+        <v>121425159</v>
       </c>
       <c r="B116" t="n">
         <v>78616</v>
@@ -14359,19 +14348,22 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512152</v>
+        <v>512216</v>
       </c>
       <c r="R116" t="n">
-        <v>6733230</v>
+        <v>6733046</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14398,36 +14390,52 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>tussar på flera granar</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121425159</v>
+        <v>121423779</v>
       </c>
       <c r="B117" t="n">
         <v>78616</v>
@@ -14461,22 +14469,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512216</v>
+        <v>512098</v>
       </c>
       <c r="R117" t="n">
-        <v>6733046</v>
+        <v>6733157</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14503,52 +14508,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>tussar på flera granar</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121423779</v>
+        <v>121425516</v>
       </c>
       <c r="B118" t="n">
         <v>78616</v>
@@ -14588,10 +14577,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512098</v>
+        <v>512100</v>
       </c>
       <c r="R118" t="n">
-        <v>6733157</v>
+        <v>6733039</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14626,6 +14615,11 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>mycket</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14638,19 +14632,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121425516</v>
+        <v>121425510</v>
       </c>
       <c r="B119" t="n">
         <v>78616</v>
@@ -14690,10 +14684,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512100</v>
+        <v>512131</v>
       </c>
       <c r="R119" t="n">
-        <v>6733039</v>
+        <v>6733029</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14726,11 +14720,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>mycket</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14757,7 +14746,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121425510</v>
+        <v>121425511</v>
       </c>
       <c r="B120" t="n">
         <v>78616</v>
@@ -14797,10 +14786,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512131</v>
+        <v>512223</v>
       </c>
       <c r="R120" t="n">
-        <v>6733029</v>
+        <v>6733062</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14859,10 +14848,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121425511</v>
+        <v>121423788</v>
       </c>
       <c r="B121" t="n">
-        <v>78616</v>
+        <v>100379</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14871,25 +14860,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14899,10 +14888,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512223</v>
+        <v>511830</v>
       </c>
       <c r="R121" t="n">
-        <v>6733062</v>
+        <v>6732919</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14949,22 +14938,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121423788</v>
+        <v>121423747</v>
       </c>
       <c r="B122" t="n">
-        <v>100379</v>
+        <v>4770</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14977,34 +14966,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>511830</v>
+        <v>512148</v>
       </c>
       <c r="R122" t="n">
-        <v>6732919</v>
+        <v>6733263</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15063,10 +15057,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121423747</v>
+        <v>121423781</v>
       </c>
       <c r="B123" t="n">
-        <v>4770</v>
+        <v>78616</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15075,43 +15069,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>512148</v>
+        <v>512210</v>
       </c>
       <c r="R123" t="n">
-        <v>6733263</v>
+        <v>6733094</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15170,10 +15159,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121423781</v>
+        <v>121423745</v>
       </c>
       <c r="B124" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15182,38 +15171,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512210</v>
+        <v>511789</v>
       </c>
       <c r="R124" t="n">
-        <v>6733094</v>
+        <v>6732877</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15272,10 +15266,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121423745</v>
+        <v>121426863</v>
       </c>
       <c r="B125" t="n">
-        <v>56569</v>
+        <v>57373</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15284,46 +15278,49 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>511789</v>
+        <v>512104</v>
       </c>
       <c r="R125" t="n">
-        <v>6732877</v>
+        <v>6733063</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15350,9 +15347,24 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Mycket färska spår</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15367,22 +15379,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121426863</v>
+        <v>121425857</v>
       </c>
       <c r="B126" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15395,45 +15407,48 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512104</v>
+        <v>512211</v>
       </c>
       <c r="R126" t="n">
-        <v>6733063</v>
+        <v>6733056</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15460,51 +15475,37 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Mycket färska spår</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121425857</v>
+        <v>121423778</v>
       </c>
       <c r="B127" t="n">
         <v>78616</v>
@@ -15537,31 +15538,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512211</v>
+        <v>512091</v>
       </c>
       <c r="R127" t="n">
-        <v>6733056</v>
+        <v>6733225</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15599,26 +15589,25 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121423778</v>
+        <v>121423777</v>
       </c>
       <c r="B128" t="n">
         <v>78616</v>
@@ -15658,10 +15647,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512091</v>
+        <v>512148</v>
       </c>
       <c r="R128" t="n">
-        <v>6733225</v>
+        <v>6733216</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15720,10 +15709,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121423777</v>
+        <v>121423760</v>
       </c>
       <c r="B129" t="n">
-        <v>78616</v>
+        <v>92039</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15736,34 +15725,43 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512148</v>
+        <v>511818</v>
       </c>
       <c r="R129" t="n">
-        <v>6733216</v>
+        <v>6733114</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15822,10 +15820,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121423760</v>
+        <v>121423757</v>
       </c>
       <c r="B130" t="n">
-        <v>92039</v>
+        <v>57481</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15838,31 +15836,27 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -15871,10 +15865,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>511818</v>
+        <v>512093</v>
       </c>
       <c r="R130" t="n">
-        <v>6733114</v>
+        <v>6733205</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15907,6 +15901,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15933,10 +15932,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121423757</v>
+        <v>121425156</v>
       </c>
       <c r="B131" t="n">
-        <v>57481</v>
+        <v>78616</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15949,42 +15948,40 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512093</v>
+        <v>512108</v>
       </c>
       <c r="R131" t="n">
-        <v>6733205</v>
+        <v>6733054</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16011,14 +16008,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16027,25 +16029,26 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121425156</v>
+        <v>121423780</v>
       </c>
       <c r="B132" t="n">
         <v>78616</v>
@@ -16079,22 +16082,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512108</v>
+        <v>512100</v>
       </c>
       <c r="R132" t="n">
-        <v>6733054</v>
+        <v>6733148</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16121,47 +16121,36 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Irina Röjås, Philipp Weiss, Beke Regelin</t>
+          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121423780</v>
+        <v>121425818</v>
       </c>
       <c r="B133" t="n">
         <v>78616</v>
@@ -16194,20 +16183,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512100</v>
+        <v>512221</v>
       </c>
       <c r="R133" t="n">
-        <v>6733148</v>
+        <v>6733056</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16245,28 +16245,29 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Beke Regelin, Irina Röjås, Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121425818</v>
+        <v>121426850</v>
       </c>
       <c r="B134" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16279,48 +16280,40 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512221</v>
+        <v>512216</v>
       </c>
       <c r="R134" t="n">
-        <v>6733056</v>
+        <v>6733046</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16347,9 +16340,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16365,22 +16368,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121426850</v>
+        <v>121426859</v>
       </c>
       <c r="B135" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16389,30 +16392,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -16420,10 +16428,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512216</v>
+        <v>512108</v>
       </c>
       <c r="R135" t="n">
-        <v>6733046</v>
+        <v>6733054</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16455,7 +16463,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16465,7 +16473,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16474,7 +16482,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -16493,10 +16500,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121426859</v>
+        <v>121425773</v>
       </c>
       <c r="B136" t="n">
-        <v>56569</v>
+        <v>57373</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16505,25 +16512,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16531,23 +16538,23 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>moberg, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512108</v>
+        <v>512215</v>
       </c>
       <c r="R136" t="n">
-        <v>6733054</v>
+        <v>6733081</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16574,19 +16581,14 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska märken</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16601,22 +16603,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121425773</v>
+        <v>121426851</v>
       </c>
       <c r="B137" t="n">
-        <v>57373</v>
+        <v>90966</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16629,45 +16631,48 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>moberg, Dlr</t>
+          <t>Hackmora Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512215</v>
+        <v>512219</v>
       </c>
       <c r="R137" t="n">
-        <v>6733081</v>
+        <v>6733049</v>
       </c>
       <c r="S137" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16694,14 +16699,19 @@
           <t>2024-12-01</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska märken</t>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16710,28 +16720,29 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121426851</v>
+        <v>104996307</v>
       </c>
       <c r="B138" t="n">
-        <v>90966</v>
+        <v>95672</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16740,52 +16751,45 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hackmora Moberg, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>512219</v>
+        <v>511633</v>
       </c>
       <c r="R138" t="n">
-        <v>6733049</v>
+        <v>6733072</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16809,22 +16813,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16845,17 +16849,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Philipp Weiss, Irina Röjås, Beke Regelin</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104996307</v>
+        <v>104720479</v>
       </c>
       <c r="B139" t="n">
-        <v>95672</v>
+        <v>91411</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16864,42 +16868,41 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>511633</v>
+        <v>511448</v>
       </c>
       <c r="R139" t="n">
-        <v>6733072</v>
+        <v>6733109</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16926,22 +16929,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16962,126 +16965,10 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>104720479</v>
-      </c>
-      <c r="B140" t="n">
-        <v>91411</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Leksand, Dlr</t>
-        </is>
-      </c>
-      <c r="Q140" t="n">
-        <v>511448</v>
-      </c>
-      <c r="R140" t="n">
-        <v>6733109</v>
-      </c>
-      <c r="S140" t="n">
-        <v>25</v>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AD140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="inlineStr"/>
-      <c r="AG140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT140" t="inlineStr"/>
-      <c r="AW140" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124640917</v>
+        <v>124637078</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning, tall.</t>
+          <t>Spillning.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16972,10 +16972,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124637078</v>
+        <v>124639270</v>
       </c>
       <c r="B140" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16984,25 +16984,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning.</t>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17089,10 +17089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124639270</v>
+        <v>124631910</v>
       </c>
       <c r="B141" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,16 +17105,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,12 +17174,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Spillning, rotvälta.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17206,10 +17201,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124631910</v>
+        <v>124638404</v>
       </c>
       <c r="B142" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17218,25 +17213,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17281,7 +17276,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17291,7 +17286,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Spillning.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17315,6 +17315,140 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>124642134</v>
+      </c>
+      <c r="B143" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Moberg, Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>511775</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6732970</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Gullvivor från fäbodtiden?</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,10 +16972,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124639270</v>
+        <v>124636585</v>
       </c>
       <c r="B140" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16984,25 +16984,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -17201,10 +17201,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124638404</v>
+        <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17213,25 +17213,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17286,12 +17286,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Spillning.</t>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124636585</v>
+        <v>124638227</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning, rotvälta.</t>
+          <t>Spillning. Tjädertall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124638227</v>
+        <v>124630674</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tjädertall.</t>
+          <t>Spillning. Tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17089,10 +17089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124631910</v>
+        <v>124639270</v>
       </c>
       <c r="B141" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,16 +17105,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,7 +17174,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17201,10 +17206,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124639270</v>
+        <v>124631910</v>
       </c>
       <c r="B142" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17217,16 +17222,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -17276,7 +17281,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17286,12 +17291,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Spillning, rotvälta.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124630674</v>
+        <v>124638227</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tall.</t>
+          <t>Spillning. Tjädertall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124638227</v>
+        <v>124630674</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tjädertall.</t>
+          <t>Spillning. Tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124630674</v>
+        <v>124638404</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tall.</t>
+          <t>Spillning.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17089,10 +17089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124639270</v>
+        <v>124631910</v>
       </c>
       <c r="B141" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,16 +17105,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,12 +17174,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Spillning, rotvälta.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17206,10 +17201,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124631910</v>
+        <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17222,16 +17217,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -17281,7 +17276,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17291,7 +17286,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124638404</v>
+        <v>124630674</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning.</t>
+          <t>Spillning. Tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124630674</v>
+        <v>124640917</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tall.</t>
+          <t>Spillning, tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,10 +16972,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124640917</v>
+        <v>124639270</v>
       </c>
       <c r="B140" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16984,25 +16984,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning, tall.</t>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17201,10 +17201,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124639270</v>
+        <v>124639165</v>
       </c>
       <c r="B142" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17213,25 +17213,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,10 +16972,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124639270</v>
+        <v>124639165</v>
       </c>
       <c r="B140" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16984,25 +16984,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -17089,10 +17089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124631910</v>
+        <v>124639270</v>
       </c>
       <c r="B141" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,16 +17105,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,7 +17174,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17201,10 +17206,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124639165</v>
+        <v>124631910</v>
       </c>
       <c r="B142" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17213,25 +17218,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17276,7 +17281,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17286,12 +17291,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>20:06</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Spillning, rotvälta.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124639165</v>
+        <v>124640774</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning, rotvälta.</t>
+          <t>Spillning, höjd.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124640774</v>
+        <v>124630674</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning, höjd.</t>
+          <t>Spillning. Tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,7 +16972,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124630674</v>
+        <v>124631719</v>
       </c>
       <c r="B140" t="n">
         <v>56722</v>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Spillning. Tall.</t>
+          <t>Spillning, tall.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17089,10 +17089,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124639270</v>
+        <v>124631910</v>
       </c>
       <c r="B141" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17105,16 +17105,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,12 +17174,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Spillning, rotvälta.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17206,10 +17201,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>124631910</v>
+        <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17222,16 +17217,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -17281,7 +17276,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17291,7 +17286,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Spillning, rotvälta.</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -16972,10 +16972,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124631719</v>
+        <v>124631910</v>
       </c>
       <c r="B140" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16984,25 +16984,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17057,12 +17057,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Spillning, tall.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17089,10 +17084,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124631910</v>
+        <v>124640917</v>
       </c>
       <c r="B141" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17101,25 +17096,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17164,7 +17159,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17174,7 +17169,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Spillning, tall.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17204,7 +17204,7 @@
         <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>124642134</v>
       </c>
       <c r="B143" t="n">
-        <v>105029</v>
+        <v>105205</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17450,6 +17450,1118 @@
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>123786219</v>
+      </c>
+      <c r="B144" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>511625</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6733194</v>
+      </c>
+      <c r="S144" t="n">
+        <v>15</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>småbitar 10 ev. höna  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>123786226</v>
+      </c>
+      <c r="B145" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>512033</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6733136</v>
+      </c>
+      <c r="S145" t="n">
+        <v>15</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd eftersom skogen nu är oskyddad och kan avverkas vilken dag som helst. Då ska i alla fall alla kunna se vilka naturvärden som fanns.</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>123777369</v>
+      </c>
+      <c r="B146" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>511637</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6733198</v>
+      </c>
+      <c r="S146" t="n">
+        <v>15</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>123777367</v>
+      </c>
+      <c r="B147" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>511646</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6733164</v>
+      </c>
+      <c r="S147" t="n">
+        <v>15</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>123786217</v>
+      </c>
+      <c r="B148" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>512041</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6733140</v>
+      </c>
+      <c r="S148" t="n">
+        <v>15</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd eftersom skogen nu är oskyddad och kan avverkas vilken dag som helst. Då ska i alla fall alla kunna se vilka naturvärden som fanns.</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>123777351</v>
+      </c>
+      <c r="B149" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>511641</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6733154</v>
+      </c>
+      <c r="S149" t="n">
+        <v>15</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, runt tall  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>123777363</v>
+      </c>
+      <c r="B150" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>511639</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6733159</v>
+      </c>
+      <c r="S150" t="n">
+        <v>15</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>123174265</v>
+      </c>
+      <c r="B151" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>SJÖS MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>512160</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6732982</v>
+      </c>
+      <c r="S151" t="n">
+        <v>25</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>104757748</v>
+      </c>
+      <c r="B152" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>512039</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6732944</v>
+      </c>
+      <c r="S152" t="n">
+        <v>50</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Den dagen var det inte bara jag som var i Moberg men just den här dagen var en vinterdag. Jag har sett tjädrar flera gånger i Moberg och i juni 2023 såg jag också en tjäderhanne ca 10 m från en spelplats men även det  tjädermötet anses i en dom ha skett på vintern och man ger därför inte mötet någon betydelse.  Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY152"/>
+  <dimension ref="A1:AY164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10399,12 +10399,7 @@
         <v>115538585</v>
       </c>
       <c r="B83" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10494,6 +10489,11 @@
       <c r="AB83" t="inlineStr">
         <is>
           <t>18:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10647,12 +10647,7 @@
         <v>115930127</v>
       </c>
       <c r="B85" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10742,6 +10737,11 @@
       <c r="AB85" t="inlineStr">
         <is>
           <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10771,12 +10771,7 @@
         <v>110261494</v>
       </c>
       <c r="B86" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10870,7 +10865,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Mycket vacker avverkningshotat höghöjds skog, fäbodskog.</t>
+          <t>Mycket vacker avverkningshotat höghöjds skog, fäbodskog. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10900,12 +10895,7 @@
         <v>108144601</v>
       </c>
       <c r="B87" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10999,7 +10989,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ett 50 tal spillning/ostkrokar, all spillning är inte med på bilden.</t>
+          <t>Ett 50 tal spillning/ostkrokar, all spillning är inte med på bilden. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11029,12 +11019,7 @@
         <v>120644581</v>
       </c>
       <c r="B88" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11064,11 +11049,14 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
@@ -11121,6 +11109,11 @@
       <c r="AB88" t="inlineStr">
         <is>
           <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>En äkta tjädertoa! Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11390,12 +11383,7 @@
         <v>115930630</v>
       </c>
       <c r="B91" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11485,6 +11473,11 @@
       <c r="AB91" t="inlineStr">
         <is>
           <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11764,12 +11757,7 @@
         <v>120667335</v>
       </c>
       <c r="B94" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11859,6 +11847,11 @@
       <c r="AB94" t="inlineStr">
         <is>
           <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -17204,12 +17197,7 @@
         <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17235,6 +17223,14 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Leksand Grim Moberg, Dlr</t>
@@ -17704,7 +17700,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123777369</v>
+        <v>123777367</v>
       </c>
       <c r="B146" t="n">
         <v>56844</v>
@@ -17732,12 +17728,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17747,10 +17747,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>511637</v>
+        <v>511646</v>
       </c>
       <c r="R146" t="n">
-        <v>6733198</v>
+        <v>6733164</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17792,12 +17792,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17824,7 +17824,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>123777367</v>
+        <v>123777369</v>
       </c>
       <c r="B147" t="n">
         <v>56844</v>
@@ -17852,16 +17852,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -17871,10 +17867,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>511646</v>
+        <v>511637</v>
       </c>
       <c r="R147" t="n">
-        <v>6733164</v>
+        <v>6733198</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17906,7 +17902,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17916,12 +17912,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18316,7 +18312,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>123174265</v>
+        <v>123769974</v>
       </c>
       <c r="B151" t="n">
         <v>56844</v>
@@ -18355,17 +18351,17 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>SJÖS MOBERG, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512160</v>
+        <v>511628</v>
       </c>
       <c r="R151" t="n">
-        <v>6732982</v>
+        <v>6733188</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18389,27 +18385,27 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+          <t>Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18436,7 +18432,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>104757748</v>
+        <v>126257619</v>
       </c>
       <c r="B152" t="n">
         <v>56844</v>
@@ -18465,11 +18461,7 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>hane</t>
@@ -18477,23 +18469,23 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512039</v>
+        <v>512226</v>
       </c>
       <c r="R152" t="n">
-        <v>6732944</v>
+        <v>6733021</v>
       </c>
       <c r="S152" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18517,27 +18509,27 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Den dagen var det inte bara jag som var i Moberg men just den här dagen var en vinterdag. Jag har sett tjädrar flera gånger i Moberg och i juni 2023 såg jag också en tjäderhanne ca 10 m från en spelplats men även det  tjädermötet anses i en dom ha skett på vintern och man ger därför inte mötet någon betydelse.  Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>Idag var en tjäderexpert med oss.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18557,10 +18549,1445 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>123174265</v>
+      </c>
+      <c r="B153" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>SJÖS MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>512160</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6732982</v>
+      </c>
+      <c r="S153" t="n">
+        <v>25</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>123174269</v>
+      </c>
+      <c r="B154" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Sjös Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>511885</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6733120</v>
+      </c>
+      <c r="S154" t="n">
+        <v>25</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>115930003</v>
+      </c>
+      <c r="B155" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>511716</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6733109</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Häll och myr Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>104757748</v>
+      </c>
+      <c r="B156" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Leksand, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>512039</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6732944</v>
+      </c>
+      <c r="S156" t="n">
+        <v>50</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Den dagen var det inte bara jag som var i Moberg men just den här dagen var en vinterdag. Jag har sett tjädrar flera gånger i Moberg och i juni 2023 såg jag också en tjäderhanne ca 10 m från en spelplats men även det  tjädermötet anses i en dom ha skett på vintern och man ger därför inte mötet någon betydelse.  Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>126257455</v>
+      </c>
+      <c r="B157" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>512175</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6732988</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Tjäderexpertens bedömning! slanthack på gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>126255291</v>
+      </c>
+      <c r="B158" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>512235</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6733035</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>126257518</v>
+      </c>
+      <c r="B159" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>512175</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6732988</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Oerhört vacker och vild natur! Från Moberg ser man till Falun (och man ser såklart Mobergkammen från Falun och bäst från Garves bod). Den höga höjden, branten mot öster och alla hyggen runt om i kombination med att vinden kan ta fart från flera mils avstånd gör att vinden fäller träd.</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>126252387</v>
+      </c>
+      <c r="B160" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>511636</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6733191</v>
+      </c>
+      <c r="S160" t="n">
+        <v>15</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>tjäderspillning Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>126252389</v>
+      </c>
+      <c r="B161" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>511690</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6733120</v>
+      </c>
+      <c r="S161" t="n">
+        <v>15</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>tjädergrop Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>126252394</v>
+      </c>
+      <c r="B162" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>511647</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6733135</v>
+      </c>
+      <c r="S162" t="n">
+        <v>15</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>färsk spillning tupp Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>126255379</v>
+      </c>
+      <c r="B163" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>512068</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6733079</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>126252388</v>
+      </c>
+      <c r="B164" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>511644</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6733104</v>
+      </c>
+      <c r="S164" t="n">
+        <v>15</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>tjäderspillning Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AY169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19989,6 +19989,611 @@
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>126258666</v>
+      </c>
+      <c r="B165" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>MOBERG, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>511454</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6733021</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>126258715</v>
+      </c>
+      <c r="B166" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>511573</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6732989</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>olika fläcknycklar, blåbär, tranbär, torra vitmossor, sönderkörd mark, fula körskador</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>126258662</v>
+      </c>
+      <c r="B167" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>MOBERG , Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>511330</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6733133</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>KÄRRVIOLER, MM</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>126258538</v>
+      </c>
+      <c r="B168" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>511693</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6733119</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>126258155</v>
+      </c>
+      <c r="B169" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>511458</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6733068</v>
+      </c>
+      <c r="S169" t="n">
+        <v>25</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -18556,7 +18556,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>123174265</v>
+        <v>115930003</v>
       </c>
       <c r="B153" t="n">
         <v>56844</v>
@@ -18595,17 +18595,17 @@
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>SJÖS MOBERG, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512160</v>
+        <v>511716</v>
       </c>
       <c r="R153" t="n">
-        <v>6732982</v>
+        <v>6733109</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18629,27 +18629,27 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+          <t>Häll och myr Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18676,7 +18676,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123174269</v>
+        <v>123174265</v>
       </c>
       <c r="B154" t="n">
         <v>56844</v>
@@ -18704,11 +18704,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
@@ -18719,14 +18715,14 @@
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>SJÖS MOBERG, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>511885</v>
+        <v>512160</v>
       </c>
       <c r="R154" t="n">
-        <v>6733120</v>
+        <v>6732982</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18758,7 +18754,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18768,12 +18764,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18800,7 +18796,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>115930003</v>
+        <v>123174269</v>
       </c>
       <c r="B155" t="n">
         <v>56844</v>
@@ -18828,7 +18824,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
@@ -18839,17 +18839,17 @@
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>511716</v>
+        <v>511885</v>
       </c>
       <c r="R155" t="n">
-        <v>6733109</v>
+        <v>6733120</v>
       </c>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18873,27 +18873,27 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Häll och myr Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19171,7 +19171,7 @@
         <v>126255291</v>
       </c>
       <c r="B158" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>126258666</v>
       </c>
       <c r="B165" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>126258715</v>
       </c>
       <c r="B166" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>126258662</v>
       </c>
       <c r="B167" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>126258538</v>
       </c>
       <c r="B168" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -10399,7 +10399,7 @@
         <v>115538585</v>
       </c>
       <c r="B83" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>115930127</v>
       </c>
       <c r="B85" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>110261494</v>
       </c>
       <c r="B86" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>108144601</v>
       </c>
       <c r="B87" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>120644581</v>
       </c>
       <c r="B88" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>115930630</v>
       </c>
       <c r="B91" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>120667335</v>
       </c>
       <c r="B94" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>123786219</v>
       </c>
       <c r="B144" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>123786226</v>
       </c>
       <c r="B145" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>123777367</v>
       </c>
       <c r="B146" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>123777369</v>
       </c>
       <c r="B147" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>123786217</v>
       </c>
       <c r="B148" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>123777351</v>
       </c>
       <c r="B149" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>123777363</v>
       </c>
       <c r="B150" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>123769974</v>
       </c>
       <c r="B151" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>126257619</v>
       </c>
       <c r="B152" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>115930003</v>
       </c>
       <c r="B153" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>123174265</v>
       </c>
       <c r="B154" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>123174269</v>
       </c>
       <c r="B155" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>104757748</v>
       </c>
       <c r="B156" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>126257455</v>
       </c>
       <c r="B157" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126255291</v>
       </c>
       <c r="B158" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>126257518</v>
       </c>
       <c r="B159" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>126252387</v>
       </c>
       <c r="B160" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>126252389</v>
       </c>
       <c r="B161" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19639,10 +19639,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126252394</v>
+        <v>126255379</v>
       </c>
       <c r="B162" t="n">
-        <v>56844</v>
+        <v>5176</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19650,49 +19650,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>MOBERG, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>511647</v>
+        <v>512068</v>
       </c>
       <c r="R162" t="n">
-        <v>6733135</v>
+        <v>6733079</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19721,7 +19714,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19731,12 +19724,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>färsk spillning tupp Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+          <t>Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19745,6 +19738,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19763,10 +19757,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126255379</v>
+        <v>126252394</v>
       </c>
       <c r="B163" t="n">
-        <v>5176</v>
+        <v>56848</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19774,42 +19768,49 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>MOBERG, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512068</v>
+        <v>511647</v>
       </c>
       <c r="R163" t="n">
-        <v>6733079</v>
+        <v>6733135</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19838,7 +19839,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -19848,12 +19849,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
+          <t>färsk spillning tupp Den här dagen hade vi en tjäderexpert med oss. Jag hade aldrig tänkt lägga in några bilder från detta besök och därför tog jag inte perfekta bilder men nu när avverkningshotet har ökat och ingen art överlever en kalhuggning så nu lägger jag ut så många fynd jag hinner. Det ska vara tydligt hur värdefull denna skog är som är som skog!</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19862,7 +19863,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19884,7 +19884,7 @@
         <v>126252388</v>
       </c>
       <c r="B164" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>126258666</v>
       </c>
       <c r="B165" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>126258715</v>
       </c>
       <c r="B166" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>126258662</v>
       </c>
       <c r="B167" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>126258538</v>
       </c>
       <c r="B168" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>126258155</v>
       </c>
       <c r="B169" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -18676,7 +18676,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123174265</v>
+        <v>123174269</v>
       </c>
       <c r="B154" t="n">
         <v>56848</v>
@@ -18704,7 +18704,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
@@ -18715,14 +18719,14 @@
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>SJÖS MOBERG, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512160</v>
+        <v>511885</v>
       </c>
       <c r="R154" t="n">
-        <v>6732982</v>
+        <v>6733120</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18754,7 +18758,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18764,12 +18768,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18796,7 +18800,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123174269</v>
+        <v>123174265</v>
       </c>
       <c r="B155" t="n">
         <v>56848</v>
@@ -18824,11 +18828,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
@@ -18839,14 +18839,14 @@
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>SJÖS MOBERG, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>511885</v>
+        <v>512160</v>
       </c>
       <c r="R155" t="n">
-        <v>6733120</v>
+        <v>6732982</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18888,12 +18888,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19994,7 +19994,7 @@
         <v>126258666</v>
       </c>
       <c r="B165" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>126258715</v>
       </c>
       <c r="B166" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>126258662</v>
       </c>
       <c r="B167" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>126258538</v>
       </c>
       <c r="B168" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -18676,7 +18676,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123174269</v>
+        <v>123174265</v>
       </c>
       <c r="B154" t="n">
         <v>56848</v>
@@ -18704,11 +18704,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
@@ -18719,14 +18715,14 @@
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>SJÖS MOBERG, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>511885</v>
+        <v>512160</v>
       </c>
       <c r="R154" t="n">
-        <v>6733120</v>
+        <v>6732982</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18758,7 +18754,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18768,12 +18764,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18800,7 +18796,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123174265</v>
+        <v>123174269</v>
       </c>
       <c r="B155" t="n">
         <v>56848</v>
@@ -18828,7 +18824,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
@@ -18839,14 +18839,14 @@
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>SJÖS MOBERG, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>512160</v>
+        <v>511885</v>
       </c>
       <c r="R155" t="n">
-        <v>6732982</v>
+        <v>6733120</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18888,12 +18888,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.  Dock kommer inte spelplats att synas.</t>
+          <t>Sovträd! Minst 150 "ostkrokar" spridda runt i riset och mossa Den här dagen hade vi en tjäderexpert med oss. Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD155" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -17700,7 +17700,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123777367</v>
+        <v>123777369</v>
       </c>
       <c r="B146" t="n">
         <v>56848</v>
@@ -17728,16 +17728,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17747,10 +17743,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>511646</v>
+        <v>511637</v>
       </c>
       <c r="R146" t="n">
-        <v>6733164</v>
+        <v>6733198</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -17782,7 +17778,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17792,12 +17788,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17824,7 +17820,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>123777369</v>
+        <v>123777367</v>
       </c>
       <c r="B147" t="n">
         <v>56848</v>
@@ -17852,12 +17848,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>511637</v>
+        <v>511646</v>
       </c>
       <c r="R147" t="n">
-        <v>6733198</v>
+        <v>6733164</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17912,12 +17912,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -10399,7 +10399,7 @@
         <v>115538585</v>
       </c>
       <c r="B83" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>115930127</v>
       </c>
       <c r="B85" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>110261494</v>
       </c>
       <c r="B86" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>108144601</v>
       </c>
       <c r="B87" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>120644581</v>
       </c>
       <c r="B88" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>115930630</v>
       </c>
       <c r="B91" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>120667335</v>
       </c>
       <c r="B94" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>124639270</v>
       </c>
       <c r="B142" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>123786219</v>
       </c>
       <c r="B144" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>123786226</v>
       </c>
       <c r="B145" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17700,10 +17700,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123777369</v>
+        <v>123777367</v>
       </c>
       <c r="B146" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17728,12 +17728,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17743,10 +17747,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>511637</v>
+        <v>511646</v>
       </c>
       <c r="R146" t="n">
-        <v>6733198</v>
+        <v>6733164</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -17778,7 +17782,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17788,12 +17792,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17820,10 +17824,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>123777367</v>
+        <v>123777369</v>
       </c>
       <c r="B147" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17848,16 +17852,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>511646</v>
+        <v>511637</v>
       </c>
       <c r="R147" t="n">
-        <v>6733164</v>
+        <v>6733198</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17912,12 +17912,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17947,7 +17947,7 @@
         <v>123786217</v>
       </c>
       <c r="B148" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>123777351</v>
       </c>
       <c r="B149" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>123777363</v>
       </c>
       <c r="B150" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>123769974</v>
       </c>
       <c r="B151" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>126257619</v>
       </c>
       <c r="B152" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>115930003</v>
       </c>
       <c r="B153" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>123174265</v>
       </c>
       <c r="B154" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>123174269</v>
       </c>
       <c r="B155" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>104757748</v>
       </c>
       <c r="B156" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>126257455</v>
       </c>
       <c r="B157" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19171,7 +19171,7 @@
         <v>126255291</v>
       </c>
       <c r="B158" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>126257518</v>
       </c>
       <c r="B159" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>126252387</v>
       </c>
       <c r="B160" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>126252389</v>
       </c>
       <c r="B161" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>126252394</v>
       </c>
       <c r="B163" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>126252388</v>
       </c>
       <c r="B164" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>126258666</v>
       </c>
       <c r="B165" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>126258715</v>
       </c>
       <c r="B166" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>126258662</v>
       </c>
       <c r="B167" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>126258538</v>
       </c>
       <c r="B168" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>126258155</v>
       </c>
       <c r="B169" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -11009,7 +11009,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -17700,7 +17700,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123777367</v>
+        <v>123777369</v>
       </c>
       <c r="B146" t="n">
         <v>56849</v>
@@ -17728,16 +17728,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17747,10 +17743,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>511646</v>
+        <v>511637</v>
       </c>
       <c r="R146" t="n">
-        <v>6733164</v>
+        <v>6733198</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -17782,7 +17778,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17792,12 +17788,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17824,7 +17820,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>123777369</v>
+        <v>123777367</v>
       </c>
       <c r="B147" t="n">
         <v>56849</v>
@@ -17852,12 +17848,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>511637</v>
+        <v>511646</v>
       </c>
       <c r="R147" t="n">
-        <v>6733198</v>
+        <v>6733164</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17912,12 +17912,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
+          <t>större och mindre,  Jag släpper ca 100 dolda fynd som bara SKS har kunnat se eftersom skogen nu är oskyddad. När den avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades.</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY169"/>
+  <dimension ref="A1:AY173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20594,6 +20594,439 @@
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>126596967</v>
+      </c>
+      <c r="B170" t="n">
+        <v>58516</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>511879</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6732860</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>126594614</v>
+      </c>
+      <c r="B171" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>511943</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6732930</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>126590737</v>
+      </c>
+      <c r="B172" t="n">
+        <v>58516</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>511976</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6732961</v>
+      </c>
+      <c r="S172" t="n">
+        <v>2</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>126594931</v>
+      </c>
+      <c r="B173" t="n">
+        <v>58516</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>511948</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6732957</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -20596,10 +20596,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126596967</v>
+        <v>126594614</v>
       </c>
       <c r="B170" t="n">
-        <v>58516</v>
+        <v>56849</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20607,16 +20607,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>511879</v>
+        <v>511943</v>
       </c>
       <c r="R170" t="n">
-        <v>6732860</v>
+        <v>6732930</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20676,7 +20676,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20703,10 +20708,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126594614</v>
+        <v>126596967</v>
       </c>
       <c r="B171" t="n">
-        <v>56849</v>
+        <v>58516</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20714,16 +20719,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100138</v>
+        <v>208249</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -20738,13 +20743,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>511943</v>
+        <v>511879</v>
       </c>
       <c r="R171" t="n">
-        <v>6732930</v>
+        <v>6732860</v>
       </c>
       <c r="S171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20773,7 +20778,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20783,12 +20788,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Fjäder.</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD171" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -20596,10 +20596,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126596967</v>
+        <v>126594614</v>
       </c>
       <c r="B170" t="n">
-        <v>58516</v>
+        <v>56849</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20607,16 +20607,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>511879</v>
+        <v>511943</v>
       </c>
       <c r="R170" t="n">
-        <v>6732860</v>
+        <v>6732930</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20676,7 +20676,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20703,10 +20708,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126594614</v>
+        <v>126596967</v>
       </c>
       <c r="B171" t="n">
-        <v>56849</v>
+        <v>58516</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20714,16 +20719,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100138</v>
+        <v>208249</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -20738,13 +20743,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>511943</v>
+        <v>511879</v>
       </c>
       <c r="R171" t="n">
-        <v>6732930</v>
+        <v>6732860</v>
       </c>
       <c r="S171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20773,7 +20778,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20783,12 +20788,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Fjäder.</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21032,7 +21032,7 @@
         <v>126591562</v>
       </c>
       <c r="B174" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -21143,7 +21143,7 @@
         <v>126595944</v>
       </c>
       <c r="B175" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -21256,7 +21256,7 @@
         <v>126590847</v>
       </c>
       <c r="B176" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -21375,7 +21375,7 @@
         <v>126597287</v>
       </c>
       <c r="B177" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -21595,7 +21595,7 @@
         <v>126596924</v>
       </c>
       <c r="B179" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -21708,7 +21708,7 @@
         <v>126594826</v>
       </c>
       <c r="B180" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>126596172</v>
       </c>
       <c r="B181" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -21929,7 +21929,7 @@
         <v>126596593</v>
       </c>
       <c r="B182" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -22509,7 +22509,7 @@
         <v>126596554</v>
       </c>
       <c r="B187" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
@@ -22753,7 +22753,7 @@
         <v>126688780</v>
       </c>
       <c r="B189" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -24044,10 +24044,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127085356</v>
+        <v>127085156</v>
       </c>
       <c r="B200" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24055,34 +24055,39 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>511487</v>
+        <v>511571</v>
       </c>
       <c r="R200" t="n">
-        <v>6733143</v>
+        <v>6733063</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24115,6 +24120,11 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24141,10 +24151,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127085429</v>
+        <v>127085145</v>
       </c>
       <c r="B201" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24152,34 +24162,39 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>512205</v>
+        <v>511991</v>
       </c>
       <c r="R201" t="n">
-        <v>6733078</v>
+        <v>6732936</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24212,6 +24227,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24238,10 +24258,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127085380</v>
+        <v>127085356</v>
       </c>
       <c r="B202" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24273,10 +24293,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>511665</v>
+        <v>511487</v>
       </c>
       <c r="R202" t="n">
-        <v>6732780</v>
+        <v>6733143</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24338,7 +24358,7 @@
         <v>127085438</v>
       </c>
       <c r="B203" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24432,50 +24452,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127085145</v>
+        <v>127085105</v>
       </c>
       <c r="B204" t="n">
-        <v>57657</v>
+        <v>91284</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>511991</v>
+        <v>512122</v>
       </c>
       <c r="R204" t="n">
-        <v>6732936</v>
+        <v>6733004</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24508,11 +24523,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24539,10 +24549,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127085156</v>
+        <v>127085380</v>
       </c>
       <c r="B205" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24550,39 +24560,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>511571</v>
+        <v>511665</v>
       </c>
       <c r="R205" t="n">
-        <v>6733063</v>
+        <v>6732780</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24615,11 +24620,6 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24646,32 +24646,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127085105</v>
+        <v>127085429</v>
       </c>
       <c r="B206" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -24681,10 +24681,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>512122</v>
+        <v>512205</v>
       </c>
       <c r="R206" t="n">
-        <v>6733004</v>
+        <v>6733078</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24743,10 +24743,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127085192</v>
+        <v>127085154</v>
       </c>
       <c r="B207" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24754,16 +24754,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -24774,7 +24774,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -24783,10 +24783,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>512240</v>
+        <v>512098</v>
       </c>
       <c r="R207" t="n">
-        <v>6733130</v>
+        <v>6733172</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24819,6 +24819,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24845,10 +24850,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127085426</v>
+        <v>127085357</v>
       </c>
       <c r="B208" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24880,10 +24885,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>512214</v>
+        <v>511531</v>
       </c>
       <c r="R208" t="n">
-        <v>6733017</v>
+        <v>6733158</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24942,10 +24947,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127085204</v>
+        <v>127085426</v>
       </c>
       <c r="B209" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24953,39 +24958,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>511872</v>
+        <v>512214</v>
       </c>
       <c r="R209" t="n">
-        <v>6732834</v>
+        <v>6733017</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25044,10 +25044,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127085357</v>
+        <v>127085204</v>
       </c>
       <c r="B210" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25055,34 +25055,39 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>511531</v>
+        <v>511872</v>
       </c>
       <c r="R210" t="n">
-        <v>6733158</v>
+        <v>6732834</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25141,10 +25146,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127085154</v>
+        <v>127085192</v>
       </c>
       <c r="B211" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25152,16 +25157,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25172,7 +25177,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -25181,10 +25186,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>512098</v>
+        <v>512240</v>
       </c>
       <c r="R211" t="n">
-        <v>6733172</v>
+        <v>6733130</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25217,11 +25222,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25248,7 +25248,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127085198</v>
+        <v>127085196</v>
       </c>
       <c r="B212" t="n">
         <v>57654</v>
@@ -25288,10 +25288,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>511652</v>
+        <v>511574</v>
       </c>
       <c r="R212" t="n">
-        <v>6732988</v>
+        <v>6733042</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25350,45 +25350,54 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127085350</v>
+        <v>127085168</v>
       </c>
       <c r="B213" t="n">
-        <v>78980</v>
+        <v>4772</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>511648</v>
+        <v>511692</v>
       </c>
       <c r="R213" t="n">
-        <v>6733131</v>
+        <v>6732762</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25429,6 +25438,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -25447,7 +25457,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127085196</v>
+        <v>127085198</v>
       </c>
       <c r="B214" t="n">
         <v>57654</v>
@@ -25487,10 +25497,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>511574</v>
+        <v>511652</v>
       </c>
       <c r="R214" t="n">
-        <v>6733042</v>
+        <v>6732988</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25549,10 +25559,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127085353</v>
+        <v>127085149</v>
       </c>
       <c r="B215" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25560,34 +25570,39 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>511443</v>
+        <v>512180</v>
       </c>
       <c r="R215" t="n">
-        <v>6733122</v>
+        <v>6733152</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25620,6 +25635,11 @@
       <c r="AA215" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25646,10 +25666,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127085149</v>
+        <v>127085350</v>
       </c>
       <c r="B216" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25657,39 +25677,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>512180</v>
+        <v>511648</v>
       </c>
       <c r="R216" t="n">
-        <v>6733152</v>
+        <v>6733131</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25722,11 +25737,6 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25753,54 +25763,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127085168</v>
+        <v>127085353</v>
       </c>
       <c r="B217" t="n">
-        <v>4772</v>
+        <v>79011</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>511692</v>
+        <v>511443</v>
       </c>
       <c r="R217" t="n">
-        <v>6732762</v>
+        <v>6733122</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25841,7 +25842,6 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -25863,7 +25863,7 @@
         <v>127085431</v>
       </c>
       <c r="B218" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>127085347</v>
       </c>
       <c r="B219" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26054,32 +26054,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127085175</v>
+        <v>127085420</v>
       </c>
       <c r="B220" t="n">
-        <v>92180</v>
+        <v>79011</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -26089,10 +26089,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>511428</v>
+        <v>512122</v>
       </c>
       <c r="R220" t="n">
-        <v>6733130</v>
+        <v>6733004</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26151,32 +26151,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127085420</v>
+        <v>127085175</v>
       </c>
       <c r="B221" t="n">
-        <v>78980</v>
+        <v>92254</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -26186,10 +26186,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>512122</v>
+        <v>511428</v>
       </c>
       <c r="R221" t="n">
-        <v>6733004</v>
+        <v>6733130</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26248,59 +26248,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127085269</v>
+        <v>127085358</v>
       </c>
       <c r="B222" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>512131</v>
+        <v>511490</v>
       </c>
       <c r="R222" t="n">
-        <v>6733255</v>
+        <v>6733157</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26359,10 +26345,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127085358</v>
+        <v>127085351</v>
       </c>
       <c r="B223" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26394,10 +26380,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>511490</v>
+        <v>511657</v>
       </c>
       <c r="R223" t="n">
-        <v>6733157</v>
+        <v>6733151</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26456,45 +26442,50 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127085351</v>
+        <v>127085082</v>
       </c>
       <c r="B224" t="n">
-        <v>78980</v>
+        <v>5196</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>511657</v>
+        <v>512165</v>
       </c>
       <c r="R224" t="n">
-        <v>6733151</v>
+        <v>6733149</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26553,10 +26544,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127085131</v>
+        <v>127085133</v>
       </c>
       <c r="B225" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26588,10 +26579,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>512090</v>
+        <v>512166</v>
       </c>
       <c r="R225" t="n">
-        <v>6733122</v>
+        <v>6733144</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26650,10 +26641,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127085133</v>
+        <v>127085131</v>
       </c>
       <c r="B226" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26685,10 +26676,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>512166</v>
+        <v>512090</v>
       </c>
       <c r="R226" t="n">
-        <v>6733144</v>
+        <v>6733122</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26747,50 +26738,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127085082</v>
+        <v>127085134</v>
       </c>
       <c r="B227" t="n">
-        <v>5196</v>
+        <v>91319</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>512165</v>
+        <v>512215</v>
       </c>
       <c r="R227" t="n">
-        <v>6733149</v>
+        <v>6733164</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26849,45 +26835,59 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127085134</v>
+        <v>127085269</v>
       </c>
       <c r="B228" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>512215</v>
+        <v>512131</v>
       </c>
       <c r="R228" t="n">
-        <v>6733164</v>
+        <v>6733255</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26946,32 +26946,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127085428</v>
+        <v>127085102</v>
       </c>
       <c r="B229" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26981,10 +26981,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>512217</v>
+        <v>511825</v>
       </c>
       <c r="R229" t="n">
-        <v>6733093</v>
+        <v>6732811</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27043,10 +27043,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127085256</v>
+        <v>127085379</v>
       </c>
       <c r="B230" t="n">
-        <v>91718</v>
+        <v>79011</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27054,21 +27054,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -27078,10 +27078,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>512114</v>
+        <v>511665</v>
       </c>
       <c r="R230" t="n">
-        <v>6733092</v>
+        <v>6732789</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27140,10 +27140,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127085379</v>
+        <v>127085256</v>
       </c>
       <c r="B231" t="n">
-        <v>78980</v>
+        <v>91792</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27151,21 +27151,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -27175,10 +27175,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>511665</v>
+        <v>512114</v>
       </c>
       <c r="R231" t="n">
-        <v>6732789</v>
+        <v>6733092</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27240,7 +27240,7 @@
         <v>127085366</v>
       </c>
       <c r="B232" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>127085338</v>
       </c>
       <c r="B233" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27431,10 +27431,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127085255</v>
+        <v>127085348</v>
       </c>
       <c r="B234" t="n">
-        <v>91652</v>
+        <v>79011</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27442,16 +27442,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -27461,10 +27466,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>512240</v>
+        <v>511691</v>
       </c>
       <c r="R234" t="n">
-        <v>6733098</v>
+        <v>6733100</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27523,10 +27528,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127085348</v>
+        <v>127085428</v>
       </c>
       <c r="B235" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27558,10 +27563,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>511691</v>
+        <v>512217</v>
       </c>
       <c r="R235" t="n">
-        <v>6733100</v>
+        <v>6733093</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27620,32 +27625,27 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127085102</v>
+        <v>127085255</v>
       </c>
       <c r="B236" t="n">
-        <v>91210</v>
+        <v>91726</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -27655,10 +27655,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>511825</v>
+        <v>512240</v>
       </c>
       <c r="R236" t="n">
-        <v>6732811</v>
+        <v>6733098</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27717,45 +27717,50 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127085390</v>
+        <v>127085080</v>
       </c>
       <c r="B237" t="n">
-        <v>78980</v>
+        <v>5196</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>512008</v>
+        <v>512226</v>
       </c>
       <c r="R237" t="n">
-        <v>6732919</v>
+        <v>6733157</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27817,7 +27822,7 @@
         <v>127085441</v>
       </c>
       <c r="B238" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27911,10 +27916,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127085278</v>
+        <v>127085127</v>
       </c>
       <c r="B239" t="n">
-        <v>91470</v>
+        <v>91319</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27922,21 +27927,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -27946,10 +27951,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>512146</v>
+        <v>511987</v>
       </c>
       <c r="R239" t="n">
-        <v>6733140</v>
+        <v>6732947</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28008,50 +28013,45 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127085458</v>
+        <v>127085125</v>
       </c>
       <c r="B240" t="n">
-        <v>5176</v>
+        <v>91319</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>512072</v>
+        <v>512223</v>
       </c>
       <c r="R240" t="n">
-        <v>6733076</v>
+        <v>6733163</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28110,10 +28110,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127085436</v>
+        <v>127085278</v>
       </c>
       <c r="B241" t="n">
-        <v>78980</v>
+        <v>91544</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28121,21 +28121,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>1101</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -28145,10 +28145,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>512103</v>
+        <v>512146</v>
       </c>
       <c r="R241" t="n">
-        <v>6733103</v>
+        <v>6733140</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28207,59 +28207,45 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127085266</v>
+        <v>127085430</v>
       </c>
       <c r="B242" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>511616</v>
+        <v>512198</v>
       </c>
       <c r="R242" t="n">
-        <v>6733018</v>
+        <v>6733079</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28292,11 +28278,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28323,10 +28304,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127085430</v>
+        <v>127085436</v>
       </c>
       <c r="B243" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28358,10 +28339,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>512198</v>
+        <v>512103</v>
       </c>
       <c r="R243" t="n">
-        <v>6733079</v>
+        <v>6733103</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28420,10 +28401,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127085459</v>
+        <v>127085107</v>
       </c>
       <c r="B244" t="n">
-        <v>5176</v>
+        <v>91284</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28431,39 +28412,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>512124</v>
+        <v>512190</v>
       </c>
       <c r="R244" t="n">
-        <v>6733193</v>
+        <v>6733157</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28522,10 +28498,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127085427</v>
+        <v>127085390</v>
       </c>
       <c r="B245" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28557,10 +28533,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>512225</v>
+        <v>512008</v>
       </c>
       <c r="R245" t="n">
-        <v>6733108</v>
+        <v>6732919</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28619,54 +28595,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127085169</v>
+        <v>127085427</v>
       </c>
       <c r="B246" t="n">
-        <v>4772</v>
+        <v>79011</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>512072</v>
+        <v>512225</v>
       </c>
       <c r="R246" t="n">
-        <v>6733076</v>
+        <v>6733108</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28707,7 +28674,6 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -28726,10 +28692,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127085080</v>
+        <v>127085458</v>
       </c>
       <c r="B247" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28737,27 +28703,27 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28766,10 +28732,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>512226</v>
+        <v>512072</v>
       </c>
       <c r="R247" t="n">
-        <v>6733157</v>
+        <v>6733076</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28828,45 +28794,50 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127085125</v>
+        <v>127085459</v>
       </c>
       <c r="B248" t="n">
-        <v>91245</v>
+        <v>5176</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>512223</v>
+        <v>512124</v>
       </c>
       <c r="R248" t="n">
-        <v>6733163</v>
+        <v>6733193</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28925,45 +28896,54 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127085127</v>
+        <v>127085169</v>
       </c>
       <c r="B249" t="n">
-        <v>91245</v>
+        <v>4772</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>511987</v>
+        <v>512072</v>
       </c>
       <c r="R249" t="n">
-        <v>6732947</v>
+        <v>6733076</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29004,6 +28984,7 @@
       <c r="AE249" t="b">
         <v>0</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -29022,45 +29003,59 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127085107</v>
+        <v>127085266</v>
       </c>
       <c r="B250" t="n">
-        <v>91210</v>
+        <v>98436</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>512190</v>
+        <v>511616</v>
       </c>
       <c r="R250" t="n">
-        <v>6733157</v>
+        <v>6733018</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29093,6 +29088,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29119,10 +29119,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127085373</v>
+        <v>127085132</v>
       </c>
       <c r="B251" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29130,21 +29130,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -29154,10 +29154,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>511572</v>
+        <v>512170</v>
       </c>
       <c r="R251" t="n">
-        <v>6733106</v>
+        <v>6733213</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29216,10 +29216,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127085432</v>
+        <v>127085373</v>
       </c>
       <c r="B252" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29251,10 +29251,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>512143</v>
+        <v>511572</v>
       </c>
       <c r="R252" t="n">
-        <v>6733060</v>
+        <v>6733106</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29313,10 +29313,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127085132</v>
+        <v>127085432</v>
       </c>
       <c r="B253" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29324,21 +29324,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -29348,10 +29348,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>512170</v>
+        <v>512143</v>
       </c>
       <c r="R253" t="n">
-        <v>6733213</v>
+        <v>6733060</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29410,7 +29410,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127085158</v>
+        <v>127085153</v>
       </c>
       <c r="B254" t="n">
         <v>57657</v>
@@ -29450,10 +29450,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>512000</v>
+        <v>511379</v>
       </c>
       <c r="R254" t="n">
-        <v>6732919</v>
+        <v>6733133</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29490,7 +29490,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Troliga spår efter födosök</t>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29517,7 +29517,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127085153</v>
+        <v>127085158</v>
       </c>
       <c r="B255" t="n">
         <v>57657</v>
@@ -29557,10 +29557,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>511379</v>
+        <v>512000</v>
       </c>
       <c r="R255" t="n">
-        <v>6733133</v>
+        <v>6732919</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29731,50 +29731,45 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127085206</v>
+        <v>127085221</v>
       </c>
       <c r="B257" t="n">
-        <v>57654</v>
+        <v>91773</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>512152</v>
+        <v>512146</v>
       </c>
       <c r="R257" t="n">
-        <v>6733134</v>
+        <v>6733146</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29833,10 +29828,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127085382</v>
+        <v>127085152</v>
       </c>
       <c r="B258" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29844,34 +29839,39 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>511938</v>
+        <v>511598</v>
       </c>
       <c r="R258" t="n">
-        <v>6732856</v>
+        <v>6733104</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29904,6 +29904,11 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29930,45 +29935,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127085221</v>
+        <v>127085148</v>
       </c>
       <c r="B259" t="n">
-        <v>91699</v>
+        <v>57657</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>512146</v>
+        <v>512064</v>
       </c>
       <c r="R259" t="n">
-        <v>6733146</v>
+        <v>6733117</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30001,6 +30011,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30030,7 +30045,7 @@
         <v>127085397</v>
       </c>
       <c r="B260" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30124,10 +30139,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127085152</v>
+        <v>127085382</v>
       </c>
       <c r="B261" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30135,39 +30150,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>511598</v>
+        <v>511938</v>
       </c>
       <c r="R261" t="n">
-        <v>6733104</v>
+        <v>6732856</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30200,11 +30210,6 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30231,10 +30236,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127085148</v>
+        <v>127085206</v>
       </c>
       <c r="B262" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30242,16 +30247,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -30262,7 +30267,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -30271,10 +30276,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>512064</v>
+        <v>512152</v>
       </c>
       <c r="R262" t="n">
-        <v>6733117</v>
+        <v>6733134</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30307,11 +30312,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30338,10 +30338,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127085370</v>
+        <v>127085092</v>
       </c>
       <c r="B263" t="n">
-        <v>78980</v>
+        <v>79043</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30349,21 +30349,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -30373,10 +30373,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>511551</v>
+        <v>512081</v>
       </c>
       <c r="R263" t="n">
-        <v>6733097</v>
+        <v>6733224</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30435,10 +30435,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127085394</v>
+        <v>127085360</v>
       </c>
       <c r="B264" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30470,10 +30470,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>511981</v>
+        <v>511493</v>
       </c>
       <c r="R264" t="n">
-        <v>6732975</v>
+        <v>6733172</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30532,10 +30532,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127085381</v>
+        <v>127085434</v>
       </c>
       <c r="B265" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30567,10 +30567,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>511930</v>
+        <v>512138</v>
       </c>
       <c r="R265" t="n">
-        <v>6732852</v>
+        <v>6733072</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30629,10 +30629,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127085360</v>
+        <v>127085394</v>
       </c>
       <c r="B266" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30664,10 +30664,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>511493</v>
+        <v>511981</v>
       </c>
       <c r="R266" t="n">
-        <v>6733172</v>
+        <v>6732975</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30726,10 +30726,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127085434</v>
+        <v>127085381</v>
       </c>
       <c r="B267" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -30761,10 +30761,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>512138</v>
+        <v>511930</v>
       </c>
       <c r="R267" t="n">
-        <v>6733072</v>
+        <v>6732852</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30823,50 +30823,45 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127085203</v>
+        <v>127085101</v>
       </c>
       <c r="B268" t="n">
-        <v>57654</v>
+        <v>91284</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P268" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>511657</v>
+        <v>511664</v>
       </c>
       <c r="R268" t="n">
-        <v>6732987</v>
+        <v>6732778</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30925,32 +30920,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127085101</v>
+        <v>127085370</v>
       </c>
       <c r="B269" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -30960,10 +30955,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>511664</v>
+        <v>511551</v>
       </c>
       <c r="R269" t="n">
-        <v>6732778</v>
+        <v>6733097</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31022,10 +31017,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127085147</v>
+        <v>127085203</v>
       </c>
       <c r="B270" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31033,16 +31028,16 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -31053,7 +31048,7 @@
       <c r="I270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -31062,10 +31057,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>512035</v>
+        <v>511657</v>
       </c>
       <c r="R270" t="n">
-        <v>6732916</v>
+        <v>6732987</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31098,11 +31093,6 @@
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31129,10 +31119,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>127085092</v>
+        <v>127085147</v>
       </c>
       <c r="B271" t="n">
-        <v>79012</v>
+        <v>57657</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31140,34 +31130,39 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>512081</v>
+        <v>512035</v>
       </c>
       <c r="R271" t="n">
-        <v>6733224</v>
+        <v>6732916</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31200,6 +31195,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31333,45 +31333,50 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127085220</v>
+        <v>127085084</v>
       </c>
       <c r="B273" t="n">
-        <v>91699</v>
+        <v>5196</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>512044</v>
+        <v>512162</v>
       </c>
       <c r="R273" t="n">
-        <v>6732937</v>
+        <v>6733053</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31430,45 +31435,54 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127085400</v>
+        <v>127085135</v>
       </c>
       <c r="B274" t="n">
-        <v>78980</v>
+        <v>98459</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>512064</v>
+        <v>511795</v>
       </c>
       <c r="R274" t="n">
-        <v>6733119</v>
+        <v>6732846</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31527,32 +31541,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>127085378</v>
+        <v>127085220</v>
       </c>
       <c r="B275" t="n">
-        <v>78980</v>
+        <v>91773</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31562,10 +31576,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>511688</v>
+        <v>512044</v>
       </c>
       <c r="R275" t="n">
-        <v>6733025</v>
+        <v>6732937</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31624,54 +31638,45 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>127085135</v>
+        <v>127085400</v>
       </c>
       <c r="B276" t="n">
-        <v>98384</v>
+        <v>79011</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>511795</v>
+        <v>512064</v>
       </c>
       <c r="R276" t="n">
-        <v>6732846</v>
+        <v>6733119</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31730,10 +31735,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127085150</v>
+        <v>127085378</v>
       </c>
       <c r="B277" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31741,39 +31746,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>512042</v>
+        <v>511688</v>
       </c>
       <c r="R277" t="n">
-        <v>6732932</v>
+        <v>6733025</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31806,11 +31806,6 @@
       <c r="AA277" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31837,10 +31832,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127085084</v>
+        <v>127085095</v>
       </c>
       <c r="B278" t="n">
-        <v>5196</v>
+        <v>91284</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31848,39 +31843,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>512162</v>
+        <v>512236</v>
       </c>
       <c r="R278" t="n">
-        <v>6733053</v>
+        <v>6733047</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31939,45 +31929,50 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>127085095</v>
+        <v>127085150</v>
       </c>
       <c r="B279" t="n">
-        <v>91210</v>
+        <v>57657</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>512236</v>
+        <v>512042</v>
       </c>
       <c r="R279" t="n">
-        <v>6733047</v>
+        <v>6732932</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32010,6 +32005,11 @@
       <c r="AA279" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32036,32 +32036,32 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127085372</v>
+        <v>127085439</v>
       </c>
       <c r="B280" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32071,10 +32071,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>511560</v>
+        <v>511871</v>
       </c>
       <c r="R280" t="n">
-        <v>6733087</v>
+        <v>6732830</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32133,10 +32133,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127085424</v>
+        <v>127085254</v>
       </c>
       <c r="B281" t="n">
-        <v>78980</v>
+        <v>91726</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32144,21 +32144,16 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -32168,10 +32163,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>512144</v>
+        <v>512201</v>
       </c>
       <c r="R281" t="n">
-        <v>6733010</v>
+        <v>6733180</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32230,10 +32225,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>127085396</v>
+        <v>127085354</v>
       </c>
       <c r="B282" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32265,10 +32260,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>512072</v>
+        <v>511469</v>
       </c>
       <c r="R282" t="n">
-        <v>6733073</v>
+        <v>6733119</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -32327,10 +32322,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127085398</v>
+        <v>127085396</v>
       </c>
       <c r="B283" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32362,10 +32357,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>512062</v>
+        <v>512072</v>
       </c>
       <c r="R283" t="n">
-        <v>6733087</v>
+        <v>6733073</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32424,32 +32419,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>127085402</v>
+        <v>127085106</v>
       </c>
       <c r="B284" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -32459,10 +32454,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>512044</v>
+        <v>512184</v>
       </c>
       <c r="R284" t="n">
-        <v>6733119</v>
+        <v>6733202</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32521,32 +32516,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127085439</v>
+        <v>127085372</v>
       </c>
       <c r="B285" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -32556,10 +32551,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>511871</v>
+        <v>511560</v>
       </c>
       <c r="R285" t="n">
-        <v>6732830</v>
+        <v>6733087</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32618,10 +32613,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>127085254</v>
+        <v>127085402</v>
       </c>
       <c r="B286" t="n">
-        <v>91652</v>
+        <v>79011</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32629,16 +32624,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -32648,10 +32648,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>512201</v>
+        <v>512044</v>
       </c>
       <c r="R286" t="n">
-        <v>6733180</v>
+        <v>6733119</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32710,10 +32710,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>127085354</v>
+        <v>127085398</v>
       </c>
       <c r="B287" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32745,10 +32745,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>511469</v>
+        <v>512062</v>
       </c>
       <c r="R287" t="n">
-        <v>6733119</v>
+        <v>6733087</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32807,50 +32807,45 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>127085457</v>
+        <v>127085424</v>
       </c>
       <c r="B288" t="n">
-        <v>5176</v>
+        <v>79011</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P288" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>511991</v>
+        <v>512144</v>
       </c>
       <c r="R288" t="n">
-        <v>6732947</v>
+        <v>6733010</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32909,45 +32904,50 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>127085106</v>
+        <v>127085157</v>
       </c>
       <c r="B289" t="n">
-        <v>91210</v>
+        <v>57657</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>512184</v>
+        <v>511525</v>
       </c>
       <c r="R289" t="n">
-        <v>6733202</v>
+        <v>6732923</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32980,6 +32980,11 @@
       <c r="AA289" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -33113,38 +33118,38 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>127085157</v>
+        <v>127085457</v>
       </c>
       <c r="B291" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -33153,10 +33158,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>511525</v>
+        <v>511991</v>
       </c>
       <c r="R291" t="n">
-        <v>6732923</v>
+        <v>6732947</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -33189,11 +33194,6 @@
       <c r="AA291" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -33223,7 +33223,7 @@
         <v>127085257</v>
       </c>
       <c r="B292" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -33326,10 +33326,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>127085371</v>
+        <v>127085440</v>
       </c>
       <c r="B293" t="n">
-        <v>78980</v>
+        <v>57578</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -33337,34 +33337,39 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P293" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>511560</v>
+        <v>511689</v>
       </c>
       <c r="R293" t="n">
-        <v>6733100</v>
+        <v>6733024</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -33423,10 +33428,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>127085423</v>
+        <v>127085377</v>
       </c>
       <c r="B294" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33458,10 +33463,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>512135</v>
+        <v>511609</v>
       </c>
       <c r="R294" t="n">
-        <v>6733010</v>
+        <v>6733076</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -33520,10 +33525,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>127085377</v>
+        <v>127085399</v>
       </c>
       <c r="B295" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33555,10 +33560,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>511609</v>
+        <v>512061</v>
       </c>
       <c r="R295" t="n">
-        <v>6733076</v>
+        <v>6733112</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33617,10 +33622,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>127085440</v>
+        <v>127085423</v>
       </c>
       <c r="B296" t="n">
-        <v>57578</v>
+        <v>79011</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33628,39 +33633,34 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P296" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>511689</v>
+        <v>512135</v>
       </c>
       <c r="R296" t="n">
-        <v>6733024</v>
+        <v>6733010</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33719,10 +33719,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>127085399</v>
+        <v>127085371</v>
       </c>
       <c r="B297" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33754,10 +33754,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>512061</v>
+        <v>511560</v>
       </c>
       <c r="R297" t="n">
-        <v>6733112</v>
+        <v>6733100</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33816,32 +33816,32 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>127085422</v>
+        <v>127085103</v>
       </c>
       <c r="B298" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -33851,10 +33851,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>512133</v>
+        <v>511864</v>
       </c>
       <c r="R298" t="n">
-        <v>6733013</v>
+        <v>6732830</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33913,10 +33913,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>127085376</v>
+        <v>127085421</v>
       </c>
       <c r="B299" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33948,10 +33948,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>511593</v>
+        <v>512117</v>
       </c>
       <c r="R299" t="n">
-        <v>6733083</v>
+        <v>6733012</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34010,10 +34010,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>127085369</v>
+        <v>127085422</v>
       </c>
       <c r="B300" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -34045,10 +34045,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>511534</v>
+        <v>512133</v>
       </c>
       <c r="R300" t="n">
-        <v>6733112</v>
+        <v>6733013</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34107,10 +34107,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>127085374</v>
+        <v>127085376</v>
       </c>
       <c r="B301" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -34142,10 +34142,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>511592</v>
+        <v>511593</v>
       </c>
       <c r="R301" t="n">
-        <v>6733098</v>
+        <v>6733083</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -34204,10 +34204,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>127085202</v>
+        <v>127085369</v>
       </c>
       <c r="B302" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -34215,39 +34215,34 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P302" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>511500</v>
+        <v>511534</v>
       </c>
       <c r="R302" t="n">
-        <v>6733094</v>
+        <v>6733112</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -34306,10 +34301,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>127085194</v>
+        <v>127085391</v>
       </c>
       <c r="B303" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34317,39 +34312,34 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P303" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>512121</v>
+        <v>512053</v>
       </c>
       <c r="R303" t="n">
-        <v>6733244</v>
+        <v>6732969</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -34408,10 +34398,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>127085421</v>
+        <v>127085374</v>
       </c>
       <c r="B304" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34443,10 +34433,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>512117</v>
+        <v>511592</v>
       </c>
       <c r="R304" t="n">
-        <v>6733012</v>
+        <v>6733098</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -34505,10 +34495,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>127085391</v>
+        <v>127085194</v>
       </c>
       <c r="B305" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34516,34 +34506,39 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>512053</v>
+        <v>512121</v>
       </c>
       <c r="R305" t="n">
-        <v>6732969</v>
+        <v>6733244</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -34602,45 +34597,50 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>127085103</v>
+        <v>127085202</v>
       </c>
       <c r="B306" t="n">
-        <v>91210</v>
+        <v>57654</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>511864</v>
+        <v>511500</v>
       </c>
       <c r="R306" t="n">
-        <v>6732830</v>
+        <v>6733094</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -34699,50 +34699,45 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>127085199</v>
+        <v>127085231</v>
       </c>
       <c r="B307" t="n">
-        <v>57654</v>
+        <v>97314</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>511661</v>
+        <v>512087</v>
       </c>
       <c r="R307" t="n">
-        <v>6732784</v>
+        <v>6733123</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -34801,45 +34796,50 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>127085231</v>
+        <v>127085195</v>
       </c>
       <c r="B308" t="n">
-        <v>97239</v>
+        <v>57654</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P308" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>512087</v>
+        <v>511486</v>
       </c>
       <c r="R308" t="n">
-        <v>6733123</v>
+        <v>6733121</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34898,10 +34898,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>127085337</v>
+        <v>127085199</v>
       </c>
       <c r="B309" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34909,34 +34909,39 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>512108</v>
+        <v>511661</v>
       </c>
       <c r="R309" t="n">
-        <v>6733225</v>
+        <v>6732784</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -34995,10 +35000,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>127085437</v>
+        <v>127085364</v>
       </c>
       <c r="B310" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -35030,10 +35035,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>512124</v>
+        <v>511529</v>
       </c>
       <c r="R310" t="n">
-        <v>6733188</v>
+        <v>6733159</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -35092,10 +35097,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>127085195</v>
+        <v>127085085</v>
       </c>
       <c r="B311" t="n">
-        <v>57654</v>
+        <v>75135</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -35103,39 +35108,34 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P311" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>511486</v>
+        <v>511488</v>
       </c>
       <c r="R311" t="n">
-        <v>6733121</v>
+        <v>6733088</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -35194,10 +35194,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>127085364</v>
+        <v>127085337</v>
       </c>
       <c r="B312" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35229,10 +35229,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>511529</v>
+        <v>512108</v>
       </c>
       <c r="R312" t="n">
-        <v>6733159</v>
+        <v>6733225</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -35291,10 +35291,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>127085375</v>
+        <v>127085437</v>
       </c>
       <c r="B313" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35326,10 +35326,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>511591</v>
+        <v>512124</v>
       </c>
       <c r="R313" t="n">
-        <v>6733096</v>
+        <v>6733188</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -35388,10 +35388,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>127085085</v>
+        <v>127085375</v>
       </c>
       <c r="B314" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35399,21 +35399,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -35423,10 +35423,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>511488</v>
+        <v>511591</v>
       </c>
       <c r="R314" t="n">
-        <v>6733088</v>
+        <v>6733096</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -35485,10 +35485,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>127085365</v>
+        <v>127085367</v>
       </c>
       <c r="B315" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35520,10 +35520,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>511539</v>
+        <v>511537</v>
       </c>
       <c r="R315" t="n">
-        <v>6733143</v>
+        <v>6733131</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -35585,7 +35585,7 @@
         <v>127085435</v>
       </c>
       <c r="B316" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35679,10 +35679,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>127085352</v>
+        <v>127085401</v>
       </c>
       <c r="B317" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35714,10 +35714,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>511672</v>
+        <v>512056</v>
       </c>
       <c r="R317" t="n">
-        <v>6733158</v>
+        <v>6733111</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -35776,10 +35776,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>127085200</v>
+        <v>127085352</v>
       </c>
       <c r="B318" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35787,39 +35787,34 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P318" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>511772</v>
+        <v>511672</v>
       </c>
       <c r="R318" t="n">
-        <v>6732831</v>
+        <v>6733158</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -35878,10 +35873,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>127085368</v>
+        <v>127085365</v>
       </c>
       <c r="B319" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35913,10 +35908,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>511537</v>
+        <v>511539</v>
       </c>
       <c r="R319" t="n">
-        <v>6733122</v>
+        <v>6733143</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -35975,59 +35970,45 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>127085264</v>
+        <v>127085368</v>
       </c>
       <c r="B320" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>512226</v>
+        <v>511537</v>
       </c>
       <c r="R320" t="n">
-        <v>6733149</v>
+        <v>6733122</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -36060,11 +36041,6 @@
       <c r="AA320" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -36091,10 +36067,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>127085193</v>
+        <v>127085388</v>
       </c>
       <c r="B321" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36102,39 +36078,34 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P321" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>511626</v>
+        <v>511962</v>
       </c>
       <c r="R321" t="n">
-        <v>6733097</v>
+        <v>6732936</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -36167,11 +36138,6 @@
       <c r="AA321" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -36198,10 +36164,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>127085388</v>
+        <v>127085200</v>
       </c>
       <c r="B322" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36209,34 +36175,39 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P322" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>511962</v>
+        <v>511772</v>
       </c>
       <c r="R322" t="n">
-        <v>6732936</v>
+        <v>6732831</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -36295,10 +36266,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127085367</v>
+        <v>127085193</v>
       </c>
       <c r="B323" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36306,34 +36277,39 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P323" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>511537</v>
+        <v>511626</v>
       </c>
       <c r="R323" t="n">
-        <v>6733131</v>
+        <v>6733097</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -36366,6 +36342,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36392,10 +36373,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127085401</v>
+        <v>127085144</v>
       </c>
       <c r="B324" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36403,34 +36384,39 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P324" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>512056</v>
+        <v>511510</v>
       </c>
       <c r="R324" t="n">
-        <v>6733111</v>
+        <v>6733106</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -36463,6 +36449,11 @@
       <c r="AA324" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36489,38 +36480,47 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>127085144</v>
+        <v>127085264</v>
       </c>
       <c r="B325" t="n">
-        <v>57657</v>
+        <v>98436</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr"/>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
@@ -36529,10 +36529,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>511510</v>
+        <v>512226</v>
       </c>
       <c r="R325" t="n">
-        <v>6733106</v>
+        <v>6733149</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -36569,7 +36569,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36596,45 +36596,50 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127085276</v>
+        <v>127085456</v>
       </c>
       <c r="B326" t="n">
-        <v>91259</v>
+        <v>5176</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P326" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>511826</v>
+        <v>511592</v>
       </c>
       <c r="R326" t="n">
-        <v>6732810</v>
+        <v>6733099</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36693,10 +36698,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127085456</v>
+        <v>127085171</v>
       </c>
       <c r="B327" t="n">
-        <v>5176</v>
+        <v>4772</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36704,39 +36709,43 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>511592</v>
+        <v>512121</v>
       </c>
       <c r="R327" t="n">
-        <v>6733099</v>
+        <v>6733244</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -36777,6 +36786,7 @@
       <c r="AE327" t="b">
         <v>0</v>
       </c>
+      <c r="AF327" t="inlineStr"/>
       <c r="AG327" t="b">
         <v>0</v>
       </c>
@@ -36795,10 +36805,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127085355</v>
+        <v>127085276</v>
       </c>
       <c r="B328" t="n">
-        <v>78980</v>
+        <v>91333</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36806,21 +36816,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -36830,10 +36840,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>511486</v>
+        <v>511826</v>
       </c>
       <c r="R328" t="n">
-        <v>6733131</v>
+        <v>6732810</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -36892,10 +36902,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127085359</v>
+        <v>127085336</v>
       </c>
       <c r="B329" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36927,10 +36937,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>511498</v>
+        <v>512117</v>
       </c>
       <c r="R329" t="n">
-        <v>6733163</v>
+        <v>6733256</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36989,10 +36999,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127085336</v>
+        <v>127085359</v>
       </c>
       <c r="B330" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -37024,10 +37034,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>512117</v>
+        <v>511498</v>
       </c>
       <c r="R330" t="n">
-        <v>6733256</v>
+        <v>6733163</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -37086,50 +37096,45 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127085081</v>
+        <v>127085355</v>
       </c>
       <c r="B331" t="n">
-        <v>5196</v>
+        <v>79011</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>511695</v>
+        <v>511486</v>
       </c>
       <c r="R331" t="n">
-        <v>6732765</v>
+        <v>6733131</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -37295,10 +37300,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>127085171</v>
+        <v>127085081</v>
       </c>
       <c r="B333" t="n">
-        <v>4772</v>
+        <v>5196</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -37306,43 +37311,39 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>512121</v>
+        <v>511695</v>
       </c>
       <c r="R333" t="n">
-        <v>6733244</v>
+        <v>6732765</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -37383,7 +37384,6 @@
       <c r="AE333" t="b">
         <v>0</v>
       </c>
-      <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="b">
         <v>0</v>
       </c>
@@ -37402,10 +37402,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>127085383</v>
+        <v>127085129</v>
       </c>
       <c r="B334" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -37413,21 +37413,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -37437,10 +37437,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>511963</v>
+        <v>512128</v>
       </c>
       <c r="R334" t="n">
-        <v>6732874</v>
+        <v>6733072</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -37502,7 +37502,7 @@
         <v>127085363</v>
       </c>
       <c r="B335" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -37596,59 +37596,45 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>127085267</v>
+        <v>127085383</v>
       </c>
       <c r="B336" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>512119</v>
+        <v>511963</v>
       </c>
       <c r="R336" t="n">
-        <v>6733261</v>
+        <v>6732874</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -37681,11 +37667,6 @@
       <c r="AA336" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -37712,45 +37693,50 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>127085129</v>
+        <v>127085083</v>
       </c>
       <c r="B337" t="n">
-        <v>91245</v>
+        <v>5196</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P337" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>512128</v>
+        <v>512159</v>
       </c>
       <c r="R337" t="n">
-        <v>6733072</v>
+        <v>6733145</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -37809,38 +37795,47 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>127085083</v>
+        <v>127085267</v>
       </c>
       <c r="B338" t="n">
-        <v>5196</v>
+        <v>98436</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr"/>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -37849,10 +37844,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>512159</v>
+        <v>512119</v>
       </c>
       <c r="R338" t="n">
-        <v>6733145</v>
+        <v>6733261</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -37885,6 +37880,11 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -37911,10 +37911,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>127085385</v>
+        <v>127085387</v>
       </c>
       <c r="B339" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -37946,10 +37946,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>511929</v>
+        <v>511959</v>
       </c>
       <c r="R339" t="n">
-        <v>6732872</v>
+        <v>6732929</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -38008,10 +38008,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>127085387</v>
+        <v>127085425</v>
       </c>
       <c r="B340" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -38043,10 +38043,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>511959</v>
+        <v>512152</v>
       </c>
       <c r="R340" t="n">
-        <v>6732929</v>
+        <v>6733002</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -38105,10 +38105,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>127085197</v>
+        <v>127085385</v>
       </c>
       <c r="B341" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -38116,39 +38116,34 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P341" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>511667</v>
+        <v>511929</v>
       </c>
       <c r="R341" t="n">
-        <v>6732993</v>
+        <v>6732872</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -38207,10 +38202,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127085425</v>
+        <v>127085197</v>
       </c>
       <c r="B342" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -38218,34 +38213,39 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P342" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>512152</v>
+        <v>511667</v>
       </c>
       <c r="R342" t="n">
-        <v>6733002</v>
+        <v>6732993</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -38409,10 +38409,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127085201</v>
+        <v>127085386</v>
       </c>
       <c r="B344" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -38420,39 +38420,34 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P344" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>512082</v>
+        <v>511933</v>
       </c>
       <c r="R344" t="n">
-        <v>6733093</v>
+        <v>6732941</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -38514,7 +38509,7 @@
         <v>127085389</v>
       </c>
       <c r="B345" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -38611,7 +38606,7 @@
         <v>127085392</v>
       </c>
       <c r="B346" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -38705,10 +38700,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127085386</v>
+        <v>127085384</v>
       </c>
       <c r="B347" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -38740,10 +38735,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>511933</v>
+        <v>511951</v>
       </c>
       <c r="R347" t="n">
-        <v>6732941</v>
+        <v>6732870</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -38802,10 +38797,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127085384</v>
+        <v>127085173</v>
       </c>
       <c r="B348" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38813,34 +38808,43 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P348" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>511951</v>
+        <v>512096</v>
       </c>
       <c r="R348" t="n">
-        <v>6732870</v>
+        <v>6733103</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -38902,7 +38906,7 @@
         <v>127085219</v>
       </c>
       <c r="B349" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -38996,10 +39000,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127085173</v>
+        <v>127085126</v>
       </c>
       <c r="B350" t="n">
-        <v>57817</v>
+        <v>91319</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -39007,43 +39011,34 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>512096</v>
+        <v>512043</v>
       </c>
       <c r="R350" t="n">
-        <v>6733103</v>
+        <v>6732961</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -39102,10 +39097,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127085126</v>
+        <v>127085201</v>
       </c>
       <c r="B351" t="n">
-        <v>91245</v>
+        <v>57654</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -39113,34 +39108,39 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P351" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>512043</v>
+        <v>512082</v>
       </c>
       <c r="R351" t="n">
-        <v>6732961</v>
+        <v>6733093</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -39318,7 +39318,7 @@
         <v>127079331</v>
       </c>
       <c r="B353" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>127086241</v>
       </c>
       <c r="B354" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>127086095</v>
       </c>
       <c r="B357" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>127078642</v>
       </c>
       <c r="B358" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>127078718</v>
       </c>
       <c r="B361" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40319,45 +40319,45 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>127084913</v>
+        <v>127069147</v>
       </c>
       <c r="B362" t="n">
-        <v>58027</v>
+        <v>91319</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>512113</v>
+        <v>512042</v>
       </c>
       <c r="R362" t="n">
-        <v>6733275</v>
+        <v>6732964</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -40389,7 +40389,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -40399,7 +40399,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -40426,45 +40426,45 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>127069147</v>
+        <v>127084913</v>
       </c>
       <c r="B363" t="n">
-        <v>91245</v>
+        <v>58027</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>512042</v>
+        <v>512113</v>
       </c>
       <c r="R363" t="n">
-        <v>6732964</v>
+        <v>6733275</v>
       </c>
       <c r="S363" t="n">
         <v>10</v>
@@ -40496,7 +40496,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -40506,7 +40506,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -40533,49 +40533,53 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>127078700</v>
+        <v>127106618</v>
       </c>
       <c r="B364" t="n">
-        <v>57657</v>
+        <v>98353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>512074</v>
+        <v>511541</v>
       </c>
       <c r="R364" t="n">
-        <v>6733265</v>
+        <v>6732980</v>
       </c>
       <c r="S364" t="n">
         <v>10</v>
@@ -40602,22 +40606,22 @@
       </c>
       <c r="Y364" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AD364" t="b">
@@ -40626,6 +40630,7 @@
       <c r="AE364" t="b">
         <v>0</v>
       </c>
+      <c r="AF364" t="inlineStr"/>
       <c r="AG364" t="b">
         <v>0</v>
       </c>
@@ -40644,53 +40649,49 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>127106618</v>
+        <v>127078700</v>
       </c>
       <c r="B365" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
       <c r="N365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>511541</v>
+        <v>512074</v>
       </c>
       <c r="R365" t="n">
-        <v>6732980</v>
+        <v>6733265</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -40717,22 +40718,22 @@
       </c>
       <c r="Y365" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD365" t="b">
@@ -40741,7 +40742,6 @@
       <c r="AE365" t="b">
         <v>0</v>
       </c>
-      <c r="AF365" t="inlineStr"/>
       <c r="AG365" t="b">
         <v>0</v>
       </c>
@@ -41216,7 +41216,7 @@
         <v>127158796</v>
       </c>
       <c r="B370" t="n">
-        <v>91652</v>
+        <v>91726</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>127151913</v>
       </c>
       <c r="B371" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>127151868</v>
       </c>
       <c r="B374" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -41770,10 +41770,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>127151856</v>
+        <v>127147125</v>
       </c>
       <c r="B375" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41781,34 +41781,34 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>511687</v>
+        <v>511478</v>
       </c>
       <c r="R375" t="n">
-        <v>6733140</v>
+        <v>6733039</v>
       </c>
       <c r="S375" t="n">
         <v>9</v>
@@ -41840,7 +41840,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -41850,7 +41850,12 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>På stående Gran högstubbe</t>
         </is>
       </c>
       <c r="AD375" t="b">
@@ -41877,10 +41882,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>127147125</v>
+        <v>127151856</v>
       </c>
       <c r="B376" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -41888,34 +41893,34 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>511478</v>
+        <v>511687</v>
       </c>
       <c r="R376" t="n">
-        <v>6733039</v>
+        <v>6733140</v>
       </c>
       <c r="S376" t="n">
         <v>9</v>
@@ -41947,7 +41952,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -41957,12 +41962,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>På stående Gran högstubbe</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -41992,7 +41992,7 @@
         <v>127158638</v>
       </c>
       <c r="B377" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>127151718</v>
       </c>
       <c r="B378" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>127151062</v>
       </c>
       <c r="B380" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>127192913</v>
       </c>
       <c r="B381" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -42654,45 +42654,50 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>127173471</v>
+        <v>127170587</v>
       </c>
       <c r="B383" t="n">
-        <v>78980</v>
+        <v>4772</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>511580</v>
+        <v>511448</v>
       </c>
       <c r="R383" t="n">
-        <v>6733109</v>
+        <v>6733009</v>
       </c>
       <c r="S383" t="n">
         <v>9</v>
@@ -42724,7 +42729,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -42734,7 +42739,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -42761,50 +42766,45 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>127170587</v>
+        <v>127173471</v>
       </c>
       <c r="B384" t="n">
-        <v>4772</v>
+        <v>79011</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P384" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>511448</v>
+        <v>511580</v>
       </c>
       <c r="R384" t="n">
-        <v>6733009</v>
+        <v>6733109</v>
       </c>
       <c r="S384" t="n">
         <v>9</v>
@@ -42836,7 +42836,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -42846,7 +42846,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -43107,10 +43107,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>127170314</v>
+        <v>127150596</v>
       </c>
       <c r="B387" t="n">
-        <v>58516</v>
+        <v>5196</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -43118,43 +43118,39 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>511427</v>
+        <v>511636</v>
       </c>
       <c r="R387" t="n">
-        <v>6733063</v>
+        <v>6733075</v>
       </c>
       <c r="S387" t="n">
         <v>9</v>
@@ -43181,22 +43177,27 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>Tretå hål i samma</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -43223,10 +43224,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>127150596</v>
+        <v>127170314</v>
       </c>
       <c r="B388" t="n">
-        <v>5196</v>
+        <v>58516</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43234,39 +43235,43 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>105930</v>
+        <v>208249</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr"/>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>511636</v>
+        <v>511427</v>
       </c>
       <c r="R388" t="n">
-        <v>6733075</v>
+        <v>6733063</v>
       </c>
       <c r="S388" t="n">
         <v>9</v>
@@ -43293,27 +43298,22 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC388" t="inlineStr">
-        <is>
-          <t>Tretå hål i samma</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -43340,10 +43340,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>127172040</v>
+        <v>127188096</v>
       </c>
       <c r="B389" t="n">
-        <v>78980</v>
+        <v>5175</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -43351,37 +43351,46 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>511528</v>
+        <v>511468</v>
       </c>
       <c r="R389" t="n">
-        <v>6733011</v>
+        <v>6733032</v>
       </c>
       <c r="S389" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -43410,7 +43419,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -43420,7 +43429,12 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>På stammen på gran ca17cm</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -43429,6 +43443,7 @@
       <c r="AE389" t="b">
         <v>0</v>
       </c>
+      <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
@@ -43447,10 +43462,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>127188096</v>
+        <v>127172040</v>
       </c>
       <c r="B390" t="n">
-        <v>5175</v>
+        <v>79011</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -43458,46 +43473,37 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>511468</v>
+        <v>511528</v>
       </c>
       <c r="R390" t="n">
-        <v>6733032</v>
+        <v>6733011</v>
       </c>
       <c r="S390" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -43526,7 +43532,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -43536,12 +43542,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC390" t="inlineStr">
-        <is>
-          <t>På stammen på gran ca17cm</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -43550,7 +43551,6 @@
       <c r="AE390" t="b">
         <v>0</v>
       </c>
-      <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="b">
         <v>0</v>
       </c>
@@ -43913,42 +43913,37 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>127195257</v>
+        <v>127194958</v>
       </c>
       <c r="B394" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
-      <c r="M394" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N394" t="inlineStr"/>
       <c r="P394" t="inlineStr">
         <is>
@@ -43956,10 +43951,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>511546</v>
+        <v>511660</v>
       </c>
       <c r="R394" t="n">
-        <v>6733130</v>
+        <v>6733092</v>
       </c>
       <c r="S394" t="n">
         <v>10</v>
@@ -43991,7 +43986,7 @@
       </c>
       <c r="Z394" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
@@ -44001,7 +43996,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD394" t="b">
@@ -44010,6 +44005,7 @@
       <c r="AE394" t="b">
         <v>0</v>
       </c>
+      <c r="AF394" t="inlineStr"/>
       <c r="AG394" t="b">
         <v>0</v>
       </c>
@@ -44028,37 +44024,42 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>127194958</v>
+        <v>127195257</v>
       </c>
       <c r="B395" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N395" t="inlineStr"/>
       <c r="P395" t="inlineStr">
         <is>
@@ -44066,10 +44067,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>511660</v>
+        <v>511546</v>
       </c>
       <c r="R395" t="n">
-        <v>6733092</v>
+        <v>6733130</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -44101,7 +44102,7 @@
       </c>
       <c r="Z395" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
@@ -44111,7 +44112,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD395" t="b">
@@ -44120,7 +44121,6 @@
       <c r="AE395" t="b">
         <v>0</v>
       </c>
-      <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="b">
         <v>0</v>
       </c>
@@ -44139,7 +44139,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>127170414</v>
+        <v>127170665</v>
       </c>
       <c r="B396" t="n">
         <v>5196</v>
@@ -44179,10 +44179,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>511433</v>
+        <v>511448</v>
       </c>
       <c r="R396" t="n">
-        <v>6733065</v>
+        <v>6733009</v>
       </c>
       <c r="S396" t="n">
         <v>9</v>
@@ -44214,7 +44214,7 @@
       </c>
       <c r="Z396" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -44224,7 +44224,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -44251,7 +44251,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>127170665</v>
+        <v>127170414</v>
       </c>
       <c r="B397" t="n">
         <v>5196</v>
@@ -44291,10 +44291,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>511448</v>
+        <v>511433</v>
       </c>
       <c r="R397" t="n">
-        <v>6733009</v>
+        <v>6733065</v>
       </c>
       <c r="S397" t="n">
         <v>9</v>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
@@ -44336,7 +44336,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -44592,43 +44592,37 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>127190540</v>
+        <v>127226987</v>
       </c>
       <c r="B400" t="n">
-        <v>5196</v>
+        <v>79011</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
@@ -44636,10 +44630,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>511525</v>
+        <v>511478</v>
       </c>
       <c r="R400" t="n">
-        <v>6733021</v>
+        <v>6733047</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -44666,22 +44660,22 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -44709,37 +44703,43 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>127226987</v>
+        <v>127190540</v>
       </c>
       <c r="B401" t="n">
-        <v>78980</v>
+        <v>5196</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
@@ -44747,10 +44747,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>511478</v>
+        <v>511525</v>
       </c>
       <c r="R401" t="n">
-        <v>6733047</v>
+        <v>6733021</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -44777,22 +44777,22 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD401" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -21032,7 +21032,7 @@
         <v>126591562</v>
       </c>
       <c r="B174" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>126595944</v>
       </c>
       <c r="B175" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>126590847</v>
       </c>
       <c r="B176" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>126597287</v>
       </c>
       <c r="B177" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>126596924</v>
       </c>
       <c r="B179" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>126594826</v>
       </c>
       <c r="B180" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>126596172</v>
       </c>
       <c r="B181" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>126596593</v>
       </c>
       <c r="B182" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>126596554</v>
       </c>
       <c r="B187" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>126688780</v>
       </c>
       <c r="B189" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126688773</v>
+        <v>126688774</v>
       </c>
       <c r="B194" t="n">
         <v>56849</v>
@@ -23377,7 +23377,11 @@
       <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -23385,10 +23389,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>511607</v>
+        <v>511625</v>
       </c>
       <c r="R194" t="n">
-        <v>6732885</v>
+        <v>6732869</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -23420,7 +23424,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23430,12 +23434,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Åter ett visitmärke på ett vindfälle som man har sågat av.</t>
+          <t>Tämligen mycket färsk spillning men även lite äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23462,7 +23466,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126688774</v>
+        <v>126688773</v>
       </c>
       <c r="B195" t="n">
         <v>56849</v>
@@ -23493,11 +23497,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -23505,10 +23505,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>511625</v>
+        <v>511607</v>
       </c>
       <c r="R195" t="n">
-        <v>6732869</v>
+        <v>6732885</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23550,12 +23550,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Tämligen mycket färsk spillning men även lite äldre</t>
+          <t>Åter ett visitmärke på ett vindfälle som man har sågat av.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24044,10 +24044,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127085156</v>
+        <v>127085356</v>
       </c>
       <c r="B200" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24055,39 +24055,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>511571</v>
+        <v>511487</v>
       </c>
       <c r="R200" t="n">
-        <v>6733063</v>
+        <v>6733143</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24120,11 +24115,6 @@
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24151,10 +24141,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127085145</v>
+        <v>127085438</v>
       </c>
       <c r="B201" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24162,39 +24152,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>511991</v>
+        <v>512121</v>
       </c>
       <c r="R201" t="n">
-        <v>6732936</v>
+        <v>6733264</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24227,11 +24212,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24258,32 +24238,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127085356</v>
+        <v>127085105</v>
       </c>
       <c r="B202" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -24293,10 +24273,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>511487</v>
+        <v>512122</v>
       </c>
       <c r="R202" t="n">
-        <v>6733143</v>
+        <v>6733004</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -24355,10 +24335,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127085438</v>
+        <v>127085380</v>
       </c>
       <c r="B203" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24390,10 +24370,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>512121</v>
+        <v>511665</v>
       </c>
       <c r="R203" t="n">
-        <v>6733264</v>
+        <v>6732780</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24452,32 +24432,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127085105</v>
+        <v>127085429</v>
       </c>
       <c r="B204" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -24487,10 +24467,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>512122</v>
+        <v>512205</v>
       </c>
       <c r="R204" t="n">
-        <v>6733004</v>
+        <v>6733078</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24549,10 +24529,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127085380</v>
+        <v>127085156</v>
       </c>
       <c r="B205" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24560,34 +24540,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>511665</v>
+        <v>511571</v>
       </c>
       <c r="R205" t="n">
-        <v>6732780</v>
+        <v>6733063</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24620,6 +24605,11 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24646,10 +24636,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127085429</v>
+        <v>127085145</v>
       </c>
       <c r="B206" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24657,34 +24647,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>512205</v>
+        <v>511991</v>
       </c>
       <c r="R206" t="n">
-        <v>6733078</v>
+        <v>6732936</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24717,6 +24712,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24743,10 +24743,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127085154</v>
+        <v>127085357</v>
       </c>
       <c r="B207" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24754,39 +24754,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>512098</v>
+        <v>511531</v>
       </c>
       <c r="R207" t="n">
-        <v>6733172</v>
+        <v>6733158</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24819,11 +24814,6 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24850,10 +24840,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127085357</v>
+        <v>127085426</v>
       </c>
       <c r="B208" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,10 +24875,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>511531</v>
+        <v>512214</v>
       </c>
       <c r="R208" t="n">
-        <v>6733158</v>
+        <v>6733017</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24947,10 +24937,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127085426</v>
+        <v>127085154</v>
       </c>
       <c r="B209" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24958,34 +24948,39 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>512214</v>
+        <v>512098</v>
       </c>
       <c r="R209" t="n">
-        <v>6733017</v>
+        <v>6733172</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25018,6 +25013,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25044,7 +25044,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127085204</v>
+        <v>127085192</v>
       </c>
       <c r="B210" t="n">
         <v>57654</v>
@@ -25075,7 +25075,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -25084,10 +25084,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>511872</v>
+        <v>512240</v>
       </c>
       <c r="R210" t="n">
-        <v>6732834</v>
+        <v>6733130</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25146,7 +25146,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127085192</v>
+        <v>127085204</v>
       </c>
       <c r="B211" t="n">
         <v>57654</v>
@@ -25177,7 +25177,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -25186,10 +25186,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>512240</v>
+        <v>511872</v>
       </c>
       <c r="R211" t="n">
-        <v>6733130</v>
+        <v>6732834</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25248,10 +25248,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127085196</v>
+        <v>127085350</v>
       </c>
       <c r="B212" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25259,39 +25259,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>511574</v>
+        <v>511648</v>
       </c>
       <c r="R212" t="n">
-        <v>6733042</v>
+        <v>6733131</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25350,54 +25345,45 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127085168</v>
+        <v>127085353</v>
       </c>
       <c r="B213" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>511692</v>
+        <v>511443</v>
       </c>
       <c r="R213" t="n">
-        <v>6732762</v>
+        <v>6733122</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25438,7 +25424,6 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -25457,10 +25442,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127085198</v>
+        <v>127085149</v>
       </c>
       <c r="B214" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25468,16 +25453,16 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -25497,10 +25482,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>511652</v>
+        <v>512180</v>
       </c>
       <c r="R214" t="n">
-        <v>6732988</v>
+        <v>6733152</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25533,6 +25518,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25559,50 +25549,54 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127085149</v>
+        <v>127085168</v>
       </c>
       <c r="B215" t="n">
-        <v>57657</v>
+        <v>4772</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>512180</v>
+        <v>511692</v>
       </c>
       <c r="R215" t="n">
-        <v>6733152</v>
+        <v>6732762</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25637,17 +25631,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -25666,10 +25656,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127085350</v>
+        <v>127085196</v>
       </c>
       <c r="B216" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25677,34 +25667,39 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>511648</v>
+        <v>511574</v>
       </c>
       <c r="R216" t="n">
-        <v>6733131</v>
+        <v>6733042</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25763,10 +25758,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127085353</v>
+        <v>127085198</v>
       </c>
       <c r="B217" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25774,34 +25769,39 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>511443</v>
+        <v>511652</v>
       </c>
       <c r="R217" t="n">
-        <v>6733122</v>
+        <v>6732988</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25863,7 +25863,7 @@
         <v>127085431</v>
       </c>
       <c r="B218" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>127085347</v>
       </c>
       <c r="B219" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26054,32 +26054,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127085420</v>
+        <v>127085175</v>
       </c>
       <c r="B220" t="n">
-        <v>79011</v>
+        <v>92260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -26089,10 +26089,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>512122</v>
+        <v>511428</v>
       </c>
       <c r="R220" t="n">
-        <v>6733004</v>
+        <v>6733130</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26151,32 +26151,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127085175</v>
+        <v>127085420</v>
       </c>
       <c r="B221" t="n">
-        <v>92254</v>
+        <v>79014</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -26186,10 +26186,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>511428</v>
+        <v>512122</v>
       </c>
       <c r="R221" t="n">
-        <v>6733130</v>
+        <v>6733004</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26251,7 +26251,7 @@
         <v>127085358</v>
       </c>
       <c r="B222" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>127085351</v>
       </c>
       <c r="B223" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26442,50 +26442,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127085082</v>
+        <v>127085133</v>
       </c>
       <c r="B224" t="n">
-        <v>5196</v>
+        <v>91325</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>512165</v>
+        <v>512166</v>
       </c>
       <c r="R224" t="n">
-        <v>6733149</v>
+        <v>6733144</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26544,10 +26539,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127085133</v>
+        <v>127085131</v>
       </c>
       <c r="B225" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26579,10 +26574,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>512166</v>
+        <v>512090</v>
       </c>
       <c r="R225" t="n">
-        <v>6733144</v>
+        <v>6733122</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26641,10 +26636,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127085131</v>
+        <v>127085134</v>
       </c>
       <c r="B226" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26676,10 +26671,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>512090</v>
+        <v>512215</v>
       </c>
       <c r="R226" t="n">
-        <v>6733122</v>
+        <v>6733164</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26738,45 +26733,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127085134</v>
+        <v>127085082</v>
       </c>
       <c r="B227" t="n">
-        <v>91319</v>
+        <v>5196</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>512215</v>
+        <v>512165</v>
       </c>
       <c r="R227" t="n">
-        <v>6733164</v>
+        <v>6733149</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26838,7 +26838,7 @@
         <v>127085269</v>
       </c>
       <c r="B228" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>127085102</v>
       </c>
       <c r="B229" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>127085379</v>
       </c>
       <c r="B230" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>127085256</v>
       </c>
       <c r="B231" t="n">
-        <v>91792</v>
+        <v>91798</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>127085366</v>
       </c>
       <c r="B232" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>127085338</v>
       </c>
       <c r="B233" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>127085348</v>
       </c>
       <c r="B234" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>127085428</v>
       </c>
       <c r="B235" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>127085255</v>
       </c>
       <c r="B236" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27717,50 +27717,45 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127085080</v>
+        <v>127085390</v>
       </c>
       <c r="B237" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>512226</v>
+        <v>512008</v>
       </c>
       <c r="R237" t="n">
-        <v>6733157</v>
+        <v>6732919</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27819,10 +27814,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127085441</v>
+        <v>127085427</v>
       </c>
       <c r="B238" t="n">
-        <v>88722</v>
+        <v>79014</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27830,21 +27825,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -27854,10 +27849,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>512169</v>
+        <v>512225</v>
       </c>
       <c r="R238" t="n">
-        <v>6733007</v>
+        <v>6733108</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27919,7 +27914,7 @@
         <v>127085127</v>
       </c>
       <c r="B239" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28013,10 +28008,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127085125</v>
+        <v>127085441</v>
       </c>
       <c r="B240" t="n">
-        <v>91319</v>
+        <v>88728</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28024,21 +28019,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -28048,10 +28043,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>512223</v>
+        <v>512169</v>
       </c>
       <c r="R240" t="n">
-        <v>6733163</v>
+        <v>6733007</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28110,10 +28105,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127085278</v>
+        <v>127085125</v>
       </c>
       <c r="B241" t="n">
-        <v>91544</v>
+        <v>91325</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28121,21 +28116,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -28145,10 +28140,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>512146</v>
+        <v>512223</v>
       </c>
       <c r="R241" t="n">
-        <v>6733140</v>
+        <v>6733163</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28207,10 +28202,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127085430</v>
+        <v>127085278</v>
       </c>
       <c r="B242" t="n">
-        <v>79011</v>
+        <v>91550</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28218,21 +28213,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>1101</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -28242,10 +28237,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>512198</v>
+        <v>512146</v>
       </c>
       <c r="R242" t="n">
-        <v>6733079</v>
+        <v>6733140</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28304,45 +28299,50 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127085436</v>
+        <v>127085458</v>
       </c>
       <c r="B243" t="n">
-        <v>79011</v>
+        <v>5176</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>512103</v>
+        <v>512072</v>
       </c>
       <c r="R243" t="n">
-        <v>6733103</v>
+        <v>6733076</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28401,10 +28401,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127085107</v>
+        <v>127085459</v>
       </c>
       <c r="B244" t="n">
-        <v>91284</v>
+        <v>5176</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28412,34 +28412,39 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>512190</v>
+        <v>512124</v>
       </c>
       <c r="R244" t="n">
-        <v>6733157</v>
+        <v>6733193</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28498,45 +28503,54 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127085390</v>
+        <v>127085169</v>
       </c>
       <c r="B245" t="n">
-        <v>79011</v>
+        <v>4772</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>512008</v>
+        <v>512072</v>
       </c>
       <c r="R245" t="n">
-        <v>6732919</v>
+        <v>6733076</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28577,6 +28591,7 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -28595,45 +28610,50 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127085427</v>
+        <v>127085080</v>
       </c>
       <c r="B246" t="n">
-        <v>79011</v>
+        <v>5196</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>512225</v>
+        <v>512226</v>
       </c>
       <c r="R246" t="n">
-        <v>6733108</v>
+        <v>6733157</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28692,38 +28712,47 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127085458</v>
+        <v>127085266</v>
       </c>
       <c r="B247" t="n">
-        <v>5176</v>
+        <v>98442</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28732,10 +28761,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>512072</v>
+        <v>511616</v>
       </c>
       <c r="R247" t="n">
-        <v>6733076</v>
+        <v>6733018</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28768,6 +28797,11 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28794,50 +28828,45 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127085459</v>
+        <v>127085430</v>
       </c>
       <c r="B248" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>512124</v>
+        <v>512198</v>
       </c>
       <c r="R248" t="n">
-        <v>6733193</v>
+        <v>6733079</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28896,54 +28925,45 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127085169</v>
+        <v>127085436</v>
       </c>
       <c r="B249" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>512072</v>
+        <v>512103</v>
       </c>
       <c r="R249" t="n">
-        <v>6733076</v>
+        <v>6733103</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28984,7 +29004,6 @@
       <c r="AE249" t="b">
         <v>0</v>
       </c>
-      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -29003,59 +29022,45 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127085266</v>
+        <v>127085107</v>
       </c>
       <c r="B250" t="n">
-        <v>98436</v>
+        <v>91290</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>511616</v>
+        <v>512190</v>
       </c>
       <c r="R250" t="n">
-        <v>6733018</v>
+        <v>6733157</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29088,11 +29093,6 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29119,10 +29119,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127085132</v>
+        <v>127085373</v>
       </c>
       <c r="B251" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29130,21 +29130,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -29154,10 +29154,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>512170</v>
+        <v>511572</v>
       </c>
       <c r="R251" t="n">
-        <v>6733213</v>
+        <v>6733106</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29216,10 +29216,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127085373</v>
+        <v>127085432</v>
       </c>
       <c r="B252" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29251,10 +29251,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>511572</v>
+        <v>512143</v>
       </c>
       <c r="R252" t="n">
-        <v>6733106</v>
+        <v>6733060</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29313,10 +29313,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127085432</v>
+        <v>127085132</v>
       </c>
       <c r="B253" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29324,21 +29324,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -29348,10 +29348,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>512143</v>
+        <v>512170</v>
       </c>
       <c r="R253" t="n">
-        <v>6733060</v>
+        <v>6733213</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29731,32 +29731,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127085221</v>
+        <v>127085397</v>
       </c>
       <c r="B257" t="n">
-        <v>91773</v>
+        <v>79014</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29766,10 +29766,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>512146</v>
+        <v>512067</v>
       </c>
       <c r="R257" t="n">
-        <v>6733146</v>
+        <v>6733087</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29828,10 +29828,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127085152</v>
+        <v>127085382</v>
       </c>
       <c r="B258" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29839,39 +29839,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>511598</v>
+        <v>511938</v>
       </c>
       <c r="R258" t="n">
-        <v>6733104</v>
+        <v>6732856</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29904,11 +29899,6 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29935,50 +29925,45 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127085148</v>
+        <v>127085221</v>
       </c>
       <c r="B259" t="n">
-        <v>57657</v>
+        <v>91779</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>512064</v>
+        <v>512146</v>
       </c>
       <c r="R259" t="n">
-        <v>6733117</v>
+        <v>6733146</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30011,11 +29996,6 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30042,10 +30022,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127085397</v>
+        <v>127085152</v>
       </c>
       <c r="B260" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30053,34 +30033,39 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>512067</v>
+        <v>511598</v>
       </c>
       <c r="R260" t="n">
-        <v>6733087</v>
+        <v>6733104</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30113,6 +30098,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30139,10 +30129,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127085382</v>
+        <v>127085148</v>
       </c>
       <c r="B261" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30150,34 +30140,39 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>511938</v>
+        <v>512064</v>
       </c>
       <c r="R261" t="n">
-        <v>6732856</v>
+        <v>6733117</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30210,6 +30205,11 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30341,7 +30341,7 @@
         <v>127085092</v>
       </c>
       <c r="B263" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30435,10 +30435,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127085360</v>
+        <v>127085147</v>
       </c>
       <c r="B264" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30446,34 +30446,39 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>511493</v>
+        <v>512035</v>
       </c>
       <c r="R264" t="n">
-        <v>6733172</v>
+        <v>6732916</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30506,6 +30511,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30532,10 +30542,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127085434</v>
+        <v>127085161</v>
       </c>
       <c r="B265" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30543,34 +30553,39 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>512138</v>
+        <v>512225</v>
       </c>
       <c r="R265" t="n">
-        <v>6733072</v>
+        <v>6733108</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30603,6 +30618,11 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30629,10 +30649,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127085394</v>
+        <v>127085203</v>
       </c>
       <c r="B266" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30640,34 +30660,39 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>511981</v>
+        <v>511657</v>
       </c>
       <c r="R266" t="n">
-        <v>6732975</v>
+        <v>6732987</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30726,10 +30751,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127085381</v>
+        <v>127085360</v>
       </c>
       <c r="B267" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -30761,10 +30786,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>511930</v>
+        <v>511493</v>
       </c>
       <c r="R267" t="n">
-        <v>6732852</v>
+        <v>6733172</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30823,32 +30848,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127085101</v>
+        <v>127085434</v>
       </c>
       <c r="B268" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30858,10 +30883,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>511664</v>
+        <v>512138</v>
       </c>
       <c r="R268" t="n">
-        <v>6732778</v>
+        <v>6733072</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30920,10 +30945,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127085370</v>
+        <v>127085394</v>
       </c>
       <c r="B269" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30955,10 +30980,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>511551</v>
+        <v>511981</v>
       </c>
       <c r="R269" t="n">
-        <v>6733097</v>
+        <v>6732975</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31017,10 +31042,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127085203</v>
+        <v>127085381</v>
       </c>
       <c r="B270" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31028,39 +31053,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>511657</v>
+        <v>511930</v>
       </c>
       <c r="R270" t="n">
-        <v>6732987</v>
+        <v>6732852</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31119,50 +31139,45 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>127085147</v>
+        <v>127085101</v>
       </c>
       <c r="B271" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>512035</v>
+        <v>511664</v>
       </c>
       <c r="R271" t="n">
-        <v>6732916</v>
+        <v>6732778</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31195,11 +31210,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31226,10 +31236,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127085161</v>
+        <v>127085370</v>
       </c>
       <c r="B272" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31237,39 +31247,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>512225</v>
+        <v>511551</v>
       </c>
       <c r="R272" t="n">
-        <v>6733108</v>
+        <v>6733097</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31302,11 +31307,6 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31333,50 +31333,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127085084</v>
+        <v>127085400</v>
       </c>
       <c r="B273" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>512162</v>
+        <v>512064</v>
       </c>
       <c r="R273" t="n">
-        <v>6733053</v>
+        <v>6733119</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31435,54 +31430,45 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127085135</v>
+        <v>127085378</v>
       </c>
       <c r="B274" t="n">
-        <v>98459</v>
+        <v>79014</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>511795</v>
+        <v>511688</v>
       </c>
       <c r="R274" t="n">
-        <v>6732846</v>
+        <v>6733025</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31541,45 +31527,45 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>127085220</v>
+        <v>127085095</v>
       </c>
       <c r="B275" t="n">
-        <v>91773</v>
+        <v>91290</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>512044</v>
+        <v>512236</v>
       </c>
       <c r="R275" t="n">
-        <v>6732937</v>
+        <v>6733047</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31638,32 +31624,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>127085400</v>
+        <v>127085220</v>
       </c>
       <c r="B276" t="n">
-        <v>79011</v>
+        <v>91779</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31673,10 +31659,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>512064</v>
+        <v>512044</v>
       </c>
       <c r="R276" t="n">
-        <v>6733119</v>
+        <v>6732937</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31735,10 +31721,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127085378</v>
+        <v>127085150</v>
       </c>
       <c r="B277" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31746,34 +31732,39 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>511688</v>
+        <v>512042</v>
       </c>
       <c r="R277" t="n">
-        <v>6733025</v>
+        <v>6732932</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31806,6 +31797,11 @@
       <c r="AA277" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31832,10 +31828,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127085095</v>
+        <v>127085084</v>
       </c>
       <c r="B278" t="n">
-        <v>91284</v>
+        <v>5196</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31843,34 +31839,39 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>512236</v>
+        <v>512162</v>
       </c>
       <c r="R278" t="n">
-        <v>6733047</v>
+        <v>6733053</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31929,38 +31930,42 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>127085150</v>
+        <v>127085135</v>
       </c>
       <c r="B279" t="n">
-        <v>57657</v>
+        <v>98465</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
@@ -31969,10 +31974,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>512042</v>
+        <v>511795</v>
       </c>
       <c r="R279" t="n">
-        <v>6732932</v>
+        <v>6732846</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32005,11 +32010,6 @@
       <c r="AA279" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32036,10 +32036,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127085439</v>
+        <v>127085457</v>
       </c>
       <c r="B280" t="n">
-        <v>98353</v>
+        <v>5176</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32047,34 +32047,39 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>511871</v>
+        <v>511991</v>
       </c>
       <c r="R280" t="n">
-        <v>6732830</v>
+        <v>6732947</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32133,10 +32138,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127085254</v>
+        <v>127085157</v>
       </c>
       <c r="B281" t="n">
-        <v>91726</v>
+        <v>57657</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32144,29 +32149,39 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>512201</v>
+        <v>511525</v>
       </c>
       <c r="R281" t="n">
-        <v>6733180</v>
+        <v>6732923</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32199,6 +32214,11 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -32225,10 +32245,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>127085354</v>
+        <v>127085159</v>
       </c>
       <c r="B282" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -32236,34 +32256,39 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>511469</v>
+        <v>512044</v>
       </c>
       <c r="R282" t="n">
-        <v>6733119</v>
+        <v>6732923</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -32296,6 +32321,11 @@
       <c r="AA282" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32322,10 +32352,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127085396</v>
+        <v>127085354</v>
       </c>
       <c r="B283" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -32357,10 +32387,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>512072</v>
+        <v>511469</v>
       </c>
       <c r="R283" t="n">
-        <v>6733073</v>
+        <v>6733119</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32419,32 +32449,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>127085106</v>
+        <v>127085396</v>
       </c>
       <c r="B284" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -32454,10 +32484,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>512184</v>
+        <v>512072</v>
       </c>
       <c r="R284" t="n">
-        <v>6733202</v>
+        <v>6733073</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32516,32 +32546,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127085372</v>
+        <v>127085106</v>
       </c>
       <c r="B285" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -32551,10 +32581,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>511560</v>
+        <v>512184</v>
       </c>
       <c r="R285" t="n">
-        <v>6733087</v>
+        <v>6733202</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32613,10 +32643,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>127085402</v>
+        <v>127085372</v>
       </c>
       <c r="B286" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32648,10 +32678,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>512044</v>
+        <v>511560</v>
       </c>
       <c r="R286" t="n">
-        <v>6733119</v>
+        <v>6733087</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32710,10 +32740,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>127085398</v>
+        <v>127085402</v>
       </c>
       <c r="B287" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32745,10 +32775,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>512062</v>
+        <v>512044</v>
       </c>
       <c r="R287" t="n">
-        <v>6733087</v>
+        <v>6733119</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32807,10 +32837,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>127085424</v>
+        <v>127085398</v>
       </c>
       <c r="B288" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32842,10 +32872,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>512144</v>
+        <v>512062</v>
       </c>
       <c r="R288" t="n">
-        <v>6733010</v>
+        <v>6733087</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32904,10 +32934,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>127085157</v>
+        <v>127085424</v>
       </c>
       <c r="B289" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32915,39 +32945,34 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>511525</v>
+        <v>512144</v>
       </c>
       <c r="R289" t="n">
-        <v>6732923</v>
+        <v>6733010</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -32980,11 +33005,6 @@
       <c r="AA289" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -33011,50 +33031,45 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>127085159</v>
+        <v>127085439</v>
       </c>
       <c r="B290" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P290" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>512044</v>
+        <v>511871</v>
       </c>
       <c r="R290" t="n">
-        <v>6732923</v>
+        <v>6732830</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -33087,11 +33102,6 @@
       <c r="AA290" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC290" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -33118,50 +33128,40 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>127085457</v>
+        <v>127085254</v>
       </c>
       <c r="B291" t="n">
-        <v>5176</v>
+        <v>91732</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P291" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>511991</v>
+        <v>512201</v>
       </c>
       <c r="R291" t="n">
-        <v>6732947</v>
+        <v>6733180</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -33223,7 +33223,7 @@
         <v>127085257</v>
       </c>
       <c r="B292" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>127085377</v>
       </c>
       <c r="B294" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>127085399</v>
       </c>
       <c r="B295" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>127085423</v>
       </c>
       <c r="B296" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>127085371</v>
       </c>
       <c r="B297" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33816,45 +33816,50 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>127085103</v>
+        <v>127085202</v>
       </c>
       <c r="B298" t="n">
-        <v>91284</v>
+        <v>57654</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>511864</v>
+        <v>511500</v>
       </c>
       <c r="R298" t="n">
-        <v>6732830</v>
+        <v>6733094</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33913,10 +33918,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>127085421</v>
+        <v>127085194</v>
       </c>
       <c r="B299" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33924,34 +33929,39 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P299" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>512117</v>
+        <v>512121</v>
       </c>
       <c r="R299" t="n">
-        <v>6733012</v>
+        <v>6733244</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34010,32 +34020,32 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>127085422</v>
+        <v>127085103</v>
       </c>
       <c r="B300" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34045,10 +34055,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>512133</v>
+        <v>511864</v>
       </c>
       <c r="R300" t="n">
-        <v>6733013</v>
+        <v>6732830</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34107,10 +34117,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>127085376</v>
+        <v>127085421</v>
       </c>
       <c r="B301" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -34142,10 +34152,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>511593</v>
+        <v>512117</v>
       </c>
       <c r="R301" t="n">
-        <v>6733083</v>
+        <v>6733012</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -34204,10 +34214,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>127085369</v>
+        <v>127085422</v>
       </c>
       <c r="B302" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -34239,10 +34249,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>511534</v>
+        <v>512133</v>
       </c>
       <c r="R302" t="n">
-        <v>6733112</v>
+        <v>6733013</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -34301,10 +34311,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>127085391</v>
+        <v>127085376</v>
       </c>
       <c r="B303" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -34336,10 +34346,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>512053</v>
+        <v>511593</v>
       </c>
       <c r="R303" t="n">
-        <v>6732969</v>
+        <v>6733083</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -34398,10 +34408,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>127085374</v>
+        <v>127085369</v>
       </c>
       <c r="B304" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34433,10 +34443,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>511592</v>
+        <v>511534</v>
       </c>
       <c r="R304" t="n">
-        <v>6733098</v>
+        <v>6733112</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -34495,10 +34505,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>127085194</v>
+        <v>127085391</v>
       </c>
       <c r="B305" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34506,39 +34516,34 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>512121</v>
+        <v>512053</v>
       </c>
       <c r="R305" t="n">
-        <v>6733244</v>
+        <v>6732969</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -34597,10 +34602,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>127085202</v>
+        <v>127085374</v>
       </c>
       <c r="B306" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34608,39 +34613,34 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>511500</v>
+        <v>511592</v>
       </c>
       <c r="R306" t="n">
-        <v>6733094</v>
+        <v>6733098</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -34699,32 +34699,32 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>127085231</v>
+        <v>127085364</v>
       </c>
       <c r="B307" t="n">
-        <v>97314</v>
+        <v>79014</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34734,10 +34734,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>512087</v>
+        <v>511529</v>
       </c>
       <c r="R307" t="n">
-        <v>6733123</v>
+        <v>6733159</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -34796,10 +34796,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>127085195</v>
+        <v>127085085</v>
       </c>
       <c r="B308" t="n">
-        <v>57654</v>
+        <v>75138</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34807,39 +34807,34 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P308" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>511486</v>
+        <v>511488</v>
       </c>
       <c r="R308" t="n">
-        <v>6733121</v>
+        <v>6733088</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -34898,10 +34893,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>127085199</v>
+        <v>127085337</v>
       </c>
       <c r="B309" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34909,39 +34904,34 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>511661</v>
+        <v>512108</v>
       </c>
       <c r="R309" t="n">
-        <v>6732784</v>
+        <v>6733225</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -35000,10 +34990,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>127085364</v>
+        <v>127085437</v>
       </c>
       <c r="B310" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -35035,10 +35025,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>511529</v>
+        <v>512124</v>
       </c>
       <c r="R310" t="n">
-        <v>6733159</v>
+        <v>6733188</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -35097,10 +35087,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>127085085</v>
+        <v>127085375</v>
       </c>
       <c r="B311" t="n">
-        <v>75135</v>
+        <v>79014</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -35108,21 +35098,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -35132,10 +35122,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>511488</v>
+        <v>511591</v>
       </c>
       <c r="R311" t="n">
-        <v>6733088</v>
+        <v>6733096</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -35194,10 +35184,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>127085337</v>
+        <v>127085199</v>
       </c>
       <c r="B312" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35205,34 +35195,39 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>512108</v>
+        <v>511661</v>
       </c>
       <c r="R312" t="n">
-        <v>6733225</v>
+        <v>6732784</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -35291,10 +35286,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>127085437</v>
+        <v>127085195</v>
       </c>
       <c r="B313" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35302,34 +35297,39 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P313" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>512124</v>
+        <v>511486</v>
       </c>
       <c r="R313" t="n">
-        <v>6733188</v>
+        <v>6733121</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -35388,32 +35388,32 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>127085375</v>
+        <v>127085231</v>
       </c>
       <c r="B314" t="n">
-        <v>79011</v>
+        <v>97320</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -35423,10 +35423,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>511591</v>
+        <v>512087</v>
       </c>
       <c r="R314" t="n">
-        <v>6733096</v>
+        <v>6733123</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -35488,7 +35488,7 @@
         <v>127085367</v>
       </c>
       <c r="B315" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>127085435</v>
       </c>
       <c r="B316" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>127085401</v>
       </c>
       <c r="B317" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>127085352</v>
       </c>
       <c r="B318" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>127085365</v>
       </c>
       <c r="B319" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>127085368</v>
       </c>
       <c r="B320" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>127085388</v>
       </c>
       <c r="B321" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36164,10 +36164,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>127085200</v>
+        <v>127085144</v>
       </c>
       <c r="B322" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36175,16 +36175,16 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -36195,7 +36195,7 @@
       <c r="I322" t="inlineStr"/>
       <c r="M322" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
@@ -36204,10 +36204,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>511772</v>
+        <v>511510</v>
       </c>
       <c r="R322" t="n">
-        <v>6732831</v>
+        <v>6733106</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -36240,6 +36240,11 @@
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36266,7 +36271,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127085193</v>
+        <v>127085200</v>
       </c>
       <c r="B323" t="n">
         <v>57654</v>
@@ -36297,7 +36302,7 @@
       <c r="I323" t="inlineStr"/>
       <c r="M323" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
@@ -36306,10 +36311,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>511626</v>
+        <v>511772</v>
       </c>
       <c r="R323" t="n">
-        <v>6733097</v>
+        <v>6732831</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -36342,11 +36347,6 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36373,10 +36373,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127085144</v>
+        <v>127085193</v>
       </c>
       <c r="B324" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36384,16 +36384,16 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -36404,7 +36404,7 @@
       <c r="I324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
@@ -36413,10 +36413,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>511510</v>
+        <v>511626</v>
       </c>
       <c r="R324" t="n">
-        <v>6733106</v>
+        <v>6733097</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -36453,7 +36453,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
+          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36483,7 +36483,7 @@
         <v>127085264</v>
       </c>
       <c r="B325" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36596,50 +36596,45 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127085456</v>
+        <v>127085336</v>
       </c>
       <c r="B326" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P326" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>511592</v>
+        <v>512117</v>
       </c>
       <c r="R326" t="n">
-        <v>6733099</v>
+        <v>6733256</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36698,54 +36693,45 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127085171</v>
+        <v>127085359</v>
       </c>
       <c r="B327" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>512121</v>
+        <v>511498</v>
       </c>
       <c r="R327" t="n">
-        <v>6733244</v>
+        <v>6733163</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -36786,7 +36772,6 @@
       <c r="AE327" t="b">
         <v>0</v>
       </c>
-      <c r="AF327" t="inlineStr"/>
       <c r="AG327" t="b">
         <v>0</v>
       </c>
@@ -36805,10 +36790,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127085276</v>
+        <v>127085355</v>
       </c>
       <c r="B328" t="n">
-        <v>91333</v>
+        <v>79014</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -36816,21 +36801,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -36840,10 +36825,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>511826</v>
+        <v>511486</v>
       </c>
       <c r="R328" t="n">
-        <v>6732810</v>
+        <v>6733131</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -36902,10 +36887,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127085336</v>
+        <v>127085151</v>
       </c>
       <c r="B329" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36913,34 +36898,39 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P329" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>512117</v>
+        <v>511484</v>
       </c>
       <c r="R329" t="n">
-        <v>6733256</v>
+        <v>6733091</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36973,6 +36963,11 @@
       <c r="AA329" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -36999,10 +36994,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127085359</v>
+        <v>127085276</v>
       </c>
       <c r="B330" t="n">
-        <v>79011</v>
+        <v>91339</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -37010,21 +37005,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -37034,10 +37029,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>511498</v>
+        <v>511826</v>
       </c>
       <c r="R330" t="n">
-        <v>6733163</v>
+        <v>6732810</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -37096,45 +37091,50 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127085355</v>
+        <v>127085456</v>
       </c>
       <c r="B331" t="n">
-        <v>79011</v>
+        <v>5176</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>511486</v>
+        <v>511592</v>
       </c>
       <c r="R331" t="n">
-        <v>6733131</v>
+        <v>6733099</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -37193,50 +37193,54 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>127085151</v>
+        <v>127085171</v>
       </c>
       <c r="B332" t="n">
-        <v>57657</v>
+        <v>4772</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>511484</v>
+        <v>512121</v>
       </c>
       <c r="R332" t="n">
-        <v>6733091</v>
+        <v>6733244</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -37271,17 +37275,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD332" t="b">
         <v>0</v>
       </c>
       <c r="AE332" t="b">
         <v>0</v>
       </c>
+      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -37402,10 +37402,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>127085129</v>
+        <v>127085363</v>
       </c>
       <c r="B334" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -37413,21 +37413,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -37437,10 +37437,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>512128</v>
+        <v>511515</v>
       </c>
       <c r="R334" t="n">
-        <v>6733072</v>
+        <v>6733167</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -37499,10 +37499,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>127085363</v>
+        <v>127085383</v>
       </c>
       <c r="B335" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -37534,10 +37534,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>511515</v>
+        <v>511963</v>
       </c>
       <c r="R335" t="n">
-        <v>6733167</v>
+        <v>6732874</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -37596,45 +37596,50 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>127085383</v>
+        <v>127085083</v>
       </c>
       <c r="B336" t="n">
-        <v>79011</v>
+        <v>5196</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P336" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>511963</v>
+        <v>512159</v>
       </c>
       <c r="R336" t="n">
-        <v>6732874</v>
+        <v>6733145</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -37693,38 +37698,47 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>127085083</v>
+        <v>127085267</v>
       </c>
       <c r="B337" t="n">
-        <v>5196</v>
+        <v>98442</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr"/>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
@@ -37733,10 +37747,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>512159</v>
+        <v>512119</v>
       </c>
       <c r="R337" t="n">
-        <v>6733145</v>
+        <v>6733261</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -37769,6 +37783,11 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -37795,59 +37814,45 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>127085267</v>
+        <v>127085129</v>
       </c>
       <c r="B338" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>512119</v>
+        <v>512128</v>
       </c>
       <c r="R338" t="n">
-        <v>6733261</v>
+        <v>6733072</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -37880,11 +37885,6 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -37914,7 +37914,7 @@
         <v>127085387</v>
       </c>
       <c r="B339" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>127085425</v>
       </c>
       <c r="B340" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>127085385</v>
       </c>
       <c r="B341" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -38202,50 +38202,53 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127085197</v>
+        <v>127085163</v>
       </c>
       <c r="B342" t="n">
-        <v>57654</v>
+        <v>56849</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>511667</v>
+        <v>511501</v>
       </c>
       <c r="R342" t="n">
-        <v>6732993</v>
+        <v>6733147</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -38304,53 +38307,50 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127085163</v>
+        <v>127085197</v>
       </c>
       <c r="B343" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M343" t="inlineStr"/>
-      <c r="N343" t="inlineStr"/>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P343" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>511501</v>
+        <v>511667</v>
       </c>
       <c r="R343" t="n">
-        <v>6733147</v>
+        <v>6732993</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -38409,32 +38409,32 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127085386</v>
+        <v>127085219</v>
       </c>
       <c r="B344" t="n">
-        <v>79011</v>
+        <v>91779</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
@@ -38444,10 +38444,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>511933</v>
+        <v>511664</v>
       </c>
       <c r="R344" t="n">
-        <v>6732941</v>
+        <v>6732778</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -38506,10 +38506,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>127085389</v>
+        <v>127085126</v>
       </c>
       <c r="B345" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -38517,21 +38517,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -38541,10 +38541,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>511971</v>
+        <v>512043</v>
       </c>
       <c r="R345" t="n">
-        <v>6732939</v>
+        <v>6732961</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -38603,10 +38603,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>127085392</v>
+        <v>127085386</v>
       </c>
       <c r="B346" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -38638,10 +38638,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>512047</v>
+        <v>511933</v>
       </c>
       <c r="R346" t="n">
-        <v>6732964</v>
+        <v>6732941</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -38700,10 +38700,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127085384</v>
+        <v>127085389</v>
       </c>
       <c r="B347" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -38735,10 +38735,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>511951</v>
+        <v>511971</v>
       </c>
       <c r="R347" t="n">
-        <v>6732870</v>
+        <v>6732939</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -38797,10 +38797,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127085173</v>
+        <v>127085392</v>
       </c>
       <c r="B348" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38808,43 +38808,34 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>512096</v>
+        <v>512047</v>
       </c>
       <c r="R348" t="n">
-        <v>6733103</v>
+        <v>6732964</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -38903,32 +38894,32 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>127085219</v>
+        <v>127085384</v>
       </c>
       <c r="B349" t="n">
-        <v>91773</v>
+        <v>79014</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
@@ -38938,10 +38929,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>511664</v>
+        <v>511951</v>
       </c>
       <c r="R349" t="n">
-        <v>6732778</v>
+        <v>6732870</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -39000,10 +38991,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127085126</v>
+        <v>127085201</v>
       </c>
       <c r="B350" t="n">
-        <v>91319</v>
+        <v>57654</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -39011,34 +39002,39 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P350" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>512043</v>
+        <v>512082</v>
       </c>
       <c r="R350" t="n">
-        <v>6732961</v>
+        <v>6733093</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -39097,10 +39093,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127085201</v>
+        <v>127085173</v>
       </c>
       <c r="B351" t="n">
-        <v>57654</v>
+        <v>57817</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -39108,27 +39104,31 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -39137,10 +39137,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>512082</v>
+        <v>512096</v>
       </c>
       <c r="R351" t="n">
-        <v>6733093</v>
+        <v>6733103</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -39318,7 +39318,7 @@
         <v>127079331</v>
       </c>
       <c r="B353" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>127086241</v>
       </c>
       <c r="B354" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>127086095</v>
       </c>
       <c r="B357" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>127078642</v>
       </c>
       <c r="B358" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>127078718</v>
       </c>
       <c r="B361" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40319,10 +40319,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>127069147</v>
+        <v>127078700</v>
       </c>
       <c r="B362" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40330,34 +40330,38 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>512042</v>
+        <v>512074</v>
       </c>
       <c r="R362" t="n">
-        <v>6732964</v>
+        <v>6733265</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -40389,7 +40393,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -40399,7 +40403,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -40536,7 +40540,7 @@
         <v>127106618</v>
       </c>
       <c r="B364" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40649,10 +40653,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>127078700</v>
+        <v>127069147</v>
       </c>
       <c r="B365" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -40660,38 +40664,34 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>512074</v>
+        <v>512042</v>
       </c>
       <c r="R365" t="n">
-        <v>6733265</v>
+        <v>6732964</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -40723,7 +40723,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD365" t="b">
@@ -41216,7 +41216,7 @@
         <v>127158796</v>
       </c>
       <c r="B370" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>127151913</v>
       </c>
       <c r="B371" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>127151868</v>
       </c>
       <c r="B374" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -41770,10 +41770,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>127147125</v>
+        <v>127151856</v>
       </c>
       <c r="B375" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41781,34 +41781,34 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>511478</v>
+        <v>511687</v>
       </c>
       <c r="R375" t="n">
-        <v>6733039</v>
+        <v>6733140</v>
       </c>
       <c r="S375" t="n">
         <v>9</v>
@@ -41840,7 +41840,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -41850,12 +41850,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>På stående Gran högstubbe</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD375" t="b">
@@ -41882,10 +41877,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>127151856</v>
+        <v>127147125</v>
       </c>
       <c r="B376" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -41893,34 +41888,34 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>511687</v>
+        <v>511478</v>
       </c>
       <c r="R376" t="n">
-        <v>6733140</v>
+        <v>6733039</v>
       </c>
       <c r="S376" t="n">
         <v>9</v>
@@ -41952,7 +41947,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -41962,7 +41957,12 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>På stående Gran högstubbe</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -41992,7 +41992,7 @@
         <v>127158638</v>
       </c>
       <c r="B377" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>127151718</v>
       </c>
       <c r="B378" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>127151062</v>
       </c>
       <c r="B380" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>127192913</v>
       </c>
       <c r="B381" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -42654,50 +42654,45 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>127170587</v>
+        <v>127173471</v>
       </c>
       <c r="B383" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>511448</v>
+        <v>511580</v>
       </c>
       <c r="R383" t="n">
-        <v>6733009</v>
+        <v>6733109</v>
       </c>
       <c r="S383" t="n">
         <v>9</v>
@@ -42729,7 +42724,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -42739,7 +42734,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -42766,48 +42761,57 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>127173471</v>
+        <v>127194531</v>
       </c>
       <c r="B384" t="n">
-        <v>79011</v>
+        <v>4772</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>511580</v>
+        <v>511649</v>
       </c>
       <c r="R384" t="n">
-        <v>6733109</v>
+        <v>6733002</v>
       </c>
       <c r="S384" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -42836,7 +42840,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -42846,7 +42850,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -42855,6 +42859,7 @@
       <c r="AE384" t="b">
         <v>0</v>
       </c>
+      <c r="AF384" t="inlineStr"/>
       <c r="AG384" t="b">
         <v>0</v>
       </c>
@@ -42873,7 +42878,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>127194531</v>
+        <v>127170587</v>
       </c>
       <c r="B385" t="n">
         <v>4772</v>
@@ -42902,28 +42907,24 @@
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N385" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>511649</v>
+        <v>511448</v>
       </c>
       <c r="R385" t="n">
-        <v>6733002</v>
+        <v>6733009</v>
       </c>
       <c r="S385" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -42952,7 +42953,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -42962,7 +42963,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -42971,7 +42972,6 @@
       <c r="AE385" t="b">
         <v>0</v>
       </c>
-      <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="b">
         <v>0</v>
       </c>
@@ -43107,10 +43107,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>127150596</v>
+        <v>127170314</v>
       </c>
       <c r="B387" t="n">
-        <v>5196</v>
+        <v>58516</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -43118,39 +43118,43 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>105930</v>
+        <v>208249</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr"/>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>511636</v>
+        <v>511427</v>
       </c>
       <c r="R387" t="n">
-        <v>6733075</v>
+        <v>6733063</v>
       </c>
       <c r="S387" t="n">
         <v>9</v>
@@ -43177,27 +43181,22 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>Tretå hål i samma</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -43224,10 +43223,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>127170314</v>
+        <v>127150596</v>
       </c>
       <c r="B388" t="n">
-        <v>58516</v>
+        <v>5196</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43235,43 +43234,39 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>511427</v>
+        <v>511636</v>
       </c>
       <c r="R388" t="n">
-        <v>6733063</v>
+        <v>6733075</v>
       </c>
       <c r="S388" t="n">
         <v>9</v>
@@ -43298,22 +43293,27 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>Tretå hål i samma</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -43340,10 +43340,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>127188096</v>
+        <v>127172040</v>
       </c>
       <c r="B389" t="n">
-        <v>5175</v>
+        <v>79014</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -43351,46 +43351,37 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>511468</v>
+        <v>511528</v>
       </c>
       <c r="R389" t="n">
-        <v>6733032</v>
+        <v>6733011</v>
       </c>
       <c r="S389" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -43419,7 +43410,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -43429,12 +43420,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>På stammen på gran ca17cm</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -43443,7 +43429,6 @@
       <c r="AE389" t="b">
         <v>0</v>
       </c>
-      <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
@@ -43462,10 +43447,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>127172040</v>
+        <v>127188096</v>
       </c>
       <c r="B390" t="n">
-        <v>79011</v>
+        <v>5175</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -43473,37 +43458,46 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>511528</v>
+        <v>511468</v>
       </c>
       <c r="R390" t="n">
-        <v>6733011</v>
+        <v>6733032</v>
       </c>
       <c r="S390" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -43532,7 +43526,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -43542,7 +43536,12 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>På stammen på gran ca17cm</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -43551,6 +43550,7 @@
       <c r="AE390" t="b">
         <v>0</v>
       </c>
+      <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="b">
         <v>0</v>
       </c>
@@ -43916,7 +43916,7 @@
         <v>127194958</v>
       </c>
       <c r="B394" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44592,37 +44592,43 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>127226987</v>
+        <v>127190540</v>
       </c>
       <c r="B400" t="n">
-        <v>79011</v>
+        <v>5196</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
@@ -44630,10 +44636,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>511478</v>
+        <v>511525</v>
       </c>
       <c r="R400" t="n">
-        <v>6733047</v>
+        <v>6733021</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -44660,22 +44666,22 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -44703,43 +44709,37 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>127190540</v>
+        <v>127226987</v>
       </c>
       <c r="B401" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
@@ -44747,10 +44747,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>511525</v>
+        <v>511478</v>
       </c>
       <c r="R401" t="n">
-        <v>6733021</v>
+        <v>6733047</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -44777,22 +44777,22 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD401" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -20596,10 +20596,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126594614</v>
+        <v>126596967</v>
       </c>
       <c r="B170" t="n">
-        <v>56849</v>
+        <v>58516</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20607,16 +20607,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100138</v>
+        <v>208249</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>511943</v>
+        <v>511879</v>
       </c>
       <c r="R170" t="n">
-        <v>6732930</v>
+        <v>6732860</v>
       </c>
       <c r="S170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20676,12 +20676,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Fjäder.</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20708,10 +20703,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126596967</v>
+        <v>126594614</v>
       </c>
       <c r="B171" t="n">
-        <v>58516</v>
+        <v>56849</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20719,16 +20714,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -20743,13 +20738,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>511879</v>
+        <v>511943</v>
       </c>
       <c r="R171" t="n">
-        <v>6732860</v>
+        <v>6732930</v>
       </c>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20778,7 +20773,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20788,7 +20783,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22750,48 +22750,57 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126688780</v>
+        <v>126596788</v>
       </c>
       <c r="B189" t="n">
-        <v>91325</v>
+        <v>56849</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>511776</v>
+        <v>511914</v>
       </c>
       <c r="R189" t="n">
-        <v>6732814</v>
+        <v>6732834</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22818,27 +22827,27 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>En stor vacker ullticka som går under så gott som hela l granlågan. Granen har troligen inte klarat av att stå emot blåsten från hygget efter avverkningen av Skogsstyrelsens Biotopen BARRSKOG N 14-2010.</t>
+          <t>Dessa spår är jättefärska för om så lätta som fjädrarna/dunen är så hade de blåst bort om det kommit en vindpust. Har ställt fråga till tjäderexpert om det kan vara kycklingfjädrar men inte fått svar ännu. Spillning fanns också på platsen. Allt under en rotvälta.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22847,7 +22856,6 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -22859,64 +22867,55 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126596788</v>
+        <v>126688780</v>
       </c>
       <c r="B190" t="n">
-        <v>56849</v>
+        <v>91325</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>511914</v>
+        <v>511776</v>
       </c>
       <c r="R190" t="n">
-        <v>6732834</v>
+        <v>6732814</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22943,27 +22942,27 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Dessa spår är jättefärska för om så lätta som fjädrarna/dunen är så hade de blåst bort om det kommit en vindpust. Har ställt fråga till tjäderexpert om det kan vara kycklingfjädrar men inte fått svar ännu. Spillning fanns också på platsen. Allt under en rotvälta.</t>
+          <t>En stor vacker ullticka som går under så gott som hela l granlågan. Granen har troligen inte klarat av att stå emot blåsten från hygget efter avverkningen av Skogsstyrelsens Biotopen BARRSKOG N 14-2010.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22972,6 +22971,7 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -22983,7 +22983,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -23346,7 +23346,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126688774</v>
+        <v>126688773</v>
       </c>
       <c r="B194" t="n">
         <v>56849</v>
@@ -23377,11 +23377,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -23389,10 +23385,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>511625</v>
+        <v>511607</v>
       </c>
       <c r="R194" t="n">
-        <v>6732869</v>
+        <v>6732885</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -23424,7 +23420,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23434,12 +23430,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Tämligen mycket färsk spillning men även lite äldre</t>
+          <t>Åter ett visitmärke på ett vindfälle som man har sågat av.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23466,7 +23462,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126688773</v>
+        <v>126688774</v>
       </c>
       <c r="B195" t="n">
         <v>56849</v>
@@ -23497,7 +23493,11 @@
       <c r="I195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -23505,10 +23505,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>511607</v>
+        <v>511625</v>
       </c>
       <c r="R195" t="n">
-        <v>6732885</v>
+        <v>6732869</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23550,12 +23550,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Åter ett visitmärke på ett vindfälle som man har sågat av.</t>
+          <t>Tämligen mycket färsk spillning men även lite äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24937,10 +24937,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127085154</v>
+        <v>127085204</v>
       </c>
       <c r="B209" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24948,16 +24948,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -24977,10 +24977,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>512098</v>
+        <v>511872</v>
       </c>
       <c r="R209" t="n">
-        <v>6733172</v>
+        <v>6732834</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25013,11 +25013,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25146,10 +25141,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127085204</v>
+        <v>127085154</v>
       </c>
       <c r="B211" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25157,16 +25152,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25186,10 +25181,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>511872</v>
+        <v>512098</v>
       </c>
       <c r="R211" t="n">
-        <v>6732834</v>
+        <v>6733172</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25222,6 +25217,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25442,10 +25442,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127085149</v>
+        <v>127085196</v>
       </c>
       <c r="B214" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25453,16 +25453,16 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -25482,10 +25482,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>512180</v>
+        <v>511574</v>
       </c>
       <c r="R214" t="n">
-        <v>6733152</v>
+        <v>6733042</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25518,11 +25518,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25549,54 +25544,50 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127085168</v>
+        <v>127085198</v>
       </c>
       <c r="B215" t="n">
-        <v>4772</v>
+        <v>57654</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>511692</v>
+        <v>511652</v>
       </c>
       <c r="R215" t="n">
-        <v>6732762</v>
+        <v>6732988</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25637,7 +25628,6 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -25656,50 +25646,54 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127085196</v>
+        <v>127085168</v>
       </c>
       <c r="B216" t="n">
-        <v>57654</v>
+        <v>4772</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>511574</v>
+        <v>511692</v>
       </c>
       <c r="R216" t="n">
-        <v>6733042</v>
+        <v>6732762</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25740,6 +25734,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -25758,10 +25753,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127085198</v>
+        <v>127085149</v>
       </c>
       <c r="B217" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25769,16 +25764,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -25798,10 +25793,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>511652</v>
+        <v>512180</v>
       </c>
       <c r="R217" t="n">
-        <v>6732988</v>
+        <v>6733152</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25834,6 +25829,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26248,45 +26248,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127085358</v>
+        <v>127085082</v>
       </c>
       <c r="B222" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>511490</v>
+        <v>512165</v>
       </c>
       <c r="R222" t="n">
-        <v>6733157</v>
+        <v>6733149</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26345,7 +26350,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127085351</v>
+        <v>127085358</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -26380,10 +26385,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>511657</v>
+        <v>511490</v>
       </c>
       <c r="R223" t="n">
-        <v>6733151</v>
+        <v>6733157</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26442,10 +26447,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127085133</v>
+        <v>127085351</v>
       </c>
       <c r="B224" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26453,21 +26458,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -26477,10 +26482,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>512166</v>
+        <v>511657</v>
       </c>
       <c r="R224" t="n">
-        <v>6733144</v>
+        <v>6733151</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26539,7 +26544,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127085131</v>
+        <v>127085133</v>
       </c>
       <c r="B225" t="n">
         <v>91325</v>
@@ -26574,10 +26579,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>512090</v>
+        <v>512166</v>
       </c>
       <c r="R225" t="n">
-        <v>6733122</v>
+        <v>6733144</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26733,50 +26738,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127085082</v>
+        <v>127085131</v>
       </c>
       <c r="B227" t="n">
-        <v>5196</v>
+        <v>91325</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>512165</v>
+        <v>512090</v>
       </c>
       <c r="R227" t="n">
-        <v>6733149</v>
+        <v>6733122</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26946,32 +26946,27 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127085102</v>
+        <v>127085255</v>
       </c>
       <c r="B229" t="n">
-        <v>91290</v>
+        <v>91732</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26981,10 +26976,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>511825</v>
+        <v>512240</v>
       </c>
       <c r="R229" t="n">
-        <v>6732811</v>
+        <v>6733098</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27043,32 +27038,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127085379</v>
+        <v>127085102</v>
       </c>
       <c r="B230" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -27078,10 +27073,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>511665</v>
+        <v>511825</v>
       </c>
       <c r="R230" t="n">
-        <v>6732789</v>
+        <v>6732811</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27140,10 +27135,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127085256</v>
+        <v>127085379</v>
       </c>
       <c r="B231" t="n">
-        <v>91798</v>
+        <v>79014</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27151,21 +27146,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -27175,10 +27170,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>512114</v>
+        <v>511665</v>
       </c>
       <c r="R231" t="n">
-        <v>6733092</v>
+        <v>6732789</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27237,10 +27232,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127085366</v>
+        <v>127085256</v>
       </c>
       <c r="B232" t="n">
-        <v>79014</v>
+        <v>91798</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27248,21 +27243,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -27272,10 +27267,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>511539</v>
+        <v>512114</v>
       </c>
       <c r="R232" t="n">
-        <v>6733139</v>
+        <v>6733092</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27334,7 +27329,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127085338</v>
+        <v>127085366</v>
       </c>
       <c r="B233" t="n">
         <v>79014</v>
@@ -27369,10 +27364,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>512088</v>
+        <v>511539</v>
       </c>
       <c r="R233" t="n">
-        <v>6733228</v>
+        <v>6733139</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27431,7 +27426,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127085348</v>
+        <v>127085338</v>
       </c>
       <c r="B234" t="n">
         <v>79014</v>
@@ -27466,10 +27461,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>511691</v>
+        <v>512088</v>
       </c>
       <c r="R234" t="n">
-        <v>6733100</v>
+        <v>6733228</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27528,7 +27523,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127085428</v>
+        <v>127085348</v>
       </c>
       <c r="B235" t="n">
         <v>79014</v>
@@ -27563,10 +27558,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>512217</v>
+        <v>511691</v>
       </c>
       <c r="R235" t="n">
-        <v>6733093</v>
+        <v>6733100</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27625,10 +27620,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127085255</v>
+        <v>127085428</v>
       </c>
       <c r="B236" t="n">
-        <v>91732</v>
+        <v>79014</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27636,16 +27631,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -27655,10 +27655,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>512240</v>
+        <v>512217</v>
       </c>
       <c r="R236" t="n">
-        <v>6733098</v>
+        <v>6733093</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27717,10 +27717,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127085390</v>
+        <v>127085441</v>
       </c>
       <c r="B237" t="n">
-        <v>79014</v>
+        <v>88728</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27728,21 +27728,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -27752,10 +27752,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>512008</v>
+        <v>512169</v>
       </c>
       <c r="R237" t="n">
-        <v>6732919</v>
+        <v>6733007</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27814,7 +27814,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127085427</v>
+        <v>127085430</v>
       </c>
       <c r="B238" t="n">
         <v>79014</v>
@@ -27849,10 +27849,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>512225</v>
+        <v>512198</v>
       </c>
       <c r="R238" t="n">
-        <v>6733108</v>
+        <v>6733079</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27911,10 +27911,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127085127</v>
+        <v>127085436</v>
       </c>
       <c r="B239" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27922,21 +27922,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -27946,10 +27946,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>511987</v>
+        <v>512103</v>
       </c>
       <c r="R239" t="n">
-        <v>6732947</v>
+        <v>6733103</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28008,32 +28008,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127085441</v>
+        <v>127085107</v>
       </c>
       <c r="B240" t="n">
-        <v>88728</v>
+        <v>91290</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -28043,10 +28043,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>512169</v>
+        <v>512190</v>
       </c>
       <c r="R240" t="n">
-        <v>6733007</v>
+        <v>6733157</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28105,10 +28105,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127085125</v>
+        <v>127085390</v>
       </c>
       <c r="B241" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28116,21 +28116,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -28140,10 +28140,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>512223</v>
+        <v>512008</v>
       </c>
       <c r="R241" t="n">
-        <v>6733163</v>
+        <v>6732919</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28202,10 +28202,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127085278</v>
+        <v>127085427</v>
       </c>
       <c r="B242" t="n">
-        <v>91550</v>
+        <v>79014</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28213,21 +28213,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1101</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -28237,10 +28237,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>512146</v>
+        <v>512225</v>
       </c>
       <c r="R242" t="n">
-        <v>6733140</v>
+        <v>6733108</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28299,50 +28299,45 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127085458</v>
+        <v>127085127</v>
       </c>
       <c r="B243" t="n">
-        <v>5176</v>
+        <v>91325</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>512072</v>
+        <v>511987</v>
       </c>
       <c r="R243" t="n">
-        <v>6733076</v>
+        <v>6732947</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28401,50 +28396,45 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127085459</v>
+        <v>127085278</v>
       </c>
       <c r="B244" t="n">
-        <v>5176</v>
+        <v>91550</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>512124</v>
+        <v>512146</v>
       </c>
       <c r="R244" t="n">
-        <v>6733193</v>
+        <v>6733140</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28503,54 +28493,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127085169</v>
+        <v>127085125</v>
       </c>
       <c r="B245" t="n">
-        <v>4772</v>
+        <v>91325</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>512072</v>
+        <v>512223</v>
       </c>
       <c r="R245" t="n">
-        <v>6733076</v>
+        <v>6733163</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28591,7 +28572,6 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -28610,38 +28590,47 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127085080</v>
+        <v>127085266</v>
       </c>
       <c r="B246" t="n">
-        <v>5196</v>
+        <v>98442</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -28650,10 +28639,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>512226</v>
+        <v>511616</v>
       </c>
       <c r="R246" t="n">
-        <v>6733157</v>
+        <v>6733018</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28686,6 +28675,11 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28712,47 +28706,38 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127085266</v>
+        <v>127085458</v>
       </c>
       <c r="B247" t="n">
-        <v>98442</v>
+        <v>5176</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -28761,10 +28746,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>511616</v>
+        <v>512072</v>
       </c>
       <c r="R247" t="n">
-        <v>6733018</v>
+        <v>6733076</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28797,11 +28782,6 @@
       <c r="AA247" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28828,45 +28808,50 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127085430</v>
+        <v>127085459</v>
       </c>
       <c r="B248" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>512198</v>
+        <v>512124</v>
       </c>
       <c r="R248" t="n">
-        <v>6733079</v>
+        <v>6733193</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28925,45 +28910,54 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127085436</v>
+        <v>127085169</v>
       </c>
       <c r="B249" t="n">
-        <v>79014</v>
+        <v>4772</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>512103</v>
+        <v>512072</v>
       </c>
       <c r="R249" t="n">
-        <v>6733103</v>
+        <v>6733076</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29004,6 +28998,7 @@
       <c r="AE249" t="b">
         <v>0</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -29022,10 +29017,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127085107</v>
+        <v>127085080</v>
       </c>
       <c r="B250" t="n">
-        <v>91290</v>
+        <v>5196</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29033,31 +29028,36 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>512190</v>
+        <v>512226</v>
       </c>
       <c r="R250" t="n">
         <v>6733157</v>
@@ -29119,10 +29119,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127085373</v>
+        <v>127085132</v>
       </c>
       <c r="B251" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29130,21 +29130,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -29154,10 +29154,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>511572</v>
+        <v>512170</v>
       </c>
       <c r="R251" t="n">
-        <v>6733106</v>
+        <v>6733213</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29216,10 +29216,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127085432</v>
+        <v>127085158</v>
       </c>
       <c r="B252" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29227,34 +29227,39 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>512143</v>
+        <v>512000</v>
       </c>
       <c r="R252" t="n">
-        <v>6733060</v>
+        <v>6732919</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29287,6 +29292,11 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29313,10 +29323,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127085132</v>
+        <v>127085155</v>
       </c>
       <c r="B253" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29324,34 +29334,39 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>512170</v>
+        <v>512141</v>
       </c>
       <c r="R253" t="n">
-        <v>6733213</v>
+        <v>6733245</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29384,6 +29399,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29410,10 +29430,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127085153</v>
+        <v>127085373</v>
       </c>
       <c r="B254" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29421,39 +29441,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>511379</v>
+        <v>511572</v>
       </c>
       <c r="R254" t="n">
-        <v>6733133</v>
+        <v>6733106</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29486,11 +29501,6 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29517,10 +29527,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127085158</v>
+        <v>127085432</v>
       </c>
       <c r="B255" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29528,39 +29538,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>512000</v>
+        <v>512143</v>
       </c>
       <c r="R255" t="n">
-        <v>6732919</v>
+        <v>6733060</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29593,11 +29598,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29624,7 +29624,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127085155</v>
+        <v>127085153</v>
       </c>
       <c r="B256" t="n">
         <v>57657</v>
@@ -29664,10 +29664,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>512141</v>
+        <v>511379</v>
       </c>
       <c r="R256" t="n">
-        <v>6733245</v>
+        <v>6733133</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29704,7 +29704,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Troliga spår efter födosök</t>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30022,10 +30022,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127085152</v>
+        <v>127085206</v>
       </c>
       <c r="B260" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30033,16 +30033,16 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -30062,10 +30062,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>511598</v>
+        <v>512152</v>
       </c>
       <c r="R260" t="n">
-        <v>6733104</v>
+        <v>6733134</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30098,11 +30098,6 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30129,7 +30124,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127085148</v>
+        <v>127085152</v>
       </c>
       <c r="B261" t="n">
         <v>57657</v>
@@ -30160,7 +30155,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
@@ -30169,10 +30164,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>512064</v>
+        <v>511598</v>
       </c>
       <c r="R261" t="n">
-        <v>6733117</v>
+        <v>6733104</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30209,7 +30204,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30236,10 +30231,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127085206</v>
+        <v>127085148</v>
       </c>
       <c r="B262" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30247,16 +30242,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -30267,7 +30262,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -30276,10 +30271,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>512152</v>
+        <v>512064</v>
       </c>
       <c r="R262" t="n">
-        <v>6733134</v>
+        <v>6733117</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30312,6 +30307,11 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30435,10 +30435,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127085147</v>
+        <v>127085360</v>
       </c>
       <c r="B264" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30446,39 +30446,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>512035</v>
+        <v>511493</v>
       </c>
       <c r="R264" t="n">
-        <v>6732916</v>
+        <v>6733172</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30511,11 +30506,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30542,10 +30532,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127085161</v>
+        <v>127085434</v>
       </c>
       <c r="B265" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30553,39 +30543,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>512225</v>
+        <v>512138</v>
       </c>
       <c r="R265" t="n">
-        <v>6733108</v>
+        <v>6733072</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30618,11 +30603,6 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30649,10 +30629,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127085203</v>
+        <v>127085394</v>
       </c>
       <c r="B266" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30660,39 +30640,34 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>511657</v>
+        <v>511981</v>
       </c>
       <c r="R266" t="n">
-        <v>6732987</v>
+        <v>6732975</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30751,7 +30726,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127085360</v>
+        <v>127085381</v>
       </c>
       <c r="B267" t="n">
         <v>79014</v>
@@ -30786,10 +30761,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>511493</v>
+        <v>511930</v>
       </c>
       <c r="R267" t="n">
-        <v>6733172</v>
+        <v>6732852</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30848,32 +30823,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127085434</v>
+        <v>127085101</v>
       </c>
       <c r="B268" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30883,10 +30858,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>512138</v>
+        <v>511664</v>
       </c>
       <c r="R268" t="n">
-        <v>6733072</v>
+        <v>6732778</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30945,7 +30920,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127085394</v>
+        <v>127085370</v>
       </c>
       <c r="B269" t="n">
         <v>79014</v>
@@ -30980,10 +30955,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>511981</v>
+        <v>511551</v>
       </c>
       <c r="R269" t="n">
-        <v>6732975</v>
+        <v>6733097</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31042,10 +31017,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127085381</v>
+        <v>127085203</v>
       </c>
       <c r="B270" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31053,34 +31028,39 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>511930</v>
+        <v>511657</v>
       </c>
       <c r="R270" t="n">
-        <v>6732852</v>
+        <v>6732987</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31139,45 +31119,50 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>127085101</v>
+        <v>127085147</v>
       </c>
       <c r="B271" t="n">
-        <v>91290</v>
+        <v>57657</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>511664</v>
+        <v>512035</v>
       </c>
       <c r="R271" t="n">
-        <v>6732778</v>
+        <v>6732916</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31210,6 +31195,11 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31236,10 +31226,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127085370</v>
+        <v>127085161</v>
       </c>
       <c r="B272" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31247,34 +31237,39 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>511551</v>
+        <v>512225</v>
       </c>
       <c r="R272" t="n">
-        <v>6733097</v>
+        <v>6733108</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31307,6 +31302,11 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31333,10 +31333,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127085400</v>
+        <v>127085150</v>
       </c>
       <c r="B273" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -31344,34 +31344,39 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>512064</v>
+        <v>512042</v>
       </c>
       <c r="R273" t="n">
-        <v>6733119</v>
+        <v>6732932</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31404,6 +31409,11 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31430,45 +31440,50 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127085378</v>
+        <v>127085084</v>
       </c>
       <c r="B274" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>511688</v>
+        <v>512162</v>
       </c>
       <c r="R274" t="n">
-        <v>6733025</v>
+        <v>6733053</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31527,10 +31542,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>127085095</v>
+        <v>127085135</v>
       </c>
       <c r="B275" t="n">
-        <v>91290</v>
+        <v>98465</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -31538,34 +31553,43 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5447</v>
+        <v>219847</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>512236</v>
+        <v>511795</v>
       </c>
       <c r="R275" t="n">
-        <v>6733047</v>
+        <v>6732846</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31624,32 +31648,32 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>127085220</v>
+        <v>127085400</v>
       </c>
       <c r="B276" t="n">
-        <v>91779</v>
+        <v>79014</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31659,10 +31683,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>512044</v>
+        <v>512064</v>
       </c>
       <c r="R276" t="n">
-        <v>6732937</v>
+        <v>6733119</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31721,10 +31745,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127085150</v>
+        <v>127085378</v>
       </c>
       <c r="B277" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -31732,39 +31756,34 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>512042</v>
+        <v>511688</v>
       </c>
       <c r="R277" t="n">
-        <v>6732932</v>
+        <v>6733025</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31797,11 +31816,6 @@
       <c r="AA277" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31828,10 +31842,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127085084</v>
+        <v>127085095</v>
       </c>
       <c r="B278" t="n">
-        <v>5196</v>
+        <v>91290</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -31839,39 +31853,34 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>512162</v>
+        <v>512236</v>
       </c>
       <c r="R278" t="n">
-        <v>6733053</v>
+        <v>6733047</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31930,54 +31939,45 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>127085135</v>
+        <v>127085220</v>
       </c>
       <c r="B279" t="n">
-        <v>98465</v>
+        <v>91779</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>219847</v>
+        <v>1209</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>511795</v>
+        <v>512044</v>
       </c>
       <c r="R279" t="n">
-        <v>6732846</v>
+        <v>6732937</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32036,50 +32036,45 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>127085457</v>
+        <v>127085354</v>
       </c>
       <c r="B280" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>511991</v>
+        <v>511469</v>
       </c>
       <c r="R280" t="n">
-        <v>6732947</v>
+        <v>6733119</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32138,10 +32133,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>127085157</v>
+        <v>127085396</v>
       </c>
       <c r="B281" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32149,39 +32144,34 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P281" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>511525</v>
+        <v>512072</v>
       </c>
       <c r="R281" t="n">
-        <v>6732923</v>
+        <v>6733073</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -32214,11 +32204,6 @@
       <c r="AA281" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -32245,50 +32230,45 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>127085159</v>
+        <v>127085106</v>
       </c>
       <c r="B282" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P282" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>512044</v>
+        <v>512184</v>
       </c>
       <c r="R282" t="n">
-        <v>6732923</v>
+        <v>6733202</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -32321,11 +32301,6 @@
       <c r="AA282" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32352,7 +32327,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127085354</v>
+        <v>127085372</v>
       </c>
       <c r="B283" t="n">
         <v>79014</v>
@@ -32387,10 +32362,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>511469</v>
+        <v>511560</v>
       </c>
       <c r="R283" t="n">
-        <v>6733119</v>
+        <v>6733087</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -32449,7 +32424,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>127085396</v>
+        <v>127085402</v>
       </c>
       <c r="B284" t="n">
         <v>79014</v>
@@ -32484,10 +32459,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>512072</v>
+        <v>512044</v>
       </c>
       <c r="R284" t="n">
-        <v>6733073</v>
+        <v>6733119</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -32546,32 +32521,32 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>127085106</v>
+        <v>127085398</v>
       </c>
       <c r="B285" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -32581,10 +32556,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>512184</v>
+        <v>512062</v>
       </c>
       <c r="R285" t="n">
-        <v>6733202</v>
+        <v>6733087</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -32643,7 +32618,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>127085372</v>
+        <v>127085424</v>
       </c>
       <c r="B286" t="n">
         <v>79014</v>
@@ -32678,10 +32653,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>511560</v>
+        <v>512144</v>
       </c>
       <c r="R286" t="n">
-        <v>6733087</v>
+        <v>6733010</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -32740,10 +32715,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>127085402</v>
+        <v>127085157</v>
       </c>
       <c r="B287" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32751,34 +32726,39 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P287" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>512044</v>
+        <v>511525</v>
       </c>
       <c r="R287" t="n">
-        <v>6733119</v>
+        <v>6732923</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -32811,6 +32791,11 @@
       <c r="AA287" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32837,10 +32822,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>127085398</v>
+        <v>127085159</v>
       </c>
       <c r="B288" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32848,34 +32833,39 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>512062</v>
+        <v>512044</v>
       </c>
       <c r="R288" t="n">
-        <v>6733087</v>
+        <v>6732923</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -32908,6 +32898,11 @@
       <c r="AA288" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32934,45 +32929,50 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>127085424</v>
+        <v>127085457</v>
       </c>
       <c r="B289" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P289" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>512144</v>
+        <v>511991</v>
       </c>
       <c r="R289" t="n">
-        <v>6733010</v>
+        <v>6732947</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -33031,32 +33031,27 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>127085439</v>
+        <v>127085254</v>
       </c>
       <c r="B290" t="n">
-        <v>98359</v>
+        <v>91732</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -33066,10 +33061,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>511871</v>
+        <v>512201</v>
       </c>
       <c r="R290" t="n">
-        <v>6732830</v>
+        <v>6733180</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -33128,27 +33123,32 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>127085254</v>
+        <v>127085439</v>
       </c>
       <c r="B291" t="n">
-        <v>91732</v>
+        <v>98359</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>6040186</v>
+        <v>219790</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -33158,10 +33158,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>512201</v>
+        <v>511871</v>
       </c>
       <c r="R291" t="n">
-        <v>6733180</v>
+        <v>6732830</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -33220,54 +33220,50 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>127085257</v>
+        <v>127085440</v>
       </c>
       <c r="B292" t="n">
-        <v>98442</v>
+        <v>57578</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>512275</v>
+        <v>511689</v>
       </c>
       <c r="R292" t="n">
-        <v>6733032</v>
+        <v>6733024</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -33326,10 +33322,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>127085440</v>
+        <v>127085377</v>
       </c>
       <c r="B293" t="n">
-        <v>57578</v>
+        <v>79014</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -33337,39 +33333,34 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P293" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>511689</v>
+        <v>511609</v>
       </c>
       <c r="R293" t="n">
-        <v>6733024</v>
+        <v>6733076</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -33428,7 +33419,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>127085377</v>
+        <v>127085399</v>
       </c>
       <c r="B294" t="n">
         <v>79014</v>
@@ -33463,10 +33454,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>511609</v>
+        <v>512061</v>
       </c>
       <c r="R294" t="n">
-        <v>6733076</v>
+        <v>6733112</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -33525,7 +33516,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>127085399</v>
+        <v>127085423</v>
       </c>
       <c r="B295" t="n">
         <v>79014</v>
@@ -33560,10 +33551,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>512061</v>
+        <v>512135</v>
       </c>
       <c r="R295" t="n">
-        <v>6733112</v>
+        <v>6733010</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33622,7 +33613,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>127085423</v>
+        <v>127085371</v>
       </c>
       <c r="B296" t="n">
         <v>79014</v>
@@ -33657,10 +33648,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>512135</v>
+        <v>511560</v>
       </c>
       <c r="R296" t="n">
-        <v>6733010</v>
+        <v>6733100</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33719,45 +33710,54 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>127085371</v>
+        <v>127085257</v>
       </c>
       <c r="B297" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>511560</v>
+        <v>512275</v>
       </c>
       <c r="R297" t="n">
-        <v>6733100</v>
+        <v>6733032</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33816,50 +33816,45 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>127085202</v>
+        <v>127085103</v>
       </c>
       <c r="B298" t="n">
-        <v>57654</v>
+        <v>91290</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>511500</v>
+        <v>511864</v>
       </c>
       <c r="R298" t="n">
-        <v>6733094</v>
+        <v>6732830</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -33918,10 +33913,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>127085194</v>
+        <v>127085421</v>
       </c>
       <c r="B299" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -33929,39 +33924,34 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>512121</v>
+        <v>512117</v>
       </c>
       <c r="R299" t="n">
-        <v>6733244</v>
+        <v>6733012</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -34020,32 +34010,32 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>127085103</v>
+        <v>127085422</v>
       </c>
       <c r="B300" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -34055,10 +34045,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>511864</v>
+        <v>512133</v>
       </c>
       <c r="R300" t="n">
-        <v>6732830</v>
+        <v>6733013</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -34117,7 +34107,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>127085421</v>
+        <v>127085376</v>
       </c>
       <c r="B301" t="n">
         <v>79014</v>
@@ -34152,10 +34142,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>512117</v>
+        <v>511593</v>
       </c>
       <c r="R301" t="n">
-        <v>6733012</v>
+        <v>6733083</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -34214,7 +34204,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>127085422</v>
+        <v>127085369</v>
       </c>
       <c r="B302" t="n">
         <v>79014</v>
@@ -34249,10 +34239,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>512133</v>
+        <v>511534</v>
       </c>
       <c r="R302" t="n">
-        <v>6733013</v>
+        <v>6733112</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -34311,7 +34301,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>127085376</v>
+        <v>127085391</v>
       </c>
       <c r="B303" t="n">
         <v>79014</v>
@@ -34346,10 +34336,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>511593</v>
+        <v>512053</v>
       </c>
       <c r="R303" t="n">
-        <v>6733083</v>
+        <v>6732969</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -34408,7 +34398,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>127085369</v>
+        <v>127085374</v>
       </c>
       <c r="B304" t="n">
         <v>79014</v>
@@ -34443,10 +34433,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>511534</v>
+        <v>511592</v>
       </c>
       <c r="R304" t="n">
-        <v>6733112</v>
+        <v>6733098</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -34505,10 +34495,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>127085391</v>
+        <v>127085194</v>
       </c>
       <c r="B305" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34516,34 +34506,39 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>512053</v>
+        <v>512121</v>
       </c>
       <c r="R305" t="n">
-        <v>6732969</v>
+        <v>6733244</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -34602,10 +34597,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>127085374</v>
+        <v>127085202</v>
       </c>
       <c r="B306" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34613,34 +34608,39 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>511592</v>
+        <v>511500</v>
       </c>
       <c r="R306" t="n">
-        <v>6733098</v>
+        <v>6733094</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -34699,10 +34699,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>127085364</v>
+        <v>127085085</v>
       </c>
       <c r="B307" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -34710,21 +34710,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -34734,10 +34734,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>511529</v>
+        <v>511488</v>
       </c>
       <c r="R307" t="n">
-        <v>6733159</v>
+        <v>6733088</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -34796,10 +34796,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>127085085</v>
+        <v>127085364</v>
       </c>
       <c r="B308" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34807,21 +34807,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -34831,10 +34831,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>511488</v>
+        <v>511529</v>
       </c>
       <c r="R308" t="n">
-        <v>6733088</v>
+        <v>6733159</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -35184,7 +35184,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>127085199</v>
+        <v>127085195</v>
       </c>
       <c r="B312" t="n">
         <v>57654</v>
@@ -35224,10 +35224,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>511661</v>
+        <v>511486</v>
       </c>
       <c r="R312" t="n">
-        <v>6732784</v>
+        <v>6733121</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -35286,7 +35286,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>127085195</v>
+        <v>127085199</v>
       </c>
       <c r="B313" t="n">
         <v>57654</v>
@@ -35326,10 +35326,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>511486</v>
+        <v>511661</v>
       </c>
       <c r="R313" t="n">
-        <v>6733121</v>
+        <v>6732784</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -35485,10 +35485,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>127085367</v>
+        <v>127085200</v>
       </c>
       <c r="B315" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35496,34 +35496,39 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>511537</v>
+        <v>511772</v>
       </c>
       <c r="R315" t="n">
-        <v>6733131</v>
+        <v>6732831</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -35582,10 +35587,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>127085435</v>
+        <v>127085193</v>
       </c>
       <c r="B316" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35593,34 +35598,39 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P316" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>512140</v>
+        <v>511626</v>
       </c>
       <c r="R316" t="n">
-        <v>6733078</v>
+        <v>6733097</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -35653,6 +35663,11 @@
       <c r="AA316" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35679,10 +35694,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>127085401</v>
+        <v>127085144</v>
       </c>
       <c r="B317" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35690,34 +35705,39 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P317" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>512056</v>
+        <v>511510</v>
       </c>
       <c r="R317" t="n">
-        <v>6733111</v>
+        <v>6733106</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -35750,6 +35770,11 @@
       <c r="AA317" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -35776,45 +35801,59 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>127085352</v>
+        <v>127085264</v>
       </c>
       <c r="B318" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P318" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>511672</v>
+        <v>512226</v>
       </c>
       <c r="R318" t="n">
-        <v>6733158</v>
+        <v>6733149</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -35847,6 +35886,11 @@
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -35873,7 +35917,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>127085365</v>
+        <v>127085367</v>
       </c>
       <c r="B319" t="n">
         <v>79014</v>
@@ -35908,10 +35952,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>511539</v>
+        <v>511537</v>
       </c>
       <c r="R319" t="n">
-        <v>6733143</v>
+        <v>6733131</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -35970,7 +36014,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>127085368</v>
+        <v>127085435</v>
       </c>
       <c r="B320" t="n">
         <v>79014</v>
@@ -36005,10 +36049,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>511537</v>
+        <v>512140</v>
       </c>
       <c r="R320" t="n">
-        <v>6733122</v>
+        <v>6733078</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -36067,7 +36111,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>127085388</v>
+        <v>127085401</v>
       </c>
       <c r="B321" t="n">
         <v>79014</v>
@@ -36102,10 +36146,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>511962</v>
+        <v>512056</v>
       </c>
       <c r="R321" t="n">
-        <v>6732936</v>
+        <v>6733111</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -36164,10 +36208,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>127085144</v>
+        <v>127085352</v>
       </c>
       <c r="B322" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36175,39 +36219,34 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P322" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>511510</v>
+        <v>511672</v>
       </c>
       <c r="R322" t="n">
-        <v>6733106</v>
+        <v>6733158</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -36240,11 +36279,6 @@
       <c r="AA322" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36271,10 +36305,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127085200</v>
+        <v>127085365</v>
       </c>
       <c r="B323" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36282,39 +36316,34 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P323" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>511772</v>
+        <v>511539</v>
       </c>
       <c r="R323" t="n">
-        <v>6732831</v>
+        <v>6733143</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -36373,10 +36402,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127085193</v>
+        <v>127085368</v>
       </c>
       <c r="B324" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36384,39 +36413,34 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P324" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>511626</v>
+        <v>511537</v>
       </c>
       <c r="R324" t="n">
-        <v>6733097</v>
+        <v>6733122</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -36449,11 +36473,6 @@
       <c r="AA324" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC324" t="inlineStr">
-        <is>
-          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36480,59 +36499,45 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>127085264</v>
+        <v>127085388</v>
       </c>
       <c r="B325" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>512226</v>
+        <v>511962</v>
       </c>
       <c r="R325" t="n">
-        <v>6733149</v>
+        <v>6732936</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -36565,11 +36570,6 @@
       <c r="AA325" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36596,10 +36596,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127085336</v>
+        <v>127085276</v>
       </c>
       <c r="B326" t="n">
-        <v>79014</v>
+        <v>91339</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36607,21 +36607,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -36631,10 +36631,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>512117</v>
+        <v>511826</v>
       </c>
       <c r="R326" t="n">
-        <v>6733256</v>
+        <v>6732810</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36693,10 +36693,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127085359</v>
+        <v>127085151</v>
       </c>
       <c r="B327" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36704,34 +36704,39 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P327" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>511498</v>
+        <v>511484</v>
       </c>
       <c r="R327" t="n">
-        <v>6733163</v>
+        <v>6733091</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -36764,6 +36769,11 @@
       <c r="AA327" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -36790,45 +36800,50 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127085355</v>
+        <v>127085456</v>
       </c>
       <c r="B328" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P328" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>511486</v>
+        <v>511592</v>
       </c>
       <c r="R328" t="n">
-        <v>6733131</v>
+        <v>6733099</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -36887,50 +36902,54 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127085151</v>
+        <v>127085171</v>
       </c>
       <c r="B329" t="n">
-        <v>57657</v>
+        <v>4772</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>511484</v>
+        <v>512121</v>
       </c>
       <c r="R329" t="n">
-        <v>6733091</v>
+        <v>6733244</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36965,17 +36984,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD329" t="b">
         <v>0</v>
       </c>
       <c r="AE329" t="b">
         <v>0</v>
       </c>
+      <c r="AF329" t="inlineStr"/>
       <c r="AG329" t="b">
         <v>0</v>
       </c>
@@ -36994,45 +37009,50 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127085276</v>
+        <v>127085081</v>
       </c>
       <c r="B330" t="n">
-        <v>91339</v>
+        <v>5196</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P330" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>511826</v>
+        <v>511695</v>
       </c>
       <c r="R330" t="n">
-        <v>6732810</v>
+        <v>6732765</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -37091,50 +37111,45 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127085456</v>
+        <v>127085336</v>
       </c>
       <c r="B331" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>511592</v>
+        <v>512117</v>
       </c>
       <c r="R331" t="n">
-        <v>6733099</v>
+        <v>6733256</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -37193,54 +37208,45 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>127085171</v>
+        <v>127085359</v>
       </c>
       <c r="B332" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>512121</v>
+        <v>511498</v>
       </c>
       <c r="R332" t="n">
-        <v>6733244</v>
+        <v>6733163</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -37281,7 +37287,6 @@
       <c r="AE332" t="b">
         <v>0</v>
       </c>
-      <c r="AF332" t="inlineStr"/>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -37300,50 +37305,45 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>127085081</v>
+        <v>127085355</v>
       </c>
       <c r="B333" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P333" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>511695</v>
+        <v>511486</v>
       </c>
       <c r="R333" t="n">
-        <v>6732765</v>
+        <v>6733131</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -37698,59 +37698,45 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>127085267</v>
+        <v>127085129</v>
       </c>
       <c r="B337" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>512119</v>
+        <v>512128</v>
       </c>
       <c r="R337" t="n">
-        <v>6733261</v>
+        <v>6733072</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -37783,11 +37769,6 @@
       <c r="AA337" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -37814,45 +37795,59 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>127085129</v>
+        <v>127085267</v>
       </c>
       <c r="B338" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P338" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>512128</v>
+        <v>512119</v>
       </c>
       <c r="R338" t="n">
-        <v>6733072</v>
+        <v>6733261</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -37885,6 +37880,11 @@
       <c r="AA338" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -37911,10 +37911,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>127085387</v>
+        <v>127085197</v>
       </c>
       <c r="B339" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -37922,34 +37922,39 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>511959</v>
+        <v>511667</v>
       </c>
       <c r="R339" t="n">
-        <v>6732929</v>
+        <v>6732993</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -38008,45 +38013,53 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>127085425</v>
+        <v>127085163</v>
       </c>
       <c r="B340" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>512152</v>
+        <v>511501</v>
       </c>
       <c r="R340" t="n">
-        <v>6733002</v>
+        <v>6733147</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -38105,7 +38118,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>127085385</v>
+        <v>127085387</v>
       </c>
       <c r="B341" t="n">
         <v>79014</v>
@@ -38140,10 +38153,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>511929</v>
+        <v>511959</v>
       </c>
       <c r="R341" t="n">
-        <v>6732872</v>
+        <v>6732929</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -38202,53 +38215,45 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127085163</v>
+        <v>127085425</v>
       </c>
       <c r="B342" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>511501</v>
+        <v>512152</v>
       </c>
       <c r="R342" t="n">
-        <v>6733147</v>
+        <v>6733002</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -38307,10 +38312,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127085197</v>
+        <v>127085385</v>
       </c>
       <c r="B343" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -38318,39 +38323,34 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P343" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>511667</v>
+        <v>511929</v>
       </c>
       <c r="R343" t="n">
-        <v>6732993</v>
+        <v>6732872</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -38409,32 +38409,32 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127085219</v>
+        <v>127085126</v>
       </c>
       <c r="B344" t="n">
-        <v>91779</v>
+        <v>91325</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
@@ -38444,10 +38444,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>511664</v>
+        <v>512043</v>
       </c>
       <c r="R344" t="n">
-        <v>6732778</v>
+        <v>6732961</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -38506,32 +38506,32 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>127085126</v>
+        <v>127085219</v>
       </c>
       <c r="B345" t="n">
-        <v>91325</v>
+        <v>91779</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -38541,10 +38541,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>512043</v>
+        <v>511664</v>
       </c>
       <c r="R345" t="n">
-        <v>6732961</v>
+        <v>6732778</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -38603,10 +38603,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>127085386</v>
+        <v>127085201</v>
       </c>
       <c r="B346" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -38614,34 +38614,39 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P346" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>511933</v>
+        <v>512082</v>
       </c>
       <c r="R346" t="n">
-        <v>6732941</v>
+        <v>6733093</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -38700,10 +38705,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127085389</v>
+        <v>127085173</v>
       </c>
       <c r="B347" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -38711,34 +38716,43 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P347" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>511971</v>
+        <v>512096</v>
       </c>
       <c r="R347" t="n">
-        <v>6732939</v>
+        <v>6733103</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -38797,7 +38811,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>127085392</v>
+        <v>127085386</v>
       </c>
       <c r="B348" t="n">
         <v>79014</v>
@@ -38832,10 +38846,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>512047</v>
+        <v>511933</v>
       </c>
       <c r="R348" t="n">
-        <v>6732964</v>
+        <v>6732941</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -38894,7 +38908,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>127085384</v>
+        <v>127085389</v>
       </c>
       <c r="B349" t="n">
         <v>79014</v>
@@ -38929,10 +38943,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>511951</v>
+        <v>511971</v>
       </c>
       <c r="R349" t="n">
-        <v>6732870</v>
+        <v>6732939</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -38991,10 +39005,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127085201</v>
+        <v>127085392</v>
       </c>
       <c r="B350" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -39002,39 +39016,34 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P350" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>512082</v>
+        <v>512047</v>
       </c>
       <c r="R350" t="n">
-        <v>6733093</v>
+        <v>6732964</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -39093,10 +39102,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127085173</v>
+        <v>127085384</v>
       </c>
       <c r="B351" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -39104,43 +39113,34 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>512096</v>
+        <v>511951</v>
       </c>
       <c r="R351" t="n">
-        <v>6733103</v>
+        <v>6732870</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -39427,10 +39427,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>127086241</v>
+        <v>126688779</v>
       </c>
       <c r="B354" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -39438,34 +39438,42 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Hackmora, Hackmora, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>512081</v>
+        <v>511820</v>
       </c>
       <c r="R354" t="n">
-        <v>6733261</v>
+        <v>6732809</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -39492,22 +39500,27 @@
       </c>
       <c r="Y354" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>Färska ringhack, borde tyda på häckning i Moberg våren - sommaren 2025! Med ringhack från olika tider måste man kunna dra slutsatsen att tretåig hackspett har ett permanent revir på Mobergkammen.  Jag har fått hacken bekräftade av ornitolog.</t>
         </is>
       </c>
       <c r="AD354" t="b">
@@ -39518,6 +39531,16 @@
       </c>
       <c r="AG354" t="b">
         <v>0</v>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>En trädlängd öster om en avverkad Nyckelbiotop, SKS N 14-2010 BARRSKOG, rörligt markvatten? myr?, ett blött skogsmaskinspår och instabil mark. Efter hela den hyggeskanten har träden ramlat in mot A 53849-2022. en trädlängd öster om detta gigantiska plockepinn hittades en, levande gran med färska ringhack.</t>
+        </is>
       </c>
       <c r="AT354" t="inlineStr"/>
       <c r="AW354" t="inlineStr">
@@ -39534,10 +39557,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>126688779</v>
+        <v>127086241</v>
       </c>
       <c r="B355" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39545,42 +39568,34 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Hackmora, Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>511820</v>
+        <v>512081</v>
       </c>
       <c r="R355" t="n">
-        <v>6732809</v>
+        <v>6733261</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -39607,27 +39622,22 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>20:56</t>
-        </is>
-      </c>
-      <c r="AC355" t="inlineStr">
-        <is>
-          <t>Färska ringhack, borde tyda på häckning i Moberg våren - sommaren 2025! Med ringhack från olika tider måste man kunna dra slutsatsen att tretåig hackspett har ett permanent revir på Mobergkammen.  Jag har fått hacken bekräftade av ornitolog.</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -39638,16 +39648,6 @@
       </c>
       <c r="AG355" t="b">
         <v>0</v>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI355" t="inlineStr">
-        <is>
-          <t>En trädlängd öster om en avverkad Nyckelbiotop, SKS N 14-2010 BARRSKOG, rörligt markvatten? myr?, ett blött skogsmaskinspår och instabil mark. Efter hela den hyggeskanten har träden ramlat in mot A 53849-2022. en trädlängd öster om detta gigantiska plockepinn hittades en, levande gran med färska ringhack.</t>
-        </is>
       </c>
       <c r="AT355" t="inlineStr"/>
       <c r="AW355" t="inlineStr">
@@ -40319,10 +40319,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>127078700</v>
+        <v>127069147</v>
       </c>
       <c r="B362" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40330,38 +40330,34 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
-      <c r="M362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>512074</v>
+        <v>512042</v>
       </c>
       <c r="R362" t="n">
-        <v>6733265</v>
+        <v>6732964</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -40393,7 +40389,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -40403,7 +40399,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -40653,10 +40649,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>127069147</v>
+        <v>127078700</v>
       </c>
       <c r="B365" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -40664,34 +40660,38 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>512042</v>
+        <v>512074</v>
       </c>
       <c r="R365" t="n">
-        <v>6732964</v>
+        <v>6733265</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -40723,7 +40723,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD365" t="b">
@@ -42654,48 +42654,57 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>127173471</v>
+        <v>127188353</v>
       </c>
       <c r="B383" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>511580</v>
+        <v>511468</v>
       </c>
       <c r="R383" t="n">
-        <v>6733109</v>
+        <v>6733032</v>
       </c>
       <c r="S383" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -42724,7 +42733,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -42734,7 +42743,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -42743,6 +42752,7 @@
       <c r="AE383" t="b">
         <v>0</v>
       </c>
+      <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
@@ -42761,57 +42771,48 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>127194531</v>
+        <v>127173471</v>
       </c>
       <c r="B384" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>511649</v>
+        <v>511580</v>
       </c>
       <c r="R384" t="n">
-        <v>6733002</v>
+        <v>6733109</v>
       </c>
       <c r="S384" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -42840,7 +42841,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -42850,7 +42851,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -42859,7 +42860,6 @@
       <c r="AE384" t="b">
         <v>0</v>
       </c>
-      <c r="AF384" t="inlineStr"/>
       <c r="AG384" t="b">
         <v>0</v>
       </c>
@@ -42878,7 +42878,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>127170587</v>
+        <v>127194531</v>
       </c>
       <c r="B385" t="n">
         <v>4772</v>
@@ -42907,24 +42907,28 @@
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>511448</v>
+        <v>511649</v>
       </c>
       <c r="R385" t="n">
-        <v>6733009</v>
+        <v>6733002</v>
       </c>
       <c r="S385" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -42953,7 +42957,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -42963,7 +42967,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -42972,6 +42976,7 @@
       <c r="AE385" t="b">
         <v>0</v>
       </c>
+      <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="b">
         <v>0</v>
       </c>
@@ -42990,10 +42995,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>127188353</v>
+        <v>127170587</v>
       </c>
       <c r="B386" t="n">
-        <v>5196</v>
+        <v>4772</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -43001,46 +43006,42 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
-      <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N386" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>511468</v>
+        <v>511448</v>
       </c>
       <c r="R386" t="n">
-        <v>6733032</v>
+        <v>6733009</v>
       </c>
       <c r="S386" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -43069,7 +43070,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -43079,7 +43080,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -43088,7 +43089,6 @@
       <c r="AE386" t="b">
         <v>0</v>
       </c>
-      <c r="AF386" t="inlineStr"/>
       <c r="AG386" t="b">
         <v>0</v>
       </c>
@@ -43107,10 +43107,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>127170314</v>
+        <v>127150596</v>
       </c>
       <c r="B387" t="n">
-        <v>58516</v>
+        <v>5196</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -43118,43 +43118,39 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>511427</v>
+        <v>511636</v>
       </c>
       <c r="R387" t="n">
-        <v>6733063</v>
+        <v>6733075</v>
       </c>
       <c r="S387" t="n">
         <v>9</v>
@@ -43181,22 +43177,27 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>Tretå hål i samma</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -43223,10 +43224,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>127150596</v>
+        <v>127170314</v>
       </c>
       <c r="B388" t="n">
-        <v>5196</v>
+        <v>58516</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43234,39 +43235,43 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>105930</v>
+        <v>208249</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr"/>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>511636</v>
+        <v>511427</v>
       </c>
       <c r="R388" t="n">
-        <v>6733075</v>
+        <v>6733063</v>
       </c>
       <c r="S388" t="n">
         <v>9</v>
@@ -43293,27 +43298,22 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC388" t="inlineStr">
-        <is>
-          <t>Tretå hål i samma</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD388" t="b">
@@ -43340,10 +43340,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>127172040</v>
+        <v>127188096</v>
       </c>
       <c r="B389" t="n">
-        <v>79014</v>
+        <v>5175</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -43351,37 +43351,46 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>102204</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr"/>
       <c r="P389" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>511528</v>
+        <v>511468</v>
       </c>
       <c r="R389" t="n">
-        <v>6733011</v>
+        <v>6733032</v>
       </c>
       <c r="S389" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -43410,7 +43419,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -43420,7 +43429,12 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>På stammen på gran ca17cm</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -43429,6 +43443,7 @@
       <c r="AE389" t="b">
         <v>0</v>
       </c>
+      <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
@@ -43447,10 +43462,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>127188096</v>
+        <v>127172040</v>
       </c>
       <c r="B390" t="n">
-        <v>5175</v>
+        <v>79014</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -43458,46 +43473,37 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>102204</v>
+        <v>6425</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N390" t="inlineStr"/>
       <c r="P390" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>511468</v>
+        <v>511528</v>
       </c>
       <c r="R390" t="n">
-        <v>6733032</v>
+        <v>6733011</v>
       </c>
       <c r="S390" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -43526,7 +43532,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -43536,12 +43542,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC390" t="inlineStr">
-        <is>
-          <t>På stammen på gran ca17cm</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -43550,7 +43551,6 @@
       <c r="AE390" t="b">
         <v>0</v>
       </c>
-      <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="b">
         <v>0</v>
       </c>
@@ -44592,43 +44592,37 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>127190540</v>
+        <v>127226987</v>
       </c>
       <c r="B400" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
@@ -44636,10 +44630,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>511525</v>
+        <v>511478</v>
       </c>
       <c r="R400" t="n">
-        <v>6733021</v>
+        <v>6733047</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -44666,22 +44660,22 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z400" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -44709,37 +44703,43 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>127226987</v>
+        <v>127190540</v>
       </c>
       <c r="B401" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
@@ -44747,10 +44747,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>511478</v>
+        <v>511525</v>
       </c>
       <c r="R401" t="n">
-        <v>6733047</v>
+        <v>6733021</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -44777,22 +44777,22 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD401" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -21479,10 +21479,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126592405</v>
+        <v>126596924</v>
       </c>
       <c r="B178" t="n">
-        <v>5176</v>
+        <v>98362</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21490,39 +21490,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100526</v>
+        <v>223597</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>512034</v>
+        <v>511881</v>
       </c>
       <c r="R178" t="n">
-        <v>6732916</v>
+        <v>6732831</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21554,7 +21549,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21564,7 +21559,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Många Jungfru Marienycklar, mycket blött, troligen asp, små alar</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21592,10 +21592,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126596924</v>
+        <v>126592405</v>
       </c>
       <c r="B179" t="n">
-        <v>98362</v>
+        <v>5176</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21603,34 +21603,39 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>223597</v>
+        <v>100526</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>511881</v>
+        <v>512034</v>
       </c>
       <c r="R179" t="n">
-        <v>6732831</v>
+        <v>6732916</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21662,7 +21667,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -21672,12 +21677,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Många Jungfru Marienycklar, mycket blött, troligen asp, små alar</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -26248,50 +26248,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127085082</v>
+        <v>127085358</v>
       </c>
       <c r="B222" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>512165</v>
+        <v>511490</v>
       </c>
       <c r="R222" t="n">
-        <v>6733149</v>
+        <v>6733157</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26350,7 +26345,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127085358</v>
+        <v>127085351</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -26385,10 +26380,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>511490</v>
+        <v>511657</v>
       </c>
       <c r="R223" t="n">
-        <v>6733157</v>
+        <v>6733151</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26447,10 +26442,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127085351</v>
+        <v>127085133</v>
       </c>
       <c r="B224" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26458,21 +26453,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -26482,10 +26477,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>511657</v>
+        <v>512166</v>
       </c>
       <c r="R224" t="n">
-        <v>6733151</v>
+        <v>6733144</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26544,7 +26539,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127085133</v>
+        <v>127085134</v>
       </c>
       <c r="B225" t="n">
         <v>91325</v>
@@ -26579,10 +26574,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>512166</v>
+        <v>512215</v>
       </c>
       <c r="R225" t="n">
-        <v>6733144</v>
+        <v>6733164</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26641,7 +26636,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127085134</v>
+        <v>127085131</v>
       </c>
       <c r="B226" t="n">
         <v>91325</v>
@@ -26676,10 +26671,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>512215</v>
+        <v>512090</v>
       </c>
       <c r="R226" t="n">
-        <v>6733164</v>
+        <v>6733122</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26738,45 +26733,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127085131</v>
+        <v>127085082</v>
       </c>
       <c r="B227" t="n">
-        <v>91325</v>
+        <v>5196</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>512090</v>
+        <v>512165</v>
       </c>
       <c r="R227" t="n">
-        <v>6733122</v>
+        <v>6733149</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -29119,10 +29119,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127085132</v>
+        <v>127085153</v>
       </c>
       <c r="B251" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29130,34 +29130,39 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>512170</v>
+        <v>511379</v>
       </c>
       <c r="R251" t="n">
-        <v>6733213</v>
+        <v>6733133</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29190,6 +29195,11 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29624,10 +29634,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127085153</v>
+        <v>127085132</v>
       </c>
       <c r="B256" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29635,39 +29645,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>511379</v>
+        <v>512170</v>
       </c>
       <c r="R256" t="n">
-        <v>6733133</v>
+        <v>6733213</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29700,11 +29705,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30338,10 +30338,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127085092</v>
+        <v>127085147</v>
       </c>
       <c r="B263" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30349,34 +30349,39 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>512081</v>
+        <v>512035</v>
       </c>
       <c r="R263" t="n">
-        <v>6733224</v>
+        <v>6732916</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30409,6 +30414,11 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30435,10 +30445,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127085360</v>
+        <v>127085161</v>
       </c>
       <c r="B264" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30446,34 +30456,39 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>511493</v>
+        <v>512225</v>
       </c>
       <c r="R264" t="n">
-        <v>6733172</v>
+        <v>6733108</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30506,6 +30521,11 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30532,10 +30552,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127085434</v>
+        <v>127085092</v>
       </c>
       <c r="B265" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30543,21 +30563,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -30567,10 +30587,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>512138</v>
+        <v>512081</v>
       </c>
       <c r="R265" t="n">
-        <v>6733072</v>
+        <v>6733224</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30629,7 +30649,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127085394</v>
+        <v>127085360</v>
       </c>
       <c r="B266" t="n">
         <v>79014</v>
@@ -30664,10 +30684,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>511981</v>
+        <v>511493</v>
       </c>
       <c r="R266" t="n">
-        <v>6732975</v>
+        <v>6733172</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30726,7 +30746,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127085381</v>
+        <v>127085434</v>
       </c>
       <c r="B267" t="n">
         <v>79014</v>
@@ -30761,10 +30781,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>511930</v>
+        <v>512138</v>
       </c>
       <c r="R267" t="n">
-        <v>6732852</v>
+        <v>6733072</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30823,32 +30843,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127085101</v>
+        <v>127085394</v>
       </c>
       <c r="B268" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30858,10 +30878,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>511664</v>
+        <v>511981</v>
       </c>
       <c r="R268" t="n">
-        <v>6732778</v>
+        <v>6732975</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30920,7 +30940,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127085370</v>
+        <v>127085381</v>
       </c>
       <c r="B269" t="n">
         <v>79014</v>
@@ -30955,10 +30975,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>511551</v>
+        <v>511930</v>
       </c>
       <c r="R269" t="n">
-        <v>6733097</v>
+        <v>6732852</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31017,50 +31037,45 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127085203</v>
+        <v>127085101</v>
       </c>
       <c r="B270" t="n">
-        <v>57654</v>
+        <v>91290</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>511657</v>
+        <v>511664</v>
       </c>
       <c r="R270" t="n">
-        <v>6732987</v>
+        <v>6732778</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31119,10 +31134,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>127085147</v>
+        <v>127085370</v>
       </c>
       <c r="B271" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31130,39 +31145,34 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P271" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>512035</v>
+        <v>511551</v>
       </c>
       <c r="R271" t="n">
-        <v>6732916</v>
+        <v>6733097</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31195,11 +31205,6 @@
       <c r="AA271" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31226,10 +31231,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>127085161</v>
+        <v>127085203</v>
       </c>
       <c r="B272" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31237,16 +31242,16 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -31266,10 +31271,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>512225</v>
+        <v>511657</v>
       </c>
       <c r="R272" t="n">
-        <v>6733108</v>
+        <v>6732987</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31302,11 +31307,6 @@
       <c r="AA272" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31333,50 +31333,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>127085150</v>
+        <v>127085220</v>
       </c>
       <c r="B273" t="n">
-        <v>57657</v>
+        <v>91779</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P273" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>512042</v>
+        <v>512044</v>
       </c>
       <c r="R273" t="n">
-        <v>6732932</v>
+        <v>6732937</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31409,11 +31404,6 @@
       <c r="AA273" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31440,10 +31430,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>127085084</v>
+        <v>127085135</v>
       </c>
       <c r="B274" t="n">
-        <v>5196</v>
+        <v>98465</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -31451,27 +31441,31 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>105930</v>
+        <v>219847</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -31480,10 +31474,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>512162</v>
+        <v>511795</v>
       </c>
       <c r="R274" t="n">
-        <v>6733053</v>
+        <v>6732846</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31542,54 +31536,45 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>127085135</v>
+        <v>127085400</v>
       </c>
       <c r="B275" t="n">
-        <v>98465</v>
+        <v>79014</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>511795</v>
+        <v>512064</v>
       </c>
       <c r="R275" t="n">
-        <v>6732846</v>
+        <v>6733119</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31648,7 +31633,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>127085400</v>
+        <v>127085378</v>
       </c>
       <c r="B276" t="n">
         <v>79014</v>
@@ -31683,10 +31668,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>512064</v>
+        <v>511688</v>
       </c>
       <c r="R276" t="n">
-        <v>6733119</v>
+        <v>6733025</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31745,45 +31730,45 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>127085378</v>
+        <v>127085095</v>
       </c>
       <c r="B277" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Hackmorkull, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>511688</v>
+        <v>512236</v>
       </c>
       <c r="R277" t="n">
-        <v>6733025</v>
+        <v>6733047</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31842,45 +31827,50 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>127085095</v>
+        <v>127085150</v>
       </c>
       <c r="B278" t="n">
-        <v>91290</v>
+        <v>57657</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Hackmorkull, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>512236</v>
+        <v>512042</v>
       </c>
       <c r="R278" t="n">
-        <v>6733047</v>
+        <v>6732932</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31913,6 +31903,11 @@
       <c r="AA278" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31939,45 +31934,50 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>127085220</v>
+        <v>127085084</v>
       </c>
       <c r="B279" t="n">
-        <v>91779</v>
+        <v>5196</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>512044</v>
+        <v>512162</v>
       </c>
       <c r="R279" t="n">
-        <v>6732937</v>
+        <v>6733053</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -33220,10 +33220,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>127085440</v>
+        <v>127085377</v>
       </c>
       <c r="B292" t="n">
-        <v>57578</v>
+        <v>79014</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -33231,39 +33231,34 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P292" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>511689</v>
+        <v>511609</v>
       </c>
       <c r="R292" t="n">
-        <v>6733024</v>
+        <v>6733076</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -33322,7 +33317,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>127085377</v>
+        <v>127085399</v>
       </c>
       <c r="B293" t="n">
         <v>79014</v>
@@ -33357,10 +33352,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>511609</v>
+        <v>512061</v>
       </c>
       <c r="R293" t="n">
-        <v>6733076</v>
+        <v>6733112</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -33419,7 +33414,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>127085399</v>
+        <v>127085423</v>
       </c>
       <c r="B294" t="n">
         <v>79014</v>
@@ -33454,10 +33449,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>512061</v>
+        <v>512135</v>
       </c>
       <c r="R294" t="n">
-        <v>6733112</v>
+        <v>6733010</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -33516,7 +33511,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>127085423</v>
+        <v>127085371</v>
       </c>
       <c r="B295" t="n">
         <v>79014</v>
@@ -33551,10 +33546,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>512135</v>
+        <v>511560</v>
       </c>
       <c r="R295" t="n">
-        <v>6733010</v>
+        <v>6733100</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33613,10 +33608,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>127085371</v>
+        <v>127085440</v>
       </c>
       <c r="B296" t="n">
-        <v>79014</v>
+        <v>57578</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -33624,34 +33619,39 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P296" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>511560</v>
+        <v>511689</v>
       </c>
       <c r="R296" t="n">
-        <v>6733100</v>
+        <v>6733024</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -35485,10 +35485,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>127085200</v>
+        <v>127085367</v>
       </c>
       <c r="B315" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35496,39 +35496,34 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P315" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>511772</v>
+        <v>511537</v>
       </c>
       <c r="R315" t="n">
-        <v>6732831</v>
+        <v>6733131</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -35587,10 +35582,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>127085193</v>
+        <v>127085435</v>
       </c>
       <c r="B316" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35598,39 +35593,34 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P316" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>511626</v>
+        <v>512140</v>
       </c>
       <c r="R316" t="n">
-        <v>6733097</v>
+        <v>6733078</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -35663,11 +35653,6 @@
       <c r="AA316" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35694,10 +35679,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>127085144</v>
+        <v>127085401</v>
       </c>
       <c r="B317" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35705,39 +35690,34 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P317" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>511510</v>
+        <v>512056</v>
       </c>
       <c r="R317" t="n">
-        <v>6733106</v>
+        <v>6733111</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -35770,11 +35750,6 @@
       <c r="AA317" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -35801,59 +35776,45 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>127085264</v>
+        <v>127085352</v>
       </c>
       <c r="B318" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>512226</v>
+        <v>511672</v>
       </c>
       <c r="R318" t="n">
-        <v>6733149</v>
+        <v>6733158</v>
       </c>
       <c r="S318" t="n">
         <v>10</v>
@@ -35886,11 +35847,6 @@
       <c r="AA318" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -35917,7 +35873,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>127085367</v>
+        <v>127085365</v>
       </c>
       <c r="B319" t="n">
         <v>79014</v>
@@ -35952,10 +35908,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>511537</v>
+        <v>511539</v>
       </c>
       <c r="R319" t="n">
-        <v>6733131</v>
+        <v>6733143</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -36014,7 +35970,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>127085435</v>
+        <v>127085368</v>
       </c>
       <c r="B320" t="n">
         <v>79014</v>
@@ -36049,10 +36005,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>512140</v>
+        <v>511537</v>
       </c>
       <c r="R320" t="n">
-        <v>6733078</v>
+        <v>6733122</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -36111,7 +36067,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>127085401</v>
+        <v>127085388</v>
       </c>
       <c r="B321" t="n">
         <v>79014</v>
@@ -36146,10 +36102,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>512056</v>
+        <v>511962</v>
       </c>
       <c r="R321" t="n">
-        <v>6733111</v>
+        <v>6732936</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -36208,10 +36164,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>127085352</v>
+        <v>127085200</v>
       </c>
       <c r="B322" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36219,34 +36175,39 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P322" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>511672</v>
+        <v>511772</v>
       </c>
       <c r="R322" t="n">
-        <v>6733158</v>
+        <v>6732831</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -36305,10 +36266,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127085365</v>
+        <v>127085193</v>
       </c>
       <c r="B323" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36316,34 +36277,39 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P323" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>511539</v>
+        <v>511626</v>
       </c>
       <c r="R323" t="n">
-        <v>6733143</v>
+        <v>6733097</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -36376,6 +36342,11 @@
       <c r="AA323" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Typiska bohål i mycket gammal tall</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36402,45 +36373,59 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127085368</v>
+        <v>127085264</v>
       </c>
       <c r="B324" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P324" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>511537</v>
+        <v>512226</v>
       </c>
       <c r="R324" t="n">
-        <v>6733122</v>
+        <v>6733149</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -36473,6 +36458,11 @@
       <c r="AA324" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36499,10 +36489,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>127085388</v>
+        <v>127085144</v>
       </c>
       <c r="B325" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36510,34 +36500,39 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P325" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>511962</v>
+        <v>511510</v>
       </c>
       <c r="R325" t="n">
-        <v>6732936</v>
+        <v>6733106</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -36570,6 +36565,11 @@
       <c r="AA325" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>Några år gamla ringhack med minst 60 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36596,45 +36596,50 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127085276</v>
+        <v>127085456</v>
       </c>
       <c r="B326" t="n">
-        <v>91339</v>
+        <v>5176</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P326" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>511826</v>
+        <v>511592</v>
       </c>
       <c r="R326" t="n">
-        <v>6732810</v>
+        <v>6733099</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36693,50 +36698,54 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127085151</v>
+        <v>127085171</v>
       </c>
       <c r="B327" t="n">
-        <v>57657</v>
+        <v>4772</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>511484</v>
+        <v>512121</v>
       </c>
       <c r="R327" t="n">
-        <v>6733091</v>
+        <v>6733244</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -36771,17 +36780,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD327" t="b">
         <v>0</v>
       </c>
       <c r="AE327" t="b">
         <v>0</v>
       </c>
+      <c r="AF327" t="inlineStr"/>
       <c r="AG327" t="b">
         <v>0</v>
       </c>
@@ -36800,50 +36805,45 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127085456</v>
+        <v>127085336</v>
       </c>
       <c r="B328" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P328" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>511592</v>
+        <v>512117</v>
       </c>
       <c r="R328" t="n">
-        <v>6733099</v>
+        <v>6733256</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -36902,54 +36902,45 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127085171</v>
+        <v>127085359</v>
       </c>
       <c r="B329" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>512121</v>
+        <v>511498</v>
       </c>
       <c r="R329" t="n">
-        <v>6733244</v>
+        <v>6733163</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36990,7 +36981,6 @@
       <c r="AE329" t="b">
         <v>0</v>
       </c>
-      <c r="AF329" t="inlineStr"/>
       <c r="AG329" t="b">
         <v>0</v>
       </c>
@@ -37009,50 +36999,45 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127085081</v>
+        <v>127085355</v>
       </c>
       <c r="B330" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P330" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>511695</v>
+        <v>511486</v>
       </c>
       <c r="R330" t="n">
-        <v>6732765</v>
+        <v>6733131</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -37111,10 +37096,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127085336</v>
+        <v>127085276</v>
       </c>
       <c r="B331" t="n">
-        <v>79014</v>
+        <v>91339</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -37122,21 +37107,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -37146,10 +37131,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>512117</v>
+        <v>511826</v>
       </c>
       <c r="R331" t="n">
-        <v>6733256</v>
+        <v>6732810</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -37208,10 +37193,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>127085359</v>
+        <v>127085151</v>
       </c>
       <c r="B332" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -37219,34 +37204,39 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P332" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>511498</v>
+        <v>511484</v>
       </c>
       <c r="R332" t="n">
-        <v>6733163</v>
+        <v>6733091</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -37279,6 +37269,11 @@
       <c r="AA332" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -37305,45 +37300,50 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>127085355</v>
+        <v>127085081</v>
       </c>
       <c r="B333" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P333" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>511486</v>
+        <v>511695</v>
       </c>
       <c r="R333" t="n">
-        <v>6733131</v>
+        <v>6732765</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -37911,10 +37911,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>127085197</v>
+        <v>127085387</v>
       </c>
       <c r="B339" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -37922,39 +37922,34 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>511667</v>
+        <v>511959</v>
       </c>
       <c r="R339" t="n">
-        <v>6732993</v>
+        <v>6732929</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -38013,53 +38008,45 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>127085163</v>
+        <v>127085425</v>
       </c>
       <c r="B340" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>511501</v>
+        <v>512152</v>
       </c>
       <c r="R340" t="n">
-        <v>6733147</v>
+        <v>6733002</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -38118,7 +38105,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>127085387</v>
+        <v>127085385</v>
       </c>
       <c r="B341" t="n">
         <v>79014</v>
@@ -38153,10 +38140,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>511959</v>
+        <v>511929</v>
       </c>
       <c r="R341" t="n">
-        <v>6732929</v>
+        <v>6732872</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -38215,10 +38202,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127085425</v>
+        <v>127085197</v>
       </c>
       <c r="B342" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -38226,34 +38213,39 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P342" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>512152</v>
+        <v>511667</v>
       </c>
       <c r="R342" t="n">
-        <v>6733002</v>
+        <v>6732993</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -38312,45 +38304,53 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127085385</v>
+        <v>127085163</v>
       </c>
       <c r="B343" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>511929</v>
+        <v>511501</v>
       </c>
       <c r="R343" t="n">
-        <v>6732872</v>
+        <v>6733147</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -38409,10 +38409,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>127085126</v>
+        <v>127085173</v>
       </c>
       <c r="B344" t="n">
-        <v>91325</v>
+        <v>57817</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -38420,34 +38420,43 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P344" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>512043</v>
+        <v>512096</v>
       </c>
       <c r="R344" t="n">
-        <v>6732961</v>
+        <v>6733103</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -38506,32 +38515,32 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>127085219</v>
+        <v>127085126</v>
       </c>
       <c r="B345" t="n">
-        <v>91779</v>
+        <v>91325</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -38541,10 +38550,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>511664</v>
+        <v>512043</v>
       </c>
       <c r="R345" t="n">
-        <v>6732778</v>
+        <v>6732961</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -38603,50 +38612,45 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>127085201</v>
+        <v>127085219</v>
       </c>
       <c r="B346" t="n">
-        <v>57654</v>
+        <v>91779</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P346" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>512082</v>
+        <v>511664</v>
       </c>
       <c r="R346" t="n">
-        <v>6733093</v>
+        <v>6732778</v>
       </c>
       <c r="S346" t="n">
         <v>10</v>
@@ -38705,10 +38709,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>127085173</v>
+        <v>127085201</v>
       </c>
       <c r="B347" t="n">
-        <v>57817</v>
+        <v>57654</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -38716,31 +38720,27 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
@@ -38749,10 +38749,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>512096</v>
+        <v>512082</v>
       </c>
       <c r="R347" t="n">
-        <v>6733103</v>
+        <v>6733093</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -40319,10 +40319,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>127069147</v>
+        <v>127078700</v>
       </c>
       <c r="B362" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40330,34 +40330,38 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>512042</v>
+        <v>512074</v>
       </c>
       <c r="R362" t="n">
-        <v>6732964</v>
+        <v>6733265</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -40389,7 +40393,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -40399,7 +40403,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -40649,10 +40653,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>127078700</v>
+        <v>127069147</v>
       </c>
       <c r="B365" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -40660,38 +40664,34 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>512074</v>
+        <v>512042</v>
       </c>
       <c r="R365" t="n">
-        <v>6733265</v>
+        <v>6732964</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -40723,7 +40723,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -40733,7 +40733,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD365" t="b">

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -21032,7 +21032,7 @@
         <v>126591562</v>
       </c>
       <c r="B174" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>126595944</v>
       </c>
       <c r="B175" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>126590847</v>
       </c>
       <c r="B176" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>126597287</v>
       </c>
       <c r="B177" t="n">
-        <v>100624</v>
+        <v>100625</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21479,10 +21479,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126596924</v>
+        <v>126592405</v>
       </c>
       <c r="B178" t="n">
-        <v>98362</v>
+        <v>5176</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21490,34 +21490,39 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>223597</v>
+        <v>100526</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>511881</v>
+        <v>512034</v>
       </c>
       <c r="R178" t="n">
-        <v>6732831</v>
+        <v>6732916</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21549,7 +21554,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21559,12 +21564,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Många Jungfru Marienycklar, mycket blött, troligen asp, små alar</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21592,10 +21592,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126592405</v>
+        <v>126596924</v>
       </c>
       <c r="B179" t="n">
-        <v>5176</v>
+        <v>98363</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21603,39 +21603,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100526</v>
+        <v>223597</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Leksand Moberg, Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>512034</v>
+        <v>511881</v>
       </c>
       <c r="R179" t="n">
-        <v>6732916</v>
+        <v>6732831</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21667,7 +21662,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -21677,7 +21672,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Många Jungfru Marienycklar, mycket blött, troligen asp, små alar</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21708,7 +21708,7 @@
         <v>126594826</v>
       </c>
       <c r="B180" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>126596172</v>
       </c>
       <c r="B181" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>126596593</v>
       </c>
       <c r="B182" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -22159,10 +22159,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126596102</v>
+        <v>126592712</v>
       </c>
       <c r="B184" t="n">
-        <v>56849</v>
+        <v>58027</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22170,42 +22170,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>511892</v>
+        <v>512034</v>
       </c>
       <c r="R184" t="n">
-        <v>6732948</v>
+        <v>6732916</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22237,7 +22229,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22247,12 +22239,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Spillning, trolig blindtarmstömning</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22272,17 +22259,17 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126592712</v>
+        <v>126596102</v>
       </c>
       <c r="B185" t="n">
-        <v>58027</v>
+        <v>56849</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22290,34 +22277,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>512034</v>
+        <v>511892</v>
       </c>
       <c r="R185" t="n">
-        <v>6732916</v>
+        <v>6732948</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22349,7 +22344,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22359,7 +22354,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Spillning, trolig blindtarmstömning</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -22509,7 +22509,7 @@
         <v>126596554</v>
       </c>
       <c r="B187" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>126688780</v>
       </c>
       <c r="B190" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>127085105</v>
       </c>
       <c r="B202" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127085380</v>
+        <v>127085429</v>
       </c>
       <c r="B203" t="n">
         <v>79014</v>
@@ -24370,10 +24370,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>511665</v>
+        <v>512205</v>
       </c>
       <c r="R203" t="n">
-        <v>6732780</v>
+        <v>6733078</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -24432,10 +24432,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127085429</v>
+        <v>127085156</v>
       </c>
       <c r="B204" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24443,34 +24443,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>512205</v>
+        <v>511571</v>
       </c>
       <c r="R204" t="n">
-        <v>6733078</v>
+        <v>6733063</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24503,6 +24508,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24529,7 +24539,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127085156</v>
+        <v>127085145</v>
       </c>
       <c r="B205" t="n">
         <v>57657</v>
@@ -24569,10 +24579,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>511571</v>
+        <v>511991</v>
       </c>
       <c r="R205" t="n">
-        <v>6733063</v>
+        <v>6732936</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24609,7 +24619,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Troliga spår efter födosök</t>
+          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24636,10 +24646,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127085145</v>
+        <v>127085380</v>
       </c>
       <c r="B206" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24647,39 +24657,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>511991</v>
+        <v>511665</v>
       </c>
       <c r="R206" t="n">
-        <v>6732936</v>
+        <v>6732780</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24712,11 +24717,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Några år gamla ringhack med 30 rader på gammal tall</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24937,10 +24937,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127085204</v>
+        <v>127085154</v>
       </c>
       <c r="B209" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24948,16 +24948,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -24977,10 +24977,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>511872</v>
+        <v>512098</v>
       </c>
       <c r="R209" t="n">
-        <v>6732834</v>
+        <v>6733172</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25013,6 +25013,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25141,10 +25146,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127085154</v>
+        <v>127085204</v>
       </c>
       <c r="B211" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25152,16 +25157,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25181,10 +25186,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>512098</v>
+        <v>511872</v>
       </c>
       <c r="R211" t="n">
-        <v>6733172</v>
+        <v>6732834</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25217,11 +25222,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25248,10 +25248,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127085350</v>
+        <v>127085198</v>
       </c>
       <c r="B212" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25259,34 +25259,39 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>511648</v>
+        <v>511652</v>
       </c>
       <c r="R212" t="n">
-        <v>6733131</v>
+        <v>6732988</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -25345,7 +25350,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127085353</v>
+        <v>127085350</v>
       </c>
       <c r="B213" t="n">
         <v>79014</v>
@@ -25380,10 +25385,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>511443</v>
+        <v>511648</v>
       </c>
       <c r="R213" t="n">
-        <v>6733122</v>
+        <v>6733131</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25442,10 +25447,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127085196</v>
+        <v>127085353</v>
       </c>
       <c r="B214" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25453,39 +25458,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>511574</v>
+        <v>511443</v>
       </c>
       <c r="R214" t="n">
-        <v>6733042</v>
+        <v>6733122</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25544,7 +25544,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127085198</v>
+        <v>127085196</v>
       </c>
       <c r="B215" t="n">
         <v>57654</v>
@@ -25584,10 +25584,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>511652</v>
+        <v>511574</v>
       </c>
       <c r="R215" t="n">
-        <v>6732988</v>
+        <v>6733042</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26057,7 +26057,7 @@
         <v>127085175</v>
       </c>
       <c r="B220" t="n">
-        <v>92260</v>
+        <v>92261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26442,10 +26442,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127085133</v>
+        <v>127085131</v>
       </c>
       <c r="B224" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26477,10 +26477,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>512166</v>
+        <v>512090</v>
       </c>
       <c r="R224" t="n">
-        <v>6733144</v>
+        <v>6733122</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26542,7 +26542,7 @@
         <v>127085134</v>
       </c>
       <c r="B225" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26636,45 +26636,50 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127085131</v>
+        <v>127085082</v>
       </c>
       <c r="B226" t="n">
-        <v>91325</v>
+        <v>5196</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>512090</v>
+        <v>512165</v>
       </c>
       <c r="R226" t="n">
-        <v>6733122</v>
+        <v>6733149</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26733,38 +26738,47 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127085082</v>
+        <v>127085269</v>
       </c>
       <c r="B227" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -26773,10 +26787,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>512165</v>
+        <v>512131</v>
       </c>
       <c r="R227" t="n">
-        <v>6733149</v>
+        <v>6733255</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26835,59 +26849,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127085269</v>
+        <v>127085133</v>
       </c>
       <c r="B228" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>512131</v>
+        <v>512166</v>
       </c>
       <c r="R228" t="n">
-        <v>6733255</v>
+        <v>6733144</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26946,27 +26946,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127085255</v>
+        <v>127085102</v>
       </c>
       <c r="B229" t="n">
-        <v>91732</v>
+        <v>91291</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26976,10 +26981,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>512240</v>
+        <v>511825</v>
       </c>
       <c r="R229" t="n">
-        <v>6733098</v>
+        <v>6732811</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -27038,32 +27043,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127085102</v>
+        <v>127085379</v>
       </c>
       <c r="B230" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -27073,10 +27078,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>511825</v>
+        <v>511665</v>
       </c>
       <c r="R230" t="n">
-        <v>6732811</v>
+        <v>6732789</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27135,10 +27140,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127085379</v>
+        <v>127085256</v>
       </c>
       <c r="B231" t="n">
-        <v>79014</v>
+        <v>91799</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27146,21 +27151,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -27170,10 +27175,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>511665</v>
+        <v>512114</v>
       </c>
       <c r="R231" t="n">
-        <v>6732789</v>
+        <v>6733092</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27232,10 +27237,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127085256</v>
+        <v>127085366</v>
       </c>
       <c r="B232" t="n">
-        <v>91798</v>
+        <v>79014</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27243,21 +27248,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -27267,10 +27272,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>512114</v>
+        <v>511539</v>
       </c>
       <c r="R232" t="n">
-        <v>6733092</v>
+        <v>6733139</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27329,7 +27334,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127085366</v>
+        <v>127085338</v>
       </c>
       <c r="B233" t="n">
         <v>79014</v>
@@ -27364,10 +27369,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>511539</v>
+        <v>512088</v>
       </c>
       <c r="R233" t="n">
-        <v>6733139</v>
+        <v>6733228</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27426,7 +27431,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127085338</v>
+        <v>127085348</v>
       </c>
       <c r="B234" t="n">
         <v>79014</v>
@@ -27461,10 +27466,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>512088</v>
+        <v>511691</v>
       </c>
       <c r="R234" t="n">
-        <v>6733228</v>
+        <v>6733100</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27523,7 +27528,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127085348</v>
+        <v>127085428</v>
       </c>
       <c r="B235" t="n">
         <v>79014</v>
@@ -27558,10 +27563,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>511691</v>
+        <v>512217</v>
       </c>
       <c r="R235" t="n">
-        <v>6733100</v>
+        <v>6733093</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27620,10 +27625,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127085428</v>
+        <v>127085255</v>
       </c>
       <c r="B236" t="n">
-        <v>79014</v>
+        <v>91733</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27631,21 +27636,16 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -27655,10 +27655,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>512217</v>
+        <v>512240</v>
       </c>
       <c r="R236" t="n">
-        <v>6733093</v>
+        <v>6733098</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27717,45 +27717,50 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127085441</v>
+        <v>127085080</v>
       </c>
       <c r="B237" t="n">
-        <v>88728</v>
+        <v>5196</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>510</v>
+        <v>105930</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>512169</v>
+        <v>512226</v>
       </c>
       <c r="R237" t="n">
-        <v>6733007</v>
+        <v>6733157</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -28011,7 +28016,7 @@
         <v>127085107</v>
       </c>
       <c r="B240" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28302,7 +28307,7 @@
         <v>127085127</v>
       </c>
       <c r="B243" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28396,10 +28401,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127085278</v>
+        <v>127085441</v>
       </c>
       <c r="B244" t="n">
-        <v>91550</v>
+        <v>88729</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28407,21 +28412,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1101</v>
+        <v>510</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -28431,10 +28436,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>512146</v>
+        <v>512169</v>
       </c>
       <c r="R244" t="n">
-        <v>6733140</v>
+        <v>6733007</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28496,7 +28501,7 @@
         <v>127085125</v>
       </c>
       <c r="B245" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28590,59 +28595,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127085266</v>
+        <v>127085278</v>
       </c>
       <c r="B246" t="n">
-        <v>98442</v>
+        <v>91551</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>511616</v>
+        <v>512146</v>
       </c>
       <c r="R246" t="n">
-        <v>6733018</v>
+        <v>6733140</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28675,11 +28666,6 @@
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -29017,38 +29003,47 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127085080</v>
+        <v>127085266</v>
       </c>
       <c r="B250" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -29057,10 +29052,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>512226</v>
+        <v>511616</v>
       </c>
       <c r="R250" t="n">
-        <v>6733157</v>
+        <v>6733018</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29093,6 +29088,11 @@
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>3 blomstjälkar</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29119,10 +29119,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127085153</v>
+        <v>127085373</v>
       </c>
       <c r="B251" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29130,39 +29130,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>511379</v>
+        <v>511572</v>
       </c>
       <c r="R251" t="n">
-        <v>6733133</v>
+        <v>6733106</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29195,11 +29190,6 @@
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29226,10 +29216,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127085158</v>
+        <v>127085432</v>
       </c>
       <c r="B252" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29237,39 +29227,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>512000</v>
+        <v>512143</v>
       </c>
       <c r="R252" t="n">
-        <v>6732919</v>
+        <v>6733060</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29302,11 +29287,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29333,7 +29313,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127085155</v>
+        <v>127085153</v>
       </c>
       <c r="B253" t="n">
         <v>57657</v>
@@ -29373,10 +29353,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>512141</v>
+        <v>511379</v>
       </c>
       <c r="R253" t="n">
-        <v>6733245</v>
+        <v>6733133</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29413,7 +29393,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Troliga spår efter födosök</t>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29440,10 +29420,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127085373</v>
+        <v>127085158</v>
       </c>
       <c r="B254" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29451,34 +29431,39 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>511572</v>
+        <v>512000</v>
       </c>
       <c r="R254" t="n">
-        <v>6733106</v>
+        <v>6732919</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29511,6 +29496,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29537,10 +29527,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>127085432</v>
+        <v>127085155</v>
       </c>
       <c r="B255" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29548,34 +29538,39 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>512143</v>
+        <v>512141</v>
       </c>
       <c r="R255" t="n">
-        <v>6733060</v>
+        <v>6733245</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29608,6 +29603,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29637,7 +29637,7 @@
         <v>127085132</v>
       </c>
       <c r="B256" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29925,45 +29925,50 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127085221</v>
+        <v>127085152</v>
       </c>
       <c r="B259" t="n">
-        <v>91779</v>
+        <v>57657</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>512146</v>
+        <v>511598</v>
       </c>
       <c r="R259" t="n">
-        <v>6733146</v>
+        <v>6733104</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29996,6 +30001,11 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30022,10 +30032,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127085206</v>
+        <v>127085148</v>
       </c>
       <c r="B260" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30033,16 +30043,16 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -30053,7 +30063,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -30062,10 +30072,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>512152</v>
+        <v>512064</v>
       </c>
       <c r="R260" t="n">
-        <v>6733134</v>
+        <v>6733117</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30098,6 +30108,11 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30124,50 +30139,45 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127085152</v>
+        <v>127085221</v>
       </c>
       <c r="B261" t="n">
-        <v>57657</v>
+        <v>91780</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P261" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>511598</v>
+        <v>512146</v>
       </c>
       <c r="R261" t="n">
-        <v>6733104</v>
+        <v>6733146</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30200,11 +30210,6 @@
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosökpå flera träd</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30231,10 +30236,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127085148</v>
+        <v>127085206</v>
       </c>
       <c r="B262" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30242,16 +30247,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -30262,7 +30267,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -30271,10 +30276,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>512064</v>
+        <v>512152</v>
       </c>
       <c r="R262" t="n">
-        <v>6733117</v>
+        <v>6733134</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30307,11 +30312,6 @@
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30338,10 +30338,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127085147</v>
+        <v>127085394</v>
       </c>
       <c r="B263" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -30349,39 +30349,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P263" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>512035</v>
+        <v>511981</v>
       </c>
       <c r="R263" t="n">
-        <v>6732916</v>
+        <v>6732975</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30414,11 +30409,6 @@
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30445,10 +30435,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127085161</v>
+        <v>127085381</v>
       </c>
       <c r="B264" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30456,39 +30446,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>512225</v>
+        <v>511930</v>
       </c>
       <c r="R264" t="n">
-        <v>6733108</v>
+        <v>6732852</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30521,11 +30506,6 @@
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Troliga spår efter födosök</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30552,10 +30532,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127085092</v>
+        <v>127085147</v>
       </c>
       <c r="B265" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30563,34 +30543,39 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>512081</v>
+        <v>512035</v>
       </c>
       <c r="R265" t="n">
-        <v>6733224</v>
+        <v>6732916</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30623,6 +30608,11 @@
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30649,10 +30639,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127085360</v>
+        <v>127085161</v>
       </c>
       <c r="B266" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30660,34 +30650,39 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>1001